--- a/output/f7/tablas_m1.xlsx
+++ b/output/f7/tablas_m1.xlsx
@@ -4155,480 +4155,1005 @@
     </comment>
     <comment ref="B233" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C233" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D233" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B234" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C234" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D234" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B235" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C235" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D235" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B236" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C236" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D236" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B237" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C237" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D237" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B238" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C238" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D238" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B239" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C239" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D239" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B240" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C240" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D240" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B241" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C233" authorId="0" shapeId="0">
+    <comment ref="C241" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D233" authorId="0" shapeId="0">
+    <comment ref="D241" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B234" authorId="0" shapeId="0">
+    <comment ref="B242" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C234" authorId="0" shapeId="0">
+    <comment ref="C242" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D234" authorId="0" shapeId="0">
+    <comment ref="D242" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B235" authorId="0" shapeId="0">
+    <comment ref="B243" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C235" authorId="0" shapeId="0">
+    <comment ref="C243" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D235" authorId="0" shapeId="0">
+    <comment ref="D243" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B236" authorId="0" shapeId="0">
+    <comment ref="B244" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C236" authorId="0" shapeId="0">
+    <comment ref="C244" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D236" authorId="0" shapeId="0">
+    <comment ref="D244" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B237" authorId="0" shapeId="0">
+    <comment ref="B245" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C237" authorId="0" shapeId="0">
+    <comment ref="C245" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D237" authorId="0" shapeId="0">
+    <comment ref="D245" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B238" authorId="0" shapeId="0">
+    <comment ref="B246" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C238" authorId="0" shapeId="0">
+    <comment ref="C246" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D238" authorId="0" shapeId="0">
+    <comment ref="D246" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B239" authorId="0" shapeId="0">
+    <comment ref="B247" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C239" authorId="0" shapeId="0">
+    <comment ref="C247" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D239" authorId="0" shapeId="0">
+    <comment ref="D247" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B240" authorId="0" shapeId="0">
+    <comment ref="B248" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C240" authorId="0" shapeId="0">
+    <comment ref="C248" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D240" authorId="0" shapeId="0">
+    <comment ref="D248" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B241" authorId="0" shapeId="0">
+    <comment ref="B249" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C241" authorId="0" shapeId="0">
+    <comment ref="C249" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D241" authorId="0" shapeId="0">
+    <comment ref="D249" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B242" authorId="0" shapeId="0">
+    <comment ref="B250" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C242" authorId="0" shapeId="0">
+    <comment ref="C250" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D242" authorId="0" shapeId="0">
+    <comment ref="D250" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B243" authorId="0" shapeId="0">
+    <comment ref="B251" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C243" authorId="0" shapeId="0">
+    <comment ref="C251" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D243" authorId="0" shapeId="0">
+    <comment ref="D251" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B244" authorId="0" shapeId="0">
+    <comment ref="B252" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C244" authorId="0" shapeId="0">
+    <comment ref="C252" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D244" authorId="0" shapeId="0">
+    <comment ref="D252" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B245" authorId="0" shapeId="0">
+    <comment ref="B253" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C245" authorId="0" shapeId="0">
+    <comment ref="C253" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D245" authorId="0" shapeId="0">
+    <comment ref="D253" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B246" authorId="0" shapeId="0">
+    <comment ref="B254" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C246" authorId="0" shapeId="0">
+    <comment ref="C254" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D246" authorId="0" shapeId="0">
+    <comment ref="D254" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B247" authorId="0" shapeId="0">
+    <comment ref="B255" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C255" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D255" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B256" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C256" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D256" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B257" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C257" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D257" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B258" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C258" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D258" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B259" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C259" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D259" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B260" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C260" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D260" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B261" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C261" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D261" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B262" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C262" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D262" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B263" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C263" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D263" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B264" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C264" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D264" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B265" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C265" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D265" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B266" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C266" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D266" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B267" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C267" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D267" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B268" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C268" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D268" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B269" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
+      </text>
+    </comment>
+    <comment ref="C269" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
+      </text>
+    </comment>
+    <comment ref="D269" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
+      </text>
+    </comment>
+    <comment ref="B270" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C270" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D270" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B271" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C271" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D271" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B272" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C272" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D272" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B273" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C273" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D273" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B274" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C274" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D274" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B277" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C277" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D277" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B278" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C278" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D278" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B279" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C279" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D279" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B280" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
+      </text>
+    </comment>
+    <comment ref="C280" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
+      </text>
+    </comment>
+    <comment ref="D280" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
+      </text>
+    </comment>
+    <comment ref="B281" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="C281" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="D281" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="B282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C247" authorId="0" shapeId="0">
+    <comment ref="C282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D247" authorId="0" shapeId="0">
+    <comment ref="D282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B248" authorId="0" shapeId="0">
+    <comment ref="B283" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C248" authorId="0" shapeId="0">
+    <comment ref="C283" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D248" authorId="0" shapeId="0">
+    <comment ref="D283" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B249" authorId="0" shapeId="0">
+    <comment ref="B284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C249" authorId="0" shapeId="0">
+    <comment ref="C284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D249" authorId="0" shapeId="0">
+    <comment ref="D284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B250" authorId="0" shapeId="0">
+    <comment ref="B285" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C250" authorId="0" shapeId="0">
+    <comment ref="C285" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D250" authorId="0" shapeId="0">
+    <comment ref="D285" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B251" authorId="0" shapeId="0">
+    <comment ref="B286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C251" authorId="0" shapeId="0">
+    <comment ref="C286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D251" authorId="0" shapeId="0">
+    <comment ref="D286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B252" authorId="0" shapeId="0">
+    <comment ref="B287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C252" authorId="0" shapeId="0">
+    <comment ref="C287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D252" authorId="0" shapeId="0">
+    <comment ref="D287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B253" authorId="0" shapeId="0">
+    <comment ref="B288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C253" authorId="0" shapeId="0">
+    <comment ref="C288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D253" authorId="0" shapeId="0">
+    <comment ref="D288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B254" authorId="0" shapeId="0">
+    <comment ref="B289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C254" authorId="0" shapeId="0">
+    <comment ref="C289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D254" authorId="0" shapeId="0">
+    <comment ref="D289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B255" authorId="0" shapeId="0">
+    <comment ref="B290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C255" authorId="0" shapeId="0">
+    <comment ref="C290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D255" authorId="0" shapeId="0">
+    <comment ref="D290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B256" authorId="0" shapeId="0">
+    <comment ref="B291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C256" authorId="0" shapeId="0">
+    <comment ref="C291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D256" authorId="0" shapeId="0">
+    <comment ref="D291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B257" authorId="0" shapeId="0">
+    <comment ref="B292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C257" authorId="0" shapeId="0">
+    <comment ref="C292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D257" authorId="0" shapeId="0">
+    <comment ref="D292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B258" authorId="0" shapeId="0">
+    <comment ref="B293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C258" authorId="0" shapeId="0">
+    <comment ref="C293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D258" authorId="0" shapeId="0">
+    <comment ref="D293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B259" authorId="0" shapeId="0">
+    <comment ref="B294" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C259" authorId="0" shapeId="0">
+    <comment ref="C294" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D259" authorId="0" shapeId="0">
+    <comment ref="D294" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B260" authorId="0" shapeId="0">
+    <comment ref="B295" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C260" authorId="0" shapeId="0">
+    <comment ref="C295" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D260" authorId="0" shapeId="0">
+    <comment ref="D295" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B261" authorId="0" shapeId="0">
+    <comment ref="B296" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C261" authorId="0" shapeId="0">
+    <comment ref="C296" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D261" authorId="0" shapeId="0">
+    <comment ref="D296" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B262" authorId="0" shapeId="0">
+    <comment ref="B297" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C262" authorId="0" shapeId="0">
+    <comment ref="C297" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D262" authorId="0" shapeId="0">
+    <comment ref="D297" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B263" authorId="0" shapeId="0">
+    <comment ref="B298" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C263" authorId="0" shapeId="0">
+    <comment ref="C298" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D263" authorId="0" shapeId="0">
+    <comment ref="D298" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B264" authorId="0" shapeId="0">
+    <comment ref="B299" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C264" authorId="0" shapeId="0">
+    <comment ref="C299" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D264" authorId="0" shapeId="0">
+    <comment ref="D299" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
@@ -5738,7 +6263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L264"/>
+  <dimension ref="A1:L299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -16515,18 +17040,14 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>F4_VA_España_EDAD_0</t>
+          <t>F4_VA_EQUILIBRADO_España_0</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>-163</v>
-      </c>
-      <c r="C223" s="2" t="n">
-        <v>-219</v>
-      </c>
-      <c r="D223" s="2" t="n">
-        <v>-140</v>
-      </c>
+        <v>-121</v>
+      </c>
+      <c r="C223" s="2" t="n"/>
+      <c r="D223" s="2" t="n"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16559,25 +17080,21 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 0 años (comparador; intervalo: descuento y bienes públicos)</t>
+          <t>Valor actual del escenario principal con presupuesto equilibrado (se suma cada año el saldo medio por persona de 2024, 1,017 €), España, nacimiento</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>F4_VA_España_EDAD_20</t>
+          <t>F4_VA_EQUILIBRADO_España_30</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C224" s="2" t="n">
-        <v>-23</v>
-      </c>
-      <c r="D224" s="2" t="n">
-        <v>52</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C224" s="2" t="n"/>
+      <c r="D224" s="2" t="n"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16610,25 +17127,21 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 20 años (comparador; intervalo: descuento y bienes públicos)</t>
+          <t>Valor actual del escenario principal con presupuesto equilibrado (se suma cada año el saldo medio por persona de 2024, 1,017 €), España, llegada o edad 30</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>F4_VA_España_EDAD_30</t>
+          <t>F4_VA_EQUILIBRADO_Resto_UE_0</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="C225" s="2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="D225" s="2" t="n">
-        <v>71</v>
-      </c>
+        <v>-68</v>
+      </c>
+      <c r="C225" s="2" t="n"/>
+      <c r="D225" s="2" t="n"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16651,7 +17164,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -16661,25 +17174,21 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 30 años (comparador; intervalo: descuento y bienes públicos)</t>
+          <t>Valor actual del escenario principal con presupuesto equilibrado (se suma cada año el saldo medio por persona de 2024, 1,017 €), Resto UE, nacimiento</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>F4_VA_España_EDAD_40</t>
+          <t>F4_VA_EQUILIBRADO_Resto_UE_30</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>-41</v>
-      </c>
-      <c r="C226" s="2" t="n">
-        <v>-111</v>
-      </c>
-      <c r="D226" s="2" t="n">
-        <v>4</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C226" s="2" t="n"/>
+      <c r="D226" s="2" t="n"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16702,7 +17211,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -16712,18 +17221,18 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 40 años (comparador; intervalo: descuento y bienes públicos)</t>
+          <t>Valor actual del escenario principal con presupuesto equilibrado (se suma cada año el saldo medio por persona de 2024, 1,017 €), Resto UE, llegada o edad 30</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>F4_VA_HASTA64_Resto_UE_LLEGADA_20</t>
+          <t>F4_VA_EQUILIBRADO_Resto_del_mundo_0</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>17</v>
+        <v>-82</v>
       </c>
       <c r="C227" s="2" t="n"/>
       <c r="D227" s="2" t="n"/>
@@ -16749,7 +17258,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -16759,18 +17268,18 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 20</t>
+          <t>Valor actual del escenario principal con presupuesto equilibrado (se suma cada año el saldo medio por persona de 2024, 1,017 €), Resto del mundo, nacimiento</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>F4_VA_HASTA64_Resto_UE_LLEGADA_30</t>
+          <t>F4_VA_EQUILIBRADO_Resto_del_mundo_30</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>38</v>
+        <v>-3</v>
       </c>
       <c r="C228" s="2" t="n"/>
       <c r="D228" s="2" t="n"/>
@@ -16796,7 +17305,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -16806,21 +17315,25 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 30</t>
+          <t>Valor actual del escenario principal con presupuesto equilibrado (se suma cada año el saldo medio por persona de 2024, 1,017 €), Resto del mundo, llegada o edad 30</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>F4_VA_HASTA64_Resto_UE_LLEGADA_40</t>
+          <t>F4_VA_España_EDAD_0</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C229" s="2" t="n"/>
-      <c r="D229" s="2" t="n"/>
+        <v>-163</v>
+      </c>
+      <c r="C229" s="2" t="n">
+        <v>-219</v>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>-140</v>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16843,7 +17356,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>España</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -16853,21 +17366,25 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 40</t>
+          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 0 años (comparador; intervalo: descuento y bienes públicos)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>F4_VA_HASTA64_Resto_del_mundo_LLEGADA_20</t>
+          <t>F4_VA_España_EDAD_20</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="C230" s="2" t="n"/>
-      <c r="D230" s="2" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>-23</v>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>52</v>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16890,7 +17407,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>España</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -16900,21 +17417,25 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 20</t>
+          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 20 años (comparador; intervalo: descuento y bienes públicos)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>F4_VA_HASTA64_Resto_del_mundo_LLEGADA_30</t>
+          <t>F4_VA_España_EDAD_30</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C231" s="2" t="n"/>
-      <c r="D231" s="2" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>71</v>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16937,7 +17458,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>España</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -16947,21 +17468,25 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 30</t>
+          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 30 años (comparador; intervalo: descuento y bienes públicos)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>F4_VA_HASTA64_Resto_del_mundo_LLEGADA_40</t>
+          <t>F4_VA_España_EDAD_40</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C232" s="2" t="n"/>
-      <c r="D232" s="2" t="n"/>
+        <v>-41</v>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>-111</v>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>miles de € (VA)</t>
@@ -16984,7 +17509,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>España</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -16994,28 +17519,24 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 40</t>
+          <t>Valor actual de la contribución neta de la vida restante de una persona nacida en España de 40 años (comparador; intervalo: descuento y bienes públicos)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_0</t>
+          <t>F4_VA_HASTA64_Resto_UE_LLEGADA_20</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>-79</v>
-      </c>
-      <c r="C233" s="2" t="n">
-        <v>-287</v>
-      </c>
-      <c r="D233" s="2" t="n">
-        <v>-48</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C233" s="2" t="n"/>
+      <c r="D233" s="2" t="n"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -17040,33 +17561,29 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_20</t>
+          <t>F4_VA_HASTA64_Resto_UE_LLEGADA_30</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="C234" s="2" t="n">
-        <v>-99</v>
-      </c>
-      <c r="D234" s="2" t="n">
-        <v>117</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="C234" s="2" t="n"/>
+      <c r="D234" s="2" t="n"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -17091,33 +17608,29 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_30</t>
+          <t>F4_VA_HASTA64_Resto_UE_LLEGADA_40</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C235" s="2" t="n">
-        <v>-94</v>
-      </c>
-      <c r="D235" s="2" t="n">
-        <v>118</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C235" s="2" t="n"/>
+      <c r="D235" s="2" t="n"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -17142,33 +17655,29 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_40</t>
+          <t>F4_VA_HASTA64_Resto_del_mundo_LLEGADA_20</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C236" s="2" t="n">
-        <v>-98</v>
-      </c>
-      <c r="D236" s="2" t="n">
-        <v>83</v>
-      </c>
+        <v>-13</v>
+      </c>
+      <c r="C236" s="2" t="n"/>
+      <c r="D236" s="2" t="n"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -17188,38 +17697,34 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_0</t>
+          <t>F4_VA_HASTA64_Resto_del_mundo_LLEGADA_30</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>-93</v>
-      </c>
-      <c r="C237" s="2" t="n">
-        <v>-377</v>
-      </c>
-      <c r="D237" s="2" t="n">
-        <v>-50</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C237" s="2" t="n"/>
+      <c r="D237" s="2" t="n"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -17244,33 +17749,29 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_20</t>
+          <t>F4_VA_HASTA64_Resto_del_mundo_LLEGADA_40</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="C238" s="2" t="n">
-        <v>-198</v>
-      </c>
-      <c r="D238" s="2" t="n">
-        <v>97</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C238" s="2" t="n"/>
+      <c r="D238" s="2" t="n"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -17295,33 +17796,29 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Parte del valor actual hasta los 64 años («población joven hoy»), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_30</t>
+          <t>F4_VA_IMPUT_UE_Resto_UE_30</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="C239" s="2" t="n">
-        <v>-174</v>
-      </c>
-      <c r="D239" s="2" t="n">
-        <v>98</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C239" s="2" t="n"/>
+      <c r="D239" s="2" t="n"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -17341,38 +17838,34 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Principal con los tramos de edad suprimidos (&lt; 50 observaciones) rellenados con el perfil nativo sin escalar, Resto UE, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_40</t>
+          <t>F4_VA_IMPUT_UE_Resto_del_mundo_30</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="C240" s="2" t="n">
-        <v>-172</v>
-      </c>
-      <c r="D240" s="2" t="n">
-        <v>58</v>
-      </c>
+        <v>-12</v>
+      </c>
+      <c r="C240" s="2" t="n"/>
+      <c r="D240" s="2" t="n"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -17397,29 +17890,33 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Principal con los tramos de edad suprimidos (&lt; 50 observaciones) rellenados con el perfil nativo sin escalar, Resto del mundo, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_20</t>
+          <t>F4_VA_Resto_UE_LLEGADA_0</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="C241" s="2" t="n"/>
-      <c r="D241" s="2" t="n"/>
+        <v>-79</v>
+      </c>
+      <c r="C241" s="2" t="n">
+        <v>-287</v>
+      </c>
+      <c r="D241" s="2" t="n">
+        <v>-48</v>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -17444,29 +17941,33 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_30</t>
+          <t>F4_VA_Resto_UE_LLEGADA_20</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>-28</v>
-      </c>
-      <c r="C242" s="2" t="n"/>
-      <c r="D242" s="2" t="n"/>
+        <v>-9</v>
+      </c>
+      <c r="C242" s="2" t="n">
+        <v>-99</v>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>117</v>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -17491,29 +17992,33 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_40</t>
+          <t>F4_VA_Resto_UE_LLEGADA_30</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="C243" s="2" t="n"/>
-      <c r="D243" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>118</v>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -17538,29 +18043,33 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_20</t>
+          <t>F4_VA_Resto_UE_LLEGADA_40</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>-117</v>
-      </c>
-      <c r="C244" s="2" t="n"/>
-      <c r="D244" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>-98</v>
+      </c>
+      <c r="D244" s="2" t="n">
+        <v>83</v>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -17580,34 +18089,38 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_30</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_0</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>-101</v>
-      </c>
-      <c r="C245" s="2" t="n"/>
-      <c r="D245" s="2" t="n"/>
+        <v>-93</v>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>-377</v>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>-50</v>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -17632,29 +18145,33 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_40</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_20</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>-116</v>
-      </c>
-      <c r="C246" s="2" t="n"/>
-      <c r="D246" s="2" t="n"/>
+        <v>-34</v>
+      </c>
+      <c r="C246" s="2" t="n">
+        <v>-198</v>
+      </c>
+      <c r="D246" s="2" t="n">
+        <v>97</v>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -17679,39 +18196,43 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_30</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="C247" s="2" t="n"/>
-      <c r="D247" s="2" t="n"/>
+        <v>-13</v>
+      </c>
+      <c r="C247" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>98</v>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -17721,44 +18242,48 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_40</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C248" s="2" t="n"/>
-      <c r="D248" s="2" t="n"/>
+        <v>-16</v>
+      </c>
+      <c r="C248" s="2" t="n">
+        <v>-172</v>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>58</v>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -17768,44 +18293,44 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
+          <t>F4_VA_SIN_MIN15_Resto_UE_30</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="C249" s="2" t="n"/>
       <c r="D249" s="2" t="n"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -17815,44 +18340,44 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>Principal sin el mínimo de 15 años cotizados para la pensión contributiva, Resto UE, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_15_34</t>
+          <t>F4_VA_SIN_MIN15_Resto_del_mundo_30</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>0.9</v>
+        <v>-19</v>
       </c>
       <c r="C250" s="2" t="n"/>
       <c r="D250" s="2" t="n"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -17862,44 +18387,44 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>Principal sin el mínimo de 15 años cotizados para la pensión contributiva, Resto del mundo, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_35_54</t>
+          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_20</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>0.89</v>
+        <v>-29</v>
       </c>
       <c r="C251" s="2" t="n"/>
       <c r="D251" s="2" t="n"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -17909,44 +18434,44 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_55_74</t>
+          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_30</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>0.85</v>
+        <v>-28</v>
       </c>
       <c r="C252" s="2" t="n"/>
       <c r="D252" s="2" t="n"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -17956,44 +18481,44 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_15_34</t>
+          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_40</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>0.6</v>
+        <v>-49</v>
       </c>
       <c r="C253" s="2" t="n"/>
       <c r="D253" s="2" t="n"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -18003,44 +18528,44 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_35_54</t>
+          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_20</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>0.82</v>
+        <v>-117</v>
       </c>
       <c r="C254" s="2" t="n"/>
       <c r="D254" s="2" t="n"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -18050,44 +18575,44 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_55_74</t>
+          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_30</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>2.58</v>
+        <v>-101</v>
       </c>
       <c r="C255" s="2" t="n"/>
       <c r="D255" s="2" t="n"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -18097,44 +18622,44 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_15_34</t>
+          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_40</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>0.9</v>
+        <v>-116</v>
       </c>
       <c r="C256" s="2" t="n"/>
       <c r="D256" s="2" t="n"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -18144,44 +18669,44 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_35_54</t>
+          <t>F4_VA_SIN_SUELO_Resto_UE_30</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="C257" s="2" t="n"/>
       <c r="D257" s="2" t="n"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -18191,44 +18716,44 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>Principal sin el suelo de pensión no contributiva, Resto UE, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_55_74</t>
+          <t>F4_VA_SIN_SUELO_Resto_del_mundo_30</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="C258" s="2" t="n"/>
       <c r="D258" s="2" t="n"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -18238,297 +18763,2010 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>Principal sin el suelo de pensión no contributiva, Resto del mundo, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>F6_POB_CUOTA_FUERA_ECV</t>
+          <t>F5_P1_E1_beta</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>18.5</v>
+        <v>-0.021</v>
       </c>
       <c r="C259" s="2" t="n"/>
       <c r="D259" s="2" t="n"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>% de la población</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>ECV (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
+          <t>P1-E1: efecto sobre tasa_actividad (MC2E, especificación principal)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_España</t>
+          <t>F5_P1_E1_p</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>6252</v>
+        <v>0.995</v>
       </c>
       <c r="C260" s="2" t="n"/>
       <c r="D260" s="2" t="n"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
+          <t>P1-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
+          <t>F5_P1_E2_beta</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>2813</v>
+        <v>-0.636</v>
       </c>
       <c r="C261" s="2" t="n"/>
       <c r="D261" s="2" t="n"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+          <t>P1-E2: efecto sobre log_ocupados (MC2E, especificación principal)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+          <t>F5_P1_E2_p</t>
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>1927</v>
+        <v>0.158</v>
       </c>
       <c r="C262" s="2" t="n"/>
       <c r="D262" s="2" t="n"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+          <t>P1-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+          <t>F5_P1_E3a_beta</t>
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>2.5</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="C263" s="2" t="n"/>
       <c r="D263" s="2" t="n"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>% de las prestaciones monetarias</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+          <t>P1-E3a: efecto sobre tasa_empleo_educ_baja (MC2E, especificación principal)</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>F6_TRABAJO_CUOTA_FUERA</t>
+          <t>F5_P1_E3a_p</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
-        <v>15.5</v>
+        <v>0.008</v>
       </c>
       <c r="C264" s="2" t="n"/>
       <c r="D264" s="2" t="n"/>
       <c r="E264" t="inlineStr">
         <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>P1-E3a: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>F5_P1_E3b_beta</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="C265" s="2" t="n"/>
+      <c r="D265" s="2" t="n"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>P1-E3b: efecto sobre tasa_empleo_educ_media (MC2E, especificación principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>F5_P1_E3b_p</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="C266" s="2" t="n"/>
+      <c r="D266" s="2" t="n"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>P1-E3b: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>F5_P1_E3c_beta</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C267" s="2" t="n"/>
+      <c r="D267" s="2" t="n"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>P1-E3c: efecto sobre tasa_empleo_educ_alta (MC2E, especificación principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>F5_P1_E3c_p</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="C268" s="2" t="n"/>
+      <c r="D268" s="2" t="n"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>P1-E3c: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>F5_P1_E4_beta</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Δ log salario por punto de cuota</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>2010-2022</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>españoles (nacionalidad)</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>EES y EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>P1-E4 (Borjas): asociación entre la cuota de nacidos fuera en la celda educación × edad y el salario por hora de los españoles (primeras diferencias; IC orientativo por errores agrupados en 15 celdas; p wild bootstrap = 0.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>F5_P1_F_EFECTIVO</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="C270" s="2" t="n"/>
+      <c r="D270" s="2" t="n"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>padrón, ECP (INE)</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>F efectivo de primera etapa agrupado por provincia, especificación principal de P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>F5_P1_F_SHOCK</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C271" s="2" t="n"/>
+      <c r="D271" s="2" t="n"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>padrón, ECP (INE)</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>F de primera etapa al nivel del shock (BHJ), especificación principal de P1 (umbral pre-registrado: 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>F5_P1_H1_beta</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>-0.228</v>
+      </c>
+      <c r="C272" s="2" t="n"/>
+      <c r="D272" s="2" t="n"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>P1-H1: efecto sobre tasa_empleo (MC2E, especificación principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>F5_P1_H1_p</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="C273" s="2" t="n"/>
+      <c r="D273" s="2" t="n"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>P1-H1: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>F5_P1_H2_beta</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="C274" s="2" t="n"/>
+      <c r="D274" s="2" t="n"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>P1-H2: efecto sobre tasa_paro (MC2E, especificación principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>F5_P1_H2_p</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="C275" s="2" t="n"/>
+      <c r="D275" s="2" t="n"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>P1-H2: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>F5_P2_E1_beta</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C276" s="2" t="n"/>
+      <c r="D276" s="2" t="n"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>P2-E1: efecto sobre cuota_nomanual (MC2E, especificación principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>F5_P2_E1_p</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="C277" s="2" t="n"/>
+      <c r="D277" s="2" t="n"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>P2-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>F5_P2_E2_beta</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="C278" s="2" t="n"/>
+      <c r="D278" s="2" t="n"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>P2-E2: efecto sobre cuota_alta_cualif (MC2E, especificación principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>F5_P2_E2_p</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="C279" s="2" t="n"/>
+      <c r="D279" s="2" t="n"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>P2-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>F5_P3_EDUC_beta</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>-0.169</v>
+      </c>
+      <c r="C280" s="2" t="n">
+        <v>-0.752</v>
+      </c>
+      <c r="D280" s="2" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>alumnos por profesor por punto porcentual</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>2016-2022</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>17 CCAA</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>EDUCAbase, ECP y padrón</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>P3 (educación): asociación entre el aumento de la población nacida fuera de 5-19 años y la ratio de alumnos por profesor en centros públicos (MC2E por comunidad; F efectivo = 39.5; p wild bootstrap de la forma reducida = 0.58; IC orientativo por errores agrupados en 17 comunidades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>F5_P5_beta</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>-0.325</v>
+      </c>
+      <c r="C281" s="2" t="n"/>
+      <c r="D281" s="2" t="n"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>NUTS2 UE-27</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>nativos</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Eurostat (censo 2021, migr_imm3ctb, EU-LFS)</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>P5: asociación entre la llegada de población nacida fuera y la tasa de empleo de los nativos, NUTS2 de la UE-27, 2021-2024 (MC2E leave-one-country-out; p wild bootstrap por país = 0.38; IC: AKM0 con shocks comunes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C282" s="2" t="n"/>
+      <c r="D282" s="2" t="n"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C283" s="2" t="n"/>
+      <c r="D283" s="2" t="n"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C284" s="2" t="n"/>
+      <c r="D284" s="2" t="n"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_FAR_15_34</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C285" s="2" t="n"/>
+      <c r="D285" s="2" t="n"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_FAR_35_54</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C286" s="2" t="n"/>
+      <c r="D286" s="2" t="n"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_FAR_55_74</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C287" s="2" t="n"/>
+      <c r="D287" s="2" t="n"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_15_34</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C288" s="2" t="n"/>
+      <c r="D288" s="2" t="n"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_35_54</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C289" s="2" t="n"/>
+      <c r="D289" s="2" t="n"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_55_74</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C290" s="2" t="n"/>
+      <c r="D290" s="2" t="n"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_15_34</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C291" s="2" t="n"/>
+      <c r="D291" s="2" t="n"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_35_54</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C292" s="2" t="n"/>
+      <c r="D292" s="2" t="n"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_55_74</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C293" s="2" t="n"/>
+      <c r="D293" s="2" t="n"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>F6_POB_CUOTA_FUERA_ECV</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C294" s="2" t="n"/>
+      <c r="D294" s="2" t="n"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>% de la población</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>ECV (INE)</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_España</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>6252</v>
+      </c>
+      <c r="C295" s="2" t="n"/>
+      <c r="D295" s="2" t="n"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="n">
+        <v>2813</v>
+      </c>
+      <c r="C296" s="2" t="n"/>
+      <c r="D296" s="2" t="n"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Resto UE</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C297" s="2" t="n"/>
+      <c r="D297" s="2" t="n"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Resto del mundo</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C298" s="2" t="n"/>
+      <c r="D298" s="2" t="n"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>% de las prestaciones monetarias</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>F6_TRABAJO_CUOTA_FUERA</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C299" s="2" t="n"/>
+      <c r="D299" s="2" t="n"/>
+      <c r="E299" t="inlineStr">
+        <is>
           <t>% del total</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F299" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H299" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
         <is>
           <t>nacidos fuera</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="K299" t="inlineStr">
         <is>
           <t>ECV (INE) y Eurostat</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="L299" t="inlineStr">
         <is>
           <t>Cuota de los nacidos fuera en IRPF del trabajo y cotizaciones sociales (calibradas a las cuentas de las AAPP)</t>
         </is>

--- a/output/f7/tablas_m1.xlsx
+++ b/output/f7/tablas_m1.xlsx
@@ -4275,885 +4275,1275 @@
     </comment>
     <comment ref="B241" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C241" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D241" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B242" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C242" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D242" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B243" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C243" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D243" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B244" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C244" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D244" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B245" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C245" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D245" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B246" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="C246" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="D246" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
+      </text>
+    </comment>
+    <comment ref="B247" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C241" authorId="0" shapeId="0">
+    <comment ref="C247" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D241" authorId="0" shapeId="0">
+    <comment ref="D247" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B242" authorId="0" shapeId="0">
+    <comment ref="B248" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C242" authorId="0" shapeId="0">
+    <comment ref="C248" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D242" authorId="0" shapeId="0">
+    <comment ref="D248" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B243" authorId="0" shapeId="0">
+    <comment ref="B249" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C243" authorId="0" shapeId="0">
+    <comment ref="C249" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D243" authorId="0" shapeId="0">
+    <comment ref="D249" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B244" authorId="0" shapeId="0">
+    <comment ref="B250" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C244" authorId="0" shapeId="0">
+    <comment ref="C250" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D244" authorId="0" shapeId="0">
+    <comment ref="D250" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B245" authorId="0" shapeId="0">
+    <comment ref="B251" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C245" authorId="0" shapeId="0">
+    <comment ref="C251" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D245" authorId="0" shapeId="0">
+    <comment ref="D251" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B246" authorId="0" shapeId="0">
+    <comment ref="B252" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C246" authorId="0" shapeId="0">
+    <comment ref="C252" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D246" authorId="0" shapeId="0">
+    <comment ref="D252" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B247" authorId="0" shapeId="0">
+    <comment ref="B253" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C247" authorId="0" shapeId="0">
+    <comment ref="C253" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D247" authorId="0" shapeId="0">
+    <comment ref="D253" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B248" authorId="0" shapeId="0">
+    <comment ref="B254" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C248" authorId="0" shapeId="0">
+    <comment ref="C254" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D248" authorId="0" shapeId="0">
+    <comment ref="D254" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B249" authorId="0" shapeId="0">
+    <comment ref="B255" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C249" authorId="0" shapeId="0">
+    <comment ref="C255" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D249" authorId="0" shapeId="0">
+    <comment ref="D255" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B250" authorId="0" shapeId="0">
+    <comment ref="B256" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C250" authorId="0" shapeId="0">
+    <comment ref="C256" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D250" authorId="0" shapeId="0">
+    <comment ref="D256" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B251" authorId="0" shapeId="0">
+    <comment ref="B257" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C251" authorId="0" shapeId="0">
+    <comment ref="C257" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D251" authorId="0" shapeId="0">
+    <comment ref="D257" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B252" authorId="0" shapeId="0">
+    <comment ref="B258" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C252" authorId="0" shapeId="0">
+    <comment ref="C258" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D252" authorId="0" shapeId="0">
+    <comment ref="D258" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B253" authorId="0" shapeId="0">
+    <comment ref="B259" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C253" authorId="0" shapeId="0">
+    <comment ref="C259" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D253" authorId="0" shapeId="0">
+    <comment ref="D259" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B254" authorId="0" shapeId="0">
+    <comment ref="B260" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C254" authorId="0" shapeId="0">
+    <comment ref="C260" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D254" authorId="0" shapeId="0">
+    <comment ref="D260" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B255" authorId="0" shapeId="0">
+    <comment ref="B261" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C255" authorId="0" shapeId="0">
+    <comment ref="C261" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D255" authorId="0" shapeId="0">
+    <comment ref="D261" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B256" authorId="0" shapeId="0">
+    <comment ref="B262" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C256" authorId="0" shapeId="0">
+    <comment ref="C262" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D256" authorId="0" shapeId="0">
+    <comment ref="D262" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B257" authorId="0" shapeId="0">
+    <comment ref="B263" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C257" authorId="0" shapeId="0">
+    <comment ref="C263" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D257" authorId="0" shapeId="0">
+    <comment ref="D263" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B258" authorId="0" shapeId="0">
+    <comment ref="B264" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="C258" authorId="0" shapeId="0">
+    <comment ref="C264" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="D258" authorId="0" shapeId="0">
+    <comment ref="D264" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Perfiles M1 (src/m1/f4_ciclo_vital.py)</t>
       </text>
     </comment>
-    <comment ref="B259" authorId="0" shapeId="0">
+    <comment ref="B265" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C259" authorId="0" shapeId="0">
+    <comment ref="C265" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D259" authorId="0" shapeId="0">
+    <comment ref="D265" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B260" authorId="0" shapeId="0">
+    <comment ref="B266" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C260" authorId="0" shapeId="0">
+    <comment ref="C266" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D260" authorId="0" shapeId="0">
+    <comment ref="D266" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B261" authorId="0" shapeId="0">
+    <comment ref="B267" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C261" authorId="0" shapeId="0">
+    <comment ref="C267" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D261" authorId="0" shapeId="0">
+    <comment ref="D267" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B262" authorId="0" shapeId="0">
+    <comment ref="B268" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C262" authorId="0" shapeId="0">
+    <comment ref="C268" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D262" authorId="0" shapeId="0">
+    <comment ref="D268" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B263" authorId="0" shapeId="0">
+    <comment ref="B269" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C263" authorId="0" shapeId="0">
+    <comment ref="C269" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D263" authorId="0" shapeId="0">
+    <comment ref="D269" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B264" authorId="0" shapeId="0">
+    <comment ref="B270" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C264" authorId="0" shapeId="0">
+    <comment ref="C270" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D264" authorId="0" shapeId="0">
+    <comment ref="D270" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B265" authorId="0" shapeId="0">
+    <comment ref="B271" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C265" authorId="0" shapeId="0">
+    <comment ref="C271" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D265" authorId="0" shapeId="0">
+    <comment ref="D271" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B266" authorId="0" shapeId="0">
+    <comment ref="B272" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C266" authorId="0" shapeId="0">
+    <comment ref="C272" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D266" authorId="0" shapeId="0">
+    <comment ref="D272" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B267" authorId="0" shapeId="0">
+    <comment ref="B273" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C267" authorId="0" shapeId="0">
+    <comment ref="C273" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D267" authorId="0" shapeId="0">
+    <comment ref="D273" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B268" authorId="0" shapeId="0">
+    <comment ref="B274" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C268" authorId="0" shapeId="0">
+    <comment ref="C274" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D268" authorId="0" shapeId="0">
+    <comment ref="D274" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B269" authorId="0" shapeId="0">
+    <comment ref="B275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B277" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C277" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D277" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B278" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C278" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D278" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B279" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="C269" authorId="0" shapeId="0">
+    <comment ref="C279" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="D269" authorId="0" shapeId="0">
+    <comment ref="D279" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="B270" authorId="0" shapeId="0">
+    <comment ref="B280" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C280" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D280" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B281" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C281" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D281" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C270" authorId="0" shapeId="0">
+    <comment ref="C282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D270" authorId="0" shapeId="0">
+    <comment ref="D282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B271" authorId="0" shapeId="0">
+    <comment ref="B283" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C283" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D283" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C271" authorId="0" shapeId="0">
+    <comment ref="C284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D271" authorId="0" shapeId="0">
+    <comment ref="D284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B272" authorId="0" shapeId="0">
+    <comment ref="B285" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C285" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D285" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C272" authorId="0" shapeId="0">
+    <comment ref="C286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D272" authorId="0" shapeId="0">
+    <comment ref="D286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B273" authorId="0" shapeId="0">
+    <comment ref="B287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C273" authorId="0" shapeId="0">
+    <comment ref="C287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D273" authorId="0" shapeId="0">
+    <comment ref="D287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B274" authorId="0" shapeId="0">
+    <comment ref="B288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C274" authorId="0" shapeId="0">
+    <comment ref="C288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D274" authorId="0" shapeId="0">
+    <comment ref="D288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B275" authorId="0" shapeId="0">
+    <comment ref="B289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C275" authorId="0" shapeId="0">
+    <comment ref="C289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D275" authorId="0" shapeId="0">
+    <comment ref="D289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B276" authorId="0" shapeId="0">
+    <comment ref="B290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C276" authorId="0" shapeId="0">
+    <comment ref="C290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D276" authorId="0" shapeId="0">
+    <comment ref="D290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B277" authorId="0" shapeId="0">
+    <comment ref="B291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C277" authorId="0" shapeId="0">
+    <comment ref="C291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D277" authorId="0" shapeId="0">
+    <comment ref="D291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B278" authorId="0" shapeId="0">
+    <comment ref="B292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C278" authorId="0" shapeId="0">
+    <comment ref="C292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D278" authorId="0" shapeId="0">
+    <comment ref="D292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B279" authorId="0" shapeId="0">
+    <comment ref="B293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C279" authorId="0" shapeId="0">
+    <comment ref="C293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D279" authorId="0" shapeId="0">
+    <comment ref="D293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B280" authorId="0" shapeId="0">
+    <comment ref="B294" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C294" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D294" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B295" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C295" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D295" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B296" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C296" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D296" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B297" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C297" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D297" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B298" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C298" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D298" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B299" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C299" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D299" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B300" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C300" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D300" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B301" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C301" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D301" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B302" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="C280" authorId="0" shapeId="0">
+    <comment ref="C302" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="D280" authorId="0" shapeId="0">
+    <comment ref="D302" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="B281" authorId="0" shapeId="0">
+    <comment ref="B303" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="C303" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="D303" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="B304" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="C304" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="D304" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="B305" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="C305" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="D305" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="B306" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="C306" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="D306" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
+      </text>
+    </comment>
+    <comment ref="B307" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C281" authorId="0" shapeId="0">
+    <comment ref="C307" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D281" authorId="0" shapeId="0">
+    <comment ref="D307" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B282" authorId="0" shapeId="0">
+    <comment ref="B308" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C282" authorId="0" shapeId="0">
+    <comment ref="C308" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D282" authorId="0" shapeId="0">
+    <comment ref="D308" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B283" authorId="0" shapeId="0">
+    <comment ref="B309" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C283" authorId="0" shapeId="0">
+    <comment ref="C309" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D283" authorId="0" shapeId="0">
+    <comment ref="D309" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B284" authorId="0" shapeId="0">
+    <comment ref="B310" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C284" authorId="0" shapeId="0">
+    <comment ref="C310" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D284" authorId="0" shapeId="0">
+    <comment ref="D310" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B285" authorId="0" shapeId="0">
+    <comment ref="B311" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C285" authorId="0" shapeId="0">
+    <comment ref="C311" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D285" authorId="0" shapeId="0">
+    <comment ref="D311" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B286" authorId="0" shapeId="0">
+    <comment ref="B312" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C286" authorId="0" shapeId="0">
+    <comment ref="C312" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D286" authorId="0" shapeId="0">
+    <comment ref="D312" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B287" authorId="0" shapeId="0">
+    <comment ref="B313" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C287" authorId="0" shapeId="0">
+    <comment ref="C313" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D287" authorId="0" shapeId="0">
+    <comment ref="D313" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B288" authorId="0" shapeId="0">
+    <comment ref="B314" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C288" authorId="0" shapeId="0">
+    <comment ref="C314" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D288" authorId="0" shapeId="0">
+    <comment ref="D314" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B289" authorId="0" shapeId="0">
+    <comment ref="B315" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C289" authorId="0" shapeId="0">
+    <comment ref="C315" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D289" authorId="0" shapeId="0">
+    <comment ref="D315" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B290" authorId="0" shapeId="0">
+    <comment ref="B316" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C290" authorId="0" shapeId="0">
+    <comment ref="C316" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D290" authorId="0" shapeId="0">
+    <comment ref="D316" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B291" authorId="0" shapeId="0">
+    <comment ref="B317" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C291" authorId="0" shapeId="0">
+    <comment ref="C317" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D291" authorId="0" shapeId="0">
+    <comment ref="D317" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B292" authorId="0" shapeId="0">
+    <comment ref="B318" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C292" authorId="0" shapeId="0">
+    <comment ref="C318" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D292" authorId="0" shapeId="0">
+    <comment ref="D318" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B293" authorId="0" shapeId="0">
+    <comment ref="B319" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C293" authorId="0" shapeId="0">
+    <comment ref="C319" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D293" authorId="0" shapeId="0">
+    <comment ref="D319" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B294" authorId="0" shapeId="0">
+    <comment ref="B320" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C294" authorId="0" shapeId="0">
+    <comment ref="C320" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D294" authorId="0" shapeId="0">
+    <comment ref="D320" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B295" authorId="0" shapeId="0">
+    <comment ref="B321" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C295" authorId="0" shapeId="0">
+    <comment ref="C321" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D295" authorId="0" shapeId="0">
+    <comment ref="D321" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B296" authorId="0" shapeId="0">
+    <comment ref="B322" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C296" authorId="0" shapeId="0">
+    <comment ref="C322" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D296" authorId="0" shapeId="0">
+    <comment ref="D322" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B297" authorId="0" shapeId="0">
+    <comment ref="B323" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C297" authorId="0" shapeId="0">
+    <comment ref="C323" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D297" authorId="0" shapeId="0">
+    <comment ref="D323" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B298" authorId="0" shapeId="0">
+    <comment ref="B324" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C298" authorId="0" shapeId="0">
+    <comment ref="C324" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D298" authorId="0" shapeId="0">
+    <comment ref="D324" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B299" authorId="0" shapeId="0">
+    <comment ref="B325" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C299" authorId="0" shapeId="0">
+    <comment ref="C325" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D299" authorId="0" shapeId="0">
+    <comment ref="D325" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
@@ -6263,7 +6653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L299"/>
+  <dimension ref="A1:L325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17902,21 +18292,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_0</t>
+          <t>F4_VA_MITAD_SALIDA_Resto_UE_LLEGADA_20</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
-        <v>-79</v>
-      </c>
-      <c r="C241" s="2" t="n">
-        <v>-287</v>
-      </c>
-      <c r="D241" s="2" t="n">
-        <v>-48</v>
-      </c>
+        <v>-14</v>
+      </c>
+      <c r="C241" s="2" t="n"/>
+      <c r="D241" s="2" t="n"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -17941,33 +18327,29 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Como el principal pero con la mitad del riesgo de salida (por si las bajas por caducidad no son salidas reales), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_20</t>
+          <t>F4_VA_MITAD_SALIDA_Resto_UE_LLEGADA_30</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="C242" s="2" t="n">
-        <v>-99</v>
-      </c>
-      <c r="D242" s="2" t="n">
-        <v>117</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C242" s="2" t="n"/>
+      <c r="D242" s="2" t="n"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -17992,33 +18374,29 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Como el principal pero con la mitad del riesgo de salida (por si las bajas por caducidad no son salidas reales), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_30</t>
+          <t>F4_VA_MITAD_SALIDA_Resto_UE_LLEGADA_40</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C243" s="2" t="n">
-        <v>-94</v>
-      </c>
-      <c r="D243" s="2" t="n">
-        <v>118</v>
-      </c>
+        <v>-5</v>
+      </c>
+      <c r="C243" s="2" t="n"/>
+      <c r="D243" s="2" t="n"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -18043,33 +18421,29 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Como el principal pero con la mitad del riesgo de salida (por si las bajas por caducidad no son salidas reales), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_UE_LLEGADA_40</t>
+          <t>F4_VA_MITAD_SALIDA_Resto_del_mundo_LLEGADA_20</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C244" s="2" t="n">
-        <v>-98</v>
-      </c>
-      <c r="D244" s="2" t="n">
-        <v>83</v>
-      </c>
+        <v>-60</v>
+      </c>
+      <c r="C244" s="2" t="n"/>
+      <c r="D244" s="2" t="n"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -18089,38 +18463,34 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Como el principal pero con la mitad del riesgo de salida (por si las bajas por caducidad no son salidas reales), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_0</t>
+          <t>F4_VA_MITAD_SALIDA_Resto_del_mundo_LLEGADA_30</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>-93</v>
-      </c>
-      <c r="C245" s="2" t="n">
-        <v>-377</v>
-      </c>
-      <c r="D245" s="2" t="n">
-        <v>-50</v>
-      </c>
+        <v>-39</v>
+      </c>
+      <c r="C245" s="2" t="n"/>
+      <c r="D245" s="2" t="n"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -18145,33 +18515,29 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Como el principal pero con la mitad del riesgo de salida (por si las bajas por caducidad no son salidas reales), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_20</t>
+          <t>F4_VA_MITAD_SALIDA_Resto_del_mundo_LLEGADA_40</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="C246" s="2" t="n">
-        <v>-198</v>
-      </c>
-      <c r="D246" s="2" t="n">
-        <v>97</v>
-      </c>
+        <v>-47</v>
+      </c>
+      <c r="C246" s="2" t="n"/>
+      <c r="D246" s="2" t="n"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>miles de € (VA en 2024)</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -18196,29 +18562,29 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Como el principal pero con la mitad del riesgo de salida (por si las bajas por caducidad no son salidas reales), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_30</t>
+          <t>F4_VA_Resto_UE_LLEGADA_0</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>-13</v>
+        <v>-79</v>
       </c>
       <c r="C247" s="2" t="n">
-        <v>-174</v>
+        <v>-287</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>98</v>
+        <v>-48</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -18242,7 +18608,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -18252,24 +18618,24 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>F4_VA_Resto_del_mundo_LLEGADA_40</t>
+          <t>F4_VA_Resto_UE_LLEGADA_20</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="C248" s="2" t="n">
-        <v>-172</v>
+        <v>-99</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -18293,7 +18659,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -18303,24 +18669,28 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_MIN15_Resto_UE_30</t>
+          <t>F4_VA_Resto_UE_LLEGADA_30</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C249" s="2" t="n"/>
-      <c r="D249" s="2" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>118</v>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -18345,29 +18715,33 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Principal sin el mínimo de 15 años cotizados para la pensión contributiva, Resto UE, llegada a los 30</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_MIN15_Resto_del_mundo_30</t>
+          <t>F4_VA_Resto_UE_LLEGADA_40</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>-19</v>
-      </c>
-      <c r="C250" s="2" t="n"/>
-      <c r="D250" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="C250" s="2" t="n">
+        <v>-98</v>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>83</v>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -18387,34 +18761,38 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Principal sin el mínimo de 15 años cotizados para la pensión contributiva, Resto del mundo, llegada a los 30</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto UE que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_20</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_0</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="C251" s="2" t="n"/>
-      <c r="D251" s="2" t="n"/>
+        <v>-93</v>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>-377</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>-50</v>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -18434,34 +18812,38 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 0 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_30</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_20</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>-28</v>
-      </c>
-      <c r="C252" s="2" t="n"/>
-      <c r="D252" s="2" t="n"/>
+        <v>-34</v>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>-198</v>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>97</v>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -18481,34 +18863,38 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 20 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_40</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_30</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="C253" s="2" t="n"/>
-      <c r="D253" s="2" t="n"/>
+        <v>-13</v>
+      </c>
+      <c r="C253" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>98</v>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -18528,34 +18914,38 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 30 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_20</t>
+          <t>F4_VA_Resto_del_mundo_LLEGADA_40</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>-117</v>
-      </c>
-      <c r="C254" s="2" t="n"/>
-      <c r="D254" s="2" t="n"/>
+        <v>-16</v>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>-172</v>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>58</v>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>miles de € (VA)</t>
+          <t>miles de € (VA en 2024)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -18580,23 +18970,23 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Perfiles M1</t>
+          <t>Perfiles M1 (ECV, EPF, ENSE, cuentas AAPP) y Eurostat</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
+          <t>Valor actual de la contribución neta de por vida de una persona nacida en Resto del mundo que llega a los 40 años (principal: descuento 3 %, sin convergencia adicional, salida con riesgo decreciente calibrado a 6.3 % anual, pensiones devengadas exportables, bienes públicos a coste medio; intervalo: las 72 combinaciones de supuestos)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_30</t>
+          <t>F4_VA_SIN_MIN15_Resto_UE_30</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>-101</v>
+        <v>2</v>
       </c>
       <c r="C255" s="2" t="n"/>
       <c r="D255" s="2" t="n"/>
@@ -18622,7 +19012,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -18632,18 +19022,18 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
+          <t>Principal sin el mínimo de 15 años cotizados para la pensión contributiva, Resto UE, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_40</t>
+          <t>F4_VA_SIN_MIN15_Resto_del_mundo_30</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>-116</v>
+        <v>-19</v>
       </c>
       <c r="C256" s="2" t="n"/>
       <c r="D256" s="2" t="n"/>
@@ -18679,18 +19069,18 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
+          <t>Principal sin el mínimo de 15 años cotizados para la pensión contributiva, Resto del mundo, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SUELO_Resto_UE_30</t>
+          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_20</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>10</v>
+        <v>-29</v>
       </c>
       <c r="C257" s="2" t="n"/>
       <c r="D257" s="2" t="n"/>
@@ -18726,18 +19116,18 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>Principal sin el suelo de pensión no contributiva, Resto UE, llegada a los 30</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>F4_VA_SIN_SUELO_Resto_del_mundo_30</t>
+          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_30</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>-13</v>
+        <v>-28</v>
       </c>
       <c r="C258" s="2" t="n"/>
       <c r="D258" s="2" t="n"/>
@@ -18763,7 +19153,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -18773,315 +19163,300 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>Principal sin el suelo de pensión no contributiva, Resto del mundo, llegada a los 30</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>F5_P1_E1_beta</t>
+          <t>F4_VA_SIN_SALIDA_Resto_UE_LLEGADA_40</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>-0.021</v>
+        <v>-49</v>
       </c>
       <c r="C259" s="2" t="n"/>
       <c r="D259" s="2" t="n"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>P1-E1: efecto sobre tasa_actividad (MC2E, especificación principal)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>F5_P1_E1_p</t>
+          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_20</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>0.995</v>
+        <v>-117</v>
       </c>
       <c r="C260" s="2" t="n"/>
       <c r="D260" s="2" t="n"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>P1-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 20</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>F5_P1_E2_beta</t>
+          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_30</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
-        <v>-0.636</v>
+        <v>-101</v>
       </c>
       <c r="C261" s="2" t="n"/>
       <c r="D261" s="2" t="n"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>P1-E2: efecto sobre log_ocupados (MC2E, especificación principal)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>F5_P1_E2_p</t>
+          <t>F4_VA_SIN_SALIDA_Resto_del_mundo_LLEGADA_40</t>
         </is>
       </c>
       <c r="B262" s="2" t="n">
-        <v>0.158</v>
+        <v>-116</v>
       </c>
       <c r="C262" s="2" t="n"/>
       <c r="D262" s="2" t="n"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>P1-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>Como el principal pero sin salidas (toda la vida en España), llegada a los 40</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_beta</t>
+          <t>F4_VA_SIN_SUELO_Resto_UE_30</t>
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>-0.6889999999999999</v>
+        <v>10</v>
       </c>
       <c r="C263" s="2" t="n"/>
       <c r="D263" s="2" t="n"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>Resto UE</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>P1-E3a: efecto sobre tasa_empleo_educ_baja (MC2E, especificación principal)</t>
+          <t>Principal sin el suelo de pensión no contributiva, Resto UE, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_p</t>
+          <t>F4_VA_SIN_SUELO_Resto_del_mundo_30</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
-        <v>0.008</v>
+        <v>-13</v>
       </c>
       <c r="C264" s="2" t="n"/>
       <c r="D264" s="2" t="n"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>miles de € (VA)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>Resto del mundo</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>Perfiles M1</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>P1-E3a: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>Principal sin el suelo de pensión no contributiva, Resto del mundo, llegada a los 30</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_beta</t>
+          <t>F5_P1_E1_beta</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>-0.029</v>
+        <v>-0.021</v>
       </c>
       <c r="C265" s="2" t="n"/>
       <c r="D265" s="2" t="n"/>
@@ -19122,14 +19497,14 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>P1-E3b: efecto sobre tasa_empleo_educ_media (MC2E, especificación principal)</t>
+          <t>P1-E1: asociación con tasa_actividad (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_p</t>
+          <t>F5_P1_E1_p</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
@@ -19169,18 +19544,18 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>P1-E3b: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_beta</t>
+          <t>F5_P1_E2_beta</t>
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.636</v>
       </c>
       <c r="C267" s="2" t="n"/>
       <c r="D267" s="2" t="n"/>
@@ -19221,18 +19596,18 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>P1-E3c: efecto sobre tasa_empleo_educ_alta (MC2E, especificación principal)</t>
+          <t>P1-E2: asociación con log_ocupados (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_p</t>
+          <t>F5_P1_E2_p</t>
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>0.995</v>
+        <v>0.189</v>
       </c>
       <c r="C268" s="2" t="n"/>
       <c r="D268" s="2" t="n"/>
@@ -19268,28 +19643,24 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>P1-E3c: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>F5_P1_E4_beta</t>
+          <t>F5_P1_E3a_CONJ_A</t>
         </is>
       </c>
       <c r="B269" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C269" s="2" t="n">
-        <v>-0.5620000000000001</v>
-      </c>
-      <c r="D269" s="2" t="n">
-        <v>0.361</v>
-      </c>
+        <v>-0.85</v>
+      </c>
+      <c r="C269" s="2" t="n"/>
+      <c r="D269" s="2" t="n"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Δ log salario por punto de cuota</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -19297,51 +19668,46 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2010-2022</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>españoles (nacionalidad)</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>EES y EPA (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>P1-E4 (Borjas): asociación entre la cuota de nacidos fuera en la celda educación × edad y el salario por hora de los españoles (primeras diferencias; IC orientativo por errores agrupados en 15 celdas; p wild bootstrap = 0.61)</t>
+          <t>P1-E3a: el conjunto AKM0 es (−∞, a] ∪ [b, ∞); este es a</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>F5_P1_F_EFECTIVO</t>
+          <t>F5_P1_E3a_CONJ_B</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>24.4</v>
+        <v>1.81</v>
       </c>
       <c r="C270" s="2" t="n"/>
       <c r="D270" s="2" t="n"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -19361,34 +19727,38 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>F efectivo de primera etapa agrupado por provincia, especificación principal de P1</t>
+          <t>P1-E3a: el conjunto AKM0 es (−∞, a] ∪ [b, ∞); este es b</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>F5_P1_F_SHOCK</t>
+          <t>F5_P1_E3a_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="C271" s="2" t="n"/>
-      <c r="D271" s="2" t="n"/>
+        <v>-0.361</v>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>-1.014</v>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>-0.257</v>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -19396,6 +19766,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H271" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19408,34 +19783,34 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>F de primera etapa al nivel del shock (BHJ), especificación principal de P1 (umbral pre-registrado: 10)</t>
+          <t>P1-E3a: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True, convexo = True)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>F5_P1_H1_beta</t>
+          <t>F5_P1_E3a_PERM_p</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>-0.228</v>
+        <v>0.082</v>
       </c>
       <c r="C272" s="2" t="n"/>
       <c r="D272" s="2" t="n"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -19443,11 +19818,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H272" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19460,7 +19830,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -19470,24 +19840,24 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>P1-H1: efecto sobre tasa_empleo (MC2E, especificación principal)</t>
+          <t>P1-E3a: p del placebo de permutación de shocks (500 permutaciones)</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>F5_P1_H1_p</t>
+          <t>F5_P1_E3a_beta</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>0.388</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="C273" s="2" t="n"/>
       <c r="D273" s="2" t="n"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -19495,6 +19865,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H273" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19517,24 +19892,24 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>P1-H1: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E3a: asociación con tasa_empleo_educ_baja (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>F5_P1_H2_beta</t>
+          <t>F5_P1_E3a_p</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>0.282</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C274" s="2" t="n"/>
       <c r="D274" s="2" t="n"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -19542,11 +19917,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H274" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19569,24 +19939,24 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>P1-H2: efecto sobre tasa_paro (MC2E, especificación principal)</t>
+          <t>P1-E3a: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>F5_P1_H2_p</t>
+          <t>F5_P1_E3b_beta</t>
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>0.388</v>
+        <v>-0.029</v>
       </c>
       <c r="C275" s="2" t="n"/>
       <c r="D275" s="2" t="n"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -19594,6 +19964,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H275" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19616,24 +19991,24 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>P1-H2: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E3b: asociación con tasa_empleo_educ_media (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>F5_P2_E1_beta</t>
+          <t>F5_P1_E3b_p</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>0.025</v>
+        <v>0.995</v>
       </c>
       <c r="C276" s="2" t="n"/>
       <c r="D276" s="2" t="n"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -19641,11 +20016,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H276" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19668,24 +20038,24 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>P2-E1: efecto sobre cuota_nomanual (MC2E, especificación principal)</t>
+          <t>P1-E3b: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>F5_P2_E1_p</t>
+          <t>F5_P1_E3c_beta</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>0.985</v>
+        <v>0.18</v>
       </c>
       <c r="C277" s="2" t="n"/>
       <c r="D277" s="2" t="n"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -19693,6 +20063,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H277" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19715,24 +20090,24 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>P2-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E3c: asociación con tasa_empleo_educ_alta (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>F5_P2_E2_beta</t>
+          <t>F5_P1_E3c_p</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
-        <v>0.499</v>
+        <v>0.995</v>
       </c>
       <c r="C278" s="2" t="n"/>
       <c r="D278" s="2" t="n"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -19740,11 +20115,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H278" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19767,24 +20137,28 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>P2-E2: efecto sobre cuota_alta_cualif (MC2E, especificación principal)</t>
+          <t>P1-E3c: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>F5_P2_E2_p</t>
+          <t>F5_P1_E4_beta</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="C279" s="2" t="n"/>
-      <c r="D279" s="2" t="n"/>
+        <v>-0.1</v>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="D279" s="2" t="n">
+        <v>0.361</v>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>Δ log salario por punto de cuota</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -19792,50 +20166,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2010-2022</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>españoles (nacionalidad)</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>EES y EPA (INE)</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>P2-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E4 (Borjas): asociación entre la cuota de nacidos fuera en la celda educación × edad y el salario por hora de los españoles (primeras diferencias; IC orientativo por errores agrupados en 15 celdas; p wild bootstrap = 0.61)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>F5_P3_EDUC_beta</t>
+          <t>F5_P1_E6_beta</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>-0.169</v>
-      </c>
-      <c r="C280" s="2" t="n">
-        <v>-0.752</v>
-      </c>
-      <c r="D280" s="2" t="n">
-        <v>0.414</v>
-      </c>
+        <v>0.426</v>
+      </c>
+      <c r="C280" s="2" t="n"/>
+      <c r="D280" s="2" t="n"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>alumnos por profesor por punto porcentual</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -19850,44 +20225,44 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2016-2022</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>17 CCAA</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>EDUCAbase, ECP y padrón</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>P3 (educación): asociación entre el aumento de la población nacida fuera de 5-19 años y la ratio de alumnos por profesor en centros públicos (MC2E por comunidad; F efectivo = 39.5; p wild bootstrap de la forma reducida = 0.58; IC orientativo por errores agrupados en 17 comunidades)</t>
+          <t>P1-E6: asociación con log_pob_nativos (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>F5_P5_beta</t>
+          <t>F5_P1_E6_p</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>-0.325</v>
+        <v>0.995</v>
       </c>
       <c r="C281" s="2" t="n"/>
       <c r="D281" s="2" t="n"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -19895,51 +20270,46 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>NUTS2 UE-27</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Eurostat (censo 2021, migr_imm3ctb, EU-LFS)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>P5: asociación entre la llegada de población nacida fuera y la tasa de empleo de los nativos, NUTS2 de la UE-27, 2021-2024 (MC2E leave-one-country-out; p wild bootstrap por país = 0.38; IC: AKM0 con shocks comunes)</t>
+          <t>P1-E6: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
+          <t>F5_P1_F_EFECTIVO</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>1.02</v>
+        <v>24.4</v>
       </c>
       <c r="C282" s="2" t="n"/>
       <c r="D282" s="2" t="n"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -19949,44 +20319,44 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>F efectivo de primera etapa agrupado por provincia, especificación principal de P1</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
+          <t>F5_P1_F_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>0.84</v>
+        <v>11.1</v>
       </c>
       <c r="C283" s="2" t="n"/>
       <c r="D283" s="2" t="n"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -19996,44 +20366,44 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón (INE)</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>F de primera etapa al nivel del shock en la variante por nacionalidad</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
+          <t>F5_P1_F_SHOCK</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>0.96</v>
+        <v>6.6</v>
       </c>
       <c r="C284" s="2" t="n"/>
       <c r="D284" s="2" t="n"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -20043,44 +20413,44 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>F de primera etapa al nivel del shock (BHJ), especificación principal de P1 (umbral pre-registrado: 10)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_15_34</t>
+          <t>F5_P1_F_SIN_TOP3</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>0.9</v>
+        <v>0.21</v>
       </c>
       <c r="C285" s="2" t="n"/>
       <c r="D285" s="2" t="n"/>
       <c r="E285" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -20090,44 +20460,48 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón (INE)</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>F de primera etapa al nivel del shock al excluir los tres orígenes de mayor peso de Rotemberg (prueba no informativa si es &lt; 10)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_35_54</t>
+          <t>F5_P1_H1_MULT_MED</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="C286" s="2" t="n"/>
-      <c r="D286" s="2" t="n"/>
+        <v>-0.416</v>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>-0.652</v>
+      </c>
+      <c r="D286" s="2" t="n">
+        <v>-0.174</v>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -20135,46 +20509,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P1-H1: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_55_74</t>
+          <t>F5_P1_H1_MULT_NEG</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>0.85</v>
+        <v>32</v>
       </c>
       <c r="C287" s="2" t="n"/>
       <c r="D287" s="2" t="n"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -20184,44 +20563,44 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P1-H1: especificaciones del multiverso con β negativo (de 32)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_15_34</t>
+          <t>F5_P1_H1_MULT_RECHAZA</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C288" s="2" t="n"/>
       <c r="D288" s="2" t="n"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -20231,44 +20610,48 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>P1-H1: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_35_54</t>
+          <t>F5_P1_H1_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="C289" s="2" t="n"/>
-      <c r="D289" s="2" t="n"/>
+        <v>-0.118</v>
+      </c>
+      <c r="C289" s="2" t="n">
+        <v>-0.622</v>
+      </c>
+      <c r="D289" s="2" t="n">
+        <v>0.677</v>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -20276,46 +20659,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P1-H1: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True)</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_55_74</t>
+          <t>F5_P1_H1_beta</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>2.58</v>
+        <v>-0.228</v>
       </c>
       <c r="C290" s="2" t="n"/>
       <c r="D290" s="2" t="n"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -20323,46 +20711,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P1-H1: asociación con tasa_empleo (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_15_34</t>
+          <t>F5_P1_H1_p</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>0.9</v>
+        <v>0.388</v>
       </c>
       <c r="C291" s="2" t="n"/>
       <c r="D291" s="2" t="n"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -20372,44 +20765,48 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>P1-H1: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_35_54</t>
+          <t>F5_P1_H2_MULT_MED</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="C292" s="2" t="n"/>
-      <c r="D292" s="2" t="n"/>
+        <v>0.314</v>
+      </c>
+      <c r="C292" s="2" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D292" s="2" t="n">
+        <v>0.6</v>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -20417,46 +20814,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P1-H2: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_55_74</t>
+          <t>F5_P1_H2_MULT_NEG</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C293" s="2" t="n"/>
       <c r="D293" s="2" t="n"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -20466,307 +20868,1591 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P1-H2: especificaciones del multiverso con β negativo (de 32)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>F6_POB_CUOTA_FUERA_ECV</t>
+          <t>F5_P1_H2_MULT_RECHAZA</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>18.5</v>
+        <v>3</v>
       </c>
       <c r="C294" s="2" t="n"/>
       <c r="D294" s="2" t="n"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>% de la población</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>ECV (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
+          <t>P1-H2: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_España</t>
+          <t>F5_P1_H2_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>6252</v>
-      </c>
-      <c r="C295" s="2" t="n"/>
-      <c r="D295" s="2" t="n"/>
+        <v>0.181</v>
+      </c>
+      <c r="C295" s="2" t="n">
+        <v>-0.733</v>
+      </c>
+      <c r="D295" s="2" t="n">
+        <v>1.227</v>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
+          <t>P1-H2: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
+          <t>F5_P1_H2_beta</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>2813</v>
+        <v>0.282</v>
       </c>
       <c r="C296" s="2" t="n"/>
       <c r="D296" s="2" t="n"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+          <t>P1-H2: asociación con tasa_paro (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+          <t>F5_P1_H2_p</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>1927</v>
+        <v>0.388</v>
       </c>
       <c r="C297" s="2" t="n"/>
       <c r="D297" s="2" t="n"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+          <t>P1-H2: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+          <t>F5_P2_E1_beta</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
-        <v>2.5</v>
+        <v>0.025</v>
       </c>
       <c r="C298" s="2" t="n"/>
       <c r="D298" s="2" t="n"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t>% de las prestaciones monetarias</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+          <t>P2-E1: asociación con cuota_nomanual (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>F6_TRABAJO_CUOTA_FUERA</t>
+          <t>F5_P2_E1_p</t>
         </is>
       </c>
       <c r="B299" s="2" t="n">
-        <v>15.5</v>
+        <v>0.985</v>
       </c>
       <c r="C299" s="2" t="n"/>
       <c r="D299" s="2" t="n"/>
       <c r="E299" t="inlineStr">
         <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>P2-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>F5_P2_E2_beta</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="C300" s="2" t="n"/>
+      <c r="D300" s="2" t="n"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>P2-E2: asociación con cuota_alta_cualif (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>F5_P2_E2_p</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="C301" s="2" t="n"/>
+      <c r="D301" s="2" t="n"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>p ajustado</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>2005-2022</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>50 provincias</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>nacidos en España</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>padrón, ECP, EPA (INE)</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>P2-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>F5_P3_EDUC_beta</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="n">
+        <v>-0.169</v>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>-0.752</v>
+      </c>
+      <c r="D302" s="2" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>alumnos por profesor por punto porcentual</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>2016-2022</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>17 CCAA</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>EDUCAbase, ECP y padrón</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>P3 (educación): asociación entre el aumento de la población nacida fuera de 5-19 años y la ratio de alumnos por profesor en centros públicos (MC2E por comunidad; F efectivo = 39.5; p wild bootstrap de la forma reducida = 0.58; IC orientativo por errores agrupados en 17 comunidades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>F5_P5_HET_centro_y_este</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="C303" s="2" t="n"/>
+      <c r="D303" s="2" t="n"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>NUTS2, centro y este</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>nativos</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>P5, países centro y este: β leave-one-country-out (28 regiones; p wild bootstrap = 0.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>F5_P5_HET_continentales</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="n">
+        <v>-0.163</v>
+      </c>
+      <c r="C304" s="2" t="n"/>
+      <c r="D304" s="2" t="n"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>NUTS2, continentales</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>nativos</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>P5, países continentales: β leave-one-country-out (93 regiones; p wild bootstrap = 0.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>F5_P5_HET_mediterráneos</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="C305" s="2" t="n"/>
+      <c r="D305" s="2" t="n"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>NUTS2, mediterráneos</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>nativos</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>P5, países mediterráneos: β leave-one-country-out (57 regiones; p wild bootstrap = 0.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>F5_P5_HET_nórdicos</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="n">
+        <v>-0.904</v>
+      </c>
+      <c r="C306" s="2" t="n"/>
+      <c r="D306" s="2" t="n"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>NUTS2, nórdicos</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>nativos</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>P5, países nórdicos: β leave-one-country-out (17 regiones; p wild bootstrap = 0.33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>F5_P5_beta</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="n">
+        <v>-0.325</v>
+      </c>
+      <c r="C307" s="2" t="n">
+        <v>-0.968</v>
+      </c>
+      <c r="D307" s="2" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>pp por pp</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>2021-2024</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>NUTS2 UE-27</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>nativos</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Eurostat (censo 2021, migr_imm3ctb, EU-LFS)</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>P5: asociación entre la llegada de población nacida fuera y la tasa de empleo de los nativos, NUTS2 de la UE-27, 2021-2024 (MC2E leave-one-country-out; p wild bootstrap por país = 0.38; IC orientativo por errores agrupados por país)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C308" s="2" t="n"/>
+      <c r="D308" s="2" t="n"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C309" s="2" t="n"/>
+      <c r="D309" s="2" t="n"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C310" s="2" t="n"/>
+      <c r="D310" s="2" t="n"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_FAR_15_34</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C311" s="2" t="n"/>
+      <c r="D311" s="2" t="n"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_FAR_35_54</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C312" s="2" t="n"/>
+      <c r="D312" s="2" t="n"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_FAR_55_74</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C313" s="2" t="n"/>
+      <c r="D313" s="2" t="n"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_15_34</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C314" s="2" t="n"/>
+      <c r="D314" s="2" t="n"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_35_54</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C315" s="2" t="n"/>
+      <c r="D315" s="2" t="n"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_55_74</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C316" s="2" t="n"/>
+      <c r="D316" s="2" t="n"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_15_34</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C317" s="2" t="n"/>
+      <c r="D317" s="2" t="n"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_35_54</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C318" s="2" t="n"/>
+      <c r="D318" s="2" t="n"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_55_74</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C319" s="2" t="n"/>
+      <c r="D319" s="2" t="n"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>F6_POB_CUOTA_FUERA_ECV</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C320" s="2" t="n"/>
+      <c r="D320" s="2" t="n"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>% de la población</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>ECV (INE)</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_España</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="n">
+        <v>6252</v>
+      </c>
+      <c r="C321" s="2" t="n"/>
+      <c r="D321" s="2" t="n"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>2813</v>
+      </c>
+      <c r="C322" s="2" t="n"/>
+      <c r="D322" s="2" t="n"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Resto UE</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C323" s="2" t="n"/>
+      <c r="D323" s="2" t="n"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Resto del mundo</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C324" s="2" t="n"/>
+      <c r="D324" s="2" t="n"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>% de las prestaciones monetarias</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>F6_TRABAJO_CUOTA_FUERA</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C325" s="2" t="n"/>
+      <c r="D325" s="2" t="n"/>
+      <c r="E325" t="inlineStr">
+        <is>
           <t>% del total</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
+      <c r="F325" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
+      <c r="H325" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
         <is>
           <t>nacidos fuera</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
+      <c r="K325" t="inlineStr">
         <is>
           <t>ECV (INE) y Eurostat</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
+      <c r="L325" t="inlineStr">
         <is>
           <t>Cuota de los nacidos fuera en IRPF del trabajo y cotizaciones sociales (calibradas a las cuentas de las AAPP)</t>
         </is>

--- a/output/f7/tablas_m1.xlsx
+++ b/output/f7/tablas_m1.xlsx
@@ -4635,915 +4635,1095 @@
     </comment>
     <comment ref="B265" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C265" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D265" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B266" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C266" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D266" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B267" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C267" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D267" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B268" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C268" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D268" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B269" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C269" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D269" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B270" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C270" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D270" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B271" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C271" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D271" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B272" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C272" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D272" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B273" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C273" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D273" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B274" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C274" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D274" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D275" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D276" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B277" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C265" authorId="0" shapeId="0">
+    <comment ref="C277" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D265" authorId="0" shapeId="0">
+    <comment ref="D277" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B266" authorId="0" shapeId="0">
+    <comment ref="B278" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C266" authorId="0" shapeId="0">
+    <comment ref="C278" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D266" authorId="0" shapeId="0">
+    <comment ref="D278" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B267" authorId="0" shapeId="0">
+    <comment ref="B279" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C267" authorId="0" shapeId="0">
+    <comment ref="C279" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D267" authorId="0" shapeId="0">
+    <comment ref="D279" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B268" authorId="0" shapeId="0">
+    <comment ref="B280" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C268" authorId="0" shapeId="0">
+    <comment ref="C280" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D268" authorId="0" shapeId="0">
+    <comment ref="D280" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B269" authorId="0" shapeId="0">
+    <comment ref="B281" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C269" authorId="0" shapeId="0">
+    <comment ref="C281" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D269" authorId="0" shapeId="0">
+    <comment ref="D281" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B270" authorId="0" shapeId="0">
+    <comment ref="B282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C270" authorId="0" shapeId="0">
+    <comment ref="C282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D270" authorId="0" shapeId="0">
+    <comment ref="D282" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B271" authorId="0" shapeId="0">
+    <comment ref="B283" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C271" authorId="0" shapeId="0">
+    <comment ref="C283" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D271" authorId="0" shapeId="0">
+    <comment ref="D283" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B272" authorId="0" shapeId="0">
+    <comment ref="B284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C272" authorId="0" shapeId="0">
+    <comment ref="C284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D272" authorId="0" shapeId="0">
+    <comment ref="D284" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B273" authorId="0" shapeId="0">
+    <comment ref="B285" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C273" authorId="0" shapeId="0">
+    <comment ref="C285" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D273" authorId="0" shapeId="0">
+    <comment ref="D285" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B274" authorId="0" shapeId="0">
+    <comment ref="B286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C274" authorId="0" shapeId="0">
+    <comment ref="C286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D274" authorId="0" shapeId="0">
+    <comment ref="D286" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B275" authorId="0" shapeId="0">
+    <comment ref="B287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C275" authorId="0" shapeId="0">
+    <comment ref="C287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D275" authorId="0" shapeId="0">
+    <comment ref="D287" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B276" authorId="0" shapeId="0">
+    <comment ref="B288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C276" authorId="0" shapeId="0">
+    <comment ref="C288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D276" authorId="0" shapeId="0">
+    <comment ref="D288" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B277" authorId="0" shapeId="0">
+    <comment ref="B289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C277" authorId="0" shapeId="0">
+    <comment ref="C289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D277" authorId="0" shapeId="0">
+    <comment ref="D289" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B278" authorId="0" shapeId="0">
+    <comment ref="B290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C278" authorId="0" shapeId="0">
+    <comment ref="C290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D278" authorId="0" shapeId="0">
+    <comment ref="D290" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B279" authorId="0" shapeId="0">
+    <comment ref="B291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="C279" authorId="0" shapeId="0">
+    <comment ref="C291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="D279" authorId="0" shapeId="0">
+    <comment ref="D291" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="B280" authorId="0" shapeId="0">
+    <comment ref="B292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C280" authorId="0" shapeId="0">
+    <comment ref="C292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D280" authorId="0" shapeId="0">
+    <comment ref="D292" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B281" authorId="0" shapeId="0">
+    <comment ref="B293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C281" authorId="0" shapeId="0">
+    <comment ref="C293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D281" authorId="0" shapeId="0">
+    <comment ref="D293" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B282" authorId="0" shapeId="0">
+    <comment ref="B294" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C282" authorId="0" shapeId="0">
+    <comment ref="C294" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D282" authorId="0" shapeId="0">
+    <comment ref="D294" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B283" authorId="0" shapeId="0">
+    <comment ref="B295" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C283" authorId="0" shapeId="0">
+    <comment ref="C295" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D283" authorId="0" shapeId="0">
+    <comment ref="D295" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B284" authorId="0" shapeId="0">
+    <comment ref="B296" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C284" authorId="0" shapeId="0">
+    <comment ref="C296" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D284" authorId="0" shapeId="0">
+    <comment ref="D296" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B285" authorId="0" shapeId="0">
+    <comment ref="B297" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C285" authorId="0" shapeId="0">
+    <comment ref="C297" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D285" authorId="0" shapeId="0">
+    <comment ref="D297" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B286" authorId="0" shapeId="0">
+    <comment ref="B298" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C286" authorId="0" shapeId="0">
+    <comment ref="C298" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D286" authorId="0" shapeId="0">
+    <comment ref="D298" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B287" authorId="0" shapeId="0">
+    <comment ref="B299" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C287" authorId="0" shapeId="0">
+    <comment ref="C299" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D287" authorId="0" shapeId="0">
+    <comment ref="D299" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B288" authorId="0" shapeId="0">
+    <comment ref="B300" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C288" authorId="0" shapeId="0">
+    <comment ref="C300" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D288" authorId="0" shapeId="0">
+    <comment ref="D300" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B289" authorId="0" shapeId="0">
+    <comment ref="B301" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C289" authorId="0" shapeId="0">
+    <comment ref="C301" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D289" authorId="0" shapeId="0">
+    <comment ref="D301" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B290" authorId="0" shapeId="0">
+    <comment ref="B302" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C290" authorId="0" shapeId="0">
+    <comment ref="C302" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D290" authorId="0" shapeId="0">
+    <comment ref="D302" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B291" authorId="0" shapeId="0">
+    <comment ref="B303" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C291" authorId="0" shapeId="0">
+    <comment ref="C303" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D291" authorId="0" shapeId="0">
+    <comment ref="D303" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B292" authorId="0" shapeId="0">
+    <comment ref="B304" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C292" authorId="0" shapeId="0">
+    <comment ref="C304" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D292" authorId="0" shapeId="0">
+    <comment ref="D304" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B293" authorId="0" shapeId="0">
+    <comment ref="B305" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C293" authorId="0" shapeId="0">
+    <comment ref="C305" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D293" authorId="0" shapeId="0">
+    <comment ref="D305" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B294" authorId="0" shapeId="0">
+    <comment ref="B306" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C294" authorId="0" shapeId="0">
+    <comment ref="C306" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D294" authorId="0" shapeId="0">
+    <comment ref="D306" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B295" authorId="0" shapeId="0">
+    <comment ref="B307" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C295" authorId="0" shapeId="0">
+    <comment ref="C307" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D295" authorId="0" shapeId="0">
+    <comment ref="D307" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B296" authorId="0" shapeId="0">
+    <comment ref="B308" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C296" authorId="0" shapeId="0">
+    <comment ref="C308" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D296" authorId="0" shapeId="0">
+    <comment ref="D308" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B297" authorId="0" shapeId="0">
+    <comment ref="B309" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C297" authorId="0" shapeId="0">
+    <comment ref="C309" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D297" authorId="0" shapeId="0">
+    <comment ref="D309" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B298" authorId="0" shapeId="0">
+    <comment ref="B310" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C298" authorId="0" shapeId="0">
+    <comment ref="C310" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D298" authorId="0" shapeId="0">
+    <comment ref="D310" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B299" authorId="0" shapeId="0">
+    <comment ref="B311" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C299" authorId="0" shapeId="0">
+    <comment ref="C311" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D299" authorId="0" shapeId="0">
+    <comment ref="D311" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B300" authorId="0" shapeId="0">
+    <comment ref="B312" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C300" authorId="0" shapeId="0">
+    <comment ref="C312" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D300" authorId="0" shapeId="0">
+    <comment ref="D312" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B301" authorId="0" shapeId="0">
+    <comment ref="B313" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C301" authorId="0" shapeId="0">
+    <comment ref="C313" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D301" authorId="0" shapeId="0">
+    <comment ref="D313" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B302" authorId="0" shapeId="0">
+    <comment ref="B314" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="C302" authorId="0" shapeId="0">
+    <comment ref="C314" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="D302" authorId="0" shapeId="0">
+    <comment ref="D314" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="B303" authorId="0" shapeId="0">
+    <comment ref="B315" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C303" authorId="0" shapeId="0">
+    <comment ref="C315" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D303" authorId="0" shapeId="0">
+    <comment ref="D315" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B304" authorId="0" shapeId="0">
+    <comment ref="B316" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C304" authorId="0" shapeId="0">
+    <comment ref="C316" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D304" authorId="0" shapeId="0">
+    <comment ref="D316" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B305" authorId="0" shapeId="0">
+    <comment ref="B317" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C305" authorId="0" shapeId="0">
+    <comment ref="C317" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D305" authorId="0" shapeId="0">
+    <comment ref="D317" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B306" authorId="0" shapeId="0">
+    <comment ref="B318" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C306" authorId="0" shapeId="0">
+    <comment ref="C318" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D306" authorId="0" shapeId="0">
+    <comment ref="D318" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B307" authorId="0" shapeId="0">
+    <comment ref="B319" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C307" authorId="0" shapeId="0">
+    <comment ref="C319" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D307" authorId="0" shapeId="0">
+    <comment ref="D319" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B308" authorId="0" shapeId="0">
+    <comment ref="B320" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C308" authorId="0" shapeId="0">
+    <comment ref="C320" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D308" authorId="0" shapeId="0">
+    <comment ref="D320" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B309" authorId="0" shapeId="0">
+    <comment ref="B321" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C309" authorId="0" shapeId="0">
+    <comment ref="C321" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D309" authorId="0" shapeId="0">
+    <comment ref="D321" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B310" authorId="0" shapeId="0">
+    <comment ref="B322" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C310" authorId="0" shapeId="0">
+    <comment ref="C322" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D310" authorId="0" shapeId="0">
+    <comment ref="D322" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B311" authorId="0" shapeId="0">
+    <comment ref="B323" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C311" authorId="0" shapeId="0">
+    <comment ref="C323" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D311" authorId="0" shapeId="0">
+    <comment ref="D323" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B312" authorId="0" shapeId="0">
+    <comment ref="B324" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C312" authorId="0" shapeId="0">
+    <comment ref="C324" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D312" authorId="0" shapeId="0">
+    <comment ref="D324" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B313" authorId="0" shapeId="0">
+    <comment ref="B325" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C313" authorId="0" shapeId="0">
+    <comment ref="C325" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D313" authorId="0" shapeId="0">
+    <comment ref="D325" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B314" authorId="0" shapeId="0">
+    <comment ref="B326" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C314" authorId="0" shapeId="0">
+    <comment ref="C326" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D314" authorId="0" shapeId="0">
+    <comment ref="D326" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B315" authorId="0" shapeId="0">
+    <comment ref="B327" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C315" authorId="0" shapeId="0">
+    <comment ref="C327" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D315" authorId="0" shapeId="0">
+    <comment ref="D327" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B316" authorId="0" shapeId="0">
+    <comment ref="B328" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C316" authorId="0" shapeId="0">
+    <comment ref="C328" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D316" authorId="0" shapeId="0">
+    <comment ref="D328" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B317" authorId="0" shapeId="0">
+    <comment ref="B329" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C317" authorId="0" shapeId="0">
+    <comment ref="C329" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D317" authorId="0" shapeId="0">
+    <comment ref="D329" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B318" authorId="0" shapeId="0">
+    <comment ref="B330" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C318" authorId="0" shapeId="0">
+    <comment ref="C330" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D318" authorId="0" shapeId="0">
+    <comment ref="D330" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B319" authorId="0" shapeId="0">
+    <comment ref="B331" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C319" authorId="0" shapeId="0">
+    <comment ref="C331" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D319" authorId="0" shapeId="0">
+    <comment ref="D331" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B320" authorId="0" shapeId="0">
+    <comment ref="B332" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C320" authorId="0" shapeId="0">
+    <comment ref="C332" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D320" authorId="0" shapeId="0">
+    <comment ref="D332" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B321" authorId="0" shapeId="0">
+    <comment ref="B333" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C321" authorId="0" shapeId="0">
+    <comment ref="C333" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D321" authorId="0" shapeId="0">
+    <comment ref="D333" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B322" authorId="0" shapeId="0">
+    <comment ref="B334" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C322" authorId="0" shapeId="0">
+    <comment ref="C334" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D322" authorId="0" shapeId="0">
+    <comment ref="D334" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B323" authorId="0" shapeId="0">
+    <comment ref="B335" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C323" authorId="0" shapeId="0">
+    <comment ref="C335" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D323" authorId="0" shapeId="0">
+    <comment ref="D335" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B324" authorId="0" shapeId="0">
+    <comment ref="B336" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C324" authorId="0" shapeId="0">
+    <comment ref="C336" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D324" authorId="0" shapeId="0">
+    <comment ref="D336" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B325" authorId="0" shapeId="0">
+    <comment ref="B337" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C325" authorId="0" shapeId="0">
+    <comment ref="C337" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D325" authorId="0" shapeId="0">
+    <comment ref="D337" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
@@ -6653,7 +6833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L325"/>
+  <dimension ref="A1:L337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -19452,17 +19632,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>F5_P1_E1_beta</t>
+          <t>F5X_E3a_ELAST</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>-0.021</v>
+        <v>-0.18</v>
       </c>
       <c r="C265" s="2" t="n"/>
       <c r="D265" s="2" t="n"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>elasticidad</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -19470,11 +19650,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H265" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19487,7 +19662,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -19497,24 +19672,24 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>P1-E1: asociación con tasa_actividad (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3a expresada como elasticidad de la tasa de empleo respecto a la cuota de nacidos fuera, con medias de los años iniciales (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>F5_P1_E1_p</t>
+          <t>F5X_E3a_MCO</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
-        <v>0.995</v>
+        <v>-0.2</v>
       </c>
       <c r="C266" s="2" t="n"/>
       <c r="D266" s="2" t="n"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -19534,7 +19709,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -19544,24 +19719,24 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>P1-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E3a por MCO con la especificación principal (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>F5_P1_E2_beta</t>
+          <t>F5X_E3a_OCU</t>
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>-0.636</v>
+        <v>-2.58</v>
       </c>
       <c r="C267" s="2" t="n"/>
       <c r="D267" s="2" t="n"/>
       <c r="E267" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>log por pp</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -19569,11 +19744,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H267" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19586,7 +19756,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -19596,18 +19766,18 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>P1-E2: asociación con log_ocupados (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>Δ log ocupados nacidos en España con educación baja por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.02)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>F5_P1_E2_p</t>
+          <t>F5X_E3a_OCU_p</t>
         </is>
       </c>
       <c r="B268" s="2" t="n">
-        <v>0.189</v>
+        <v>0.021</v>
       </c>
       <c r="C268" s="2" t="n"/>
       <c r="D268" s="2" t="n"/>
@@ -19633,7 +19803,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -19643,24 +19813,24 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>P1-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>p AKM0 sin ajustar de Δ log ocupados nacidos en España con educación baja (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_CONJ_A</t>
+          <t>F5X_E3a_POB</t>
         </is>
       </c>
       <c r="B269" s="2" t="n">
-        <v>-0.85</v>
+        <v>-1.24</v>
       </c>
       <c r="C269" s="2" t="n"/>
       <c r="D269" s="2" t="n"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>log por pp</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -19690,24 +19860,24 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>P1-E3a: el conjunto AKM0 es (−∞, a] ∪ [b, ∞); este es a</t>
+          <t>Δ log población nacida en España de 16-64 con educación baja (EPA) por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.16)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_CONJ_B</t>
+          <t>F5X_E3a_POB_MA</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>1.81</v>
+        <v>0.63</v>
       </c>
       <c r="C270" s="2" t="n"/>
       <c r="D270" s="2" t="n"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>log por pp</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -19737,28 +19907,24 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>P1-E3a: el conjunto AKM0 es (−∞, a] ∪ [b, ∞); este es b</t>
+          <t>Δ log población nacida en España de 16-64 con educación media o alta (EPA) por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.16)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_NACIONALIDAD</t>
+          <t>F5X_E3a_POB_MA_p</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="C271" s="2" t="n">
-        <v>-1.014</v>
-      </c>
-      <c r="D271" s="2" t="n">
-        <v>-0.257</v>
-      </c>
+        <v>0.164</v>
+      </c>
+      <c r="C271" s="2" t="n"/>
+      <c r="D271" s="2" t="n"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -19766,11 +19932,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H271" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19793,18 +19954,18 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>P1-E3a: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True, convexo = True)</t>
+          <t>p AKM0 sin ajustar de Δ log población nacida en España de 16-64 con educación media o alta (EPA) (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_PERM_p</t>
+          <t>F5X_E3a_POB_p</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>0.082</v>
+        <v>0.158</v>
       </c>
       <c r="C272" s="2" t="n"/>
       <c r="D272" s="2" t="n"/>
@@ -19840,18 +20001,18 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>P1-E3a: p del placebo de permutación de shocks (500 permutaciones)</t>
+          <t>p AKM0 sin ajustar de Δ log población nacida en España de 16-64 con educación baja (EPA) (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_beta</t>
+          <t>F5X_E3b_NAC</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
-        <v>-0.6889999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="C273" s="2" t="n"/>
       <c r="D273" s="2" t="n"/>
@@ -19865,11 +20026,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H273" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19882,7 +20038,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación media</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -19892,24 +20048,24 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>P1-E3a: asociación con tasa_empleo_educ_baja (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3b (educación media), variante por nacionalidad (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_p</t>
+          <t>F5X_E3c_NAC</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="C274" s="2" t="n"/>
       <c r="D274" s="2" t="n"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -19929,7 +20085,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación alta</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -19939,18 +20095,18 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>P1-E3a: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E3c (educación alta), variante por nacionalidad (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_beta</t>
+          <t>F5X_NAC_IMPLICITO</t>
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>-0.029</v>
+        <v>-0.16</v>
       </c>
       <c r="C275" s="2" t="n"/>
       <c r="D275" s="2" t="n"/>
@@ -19964,11 +20120,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H275" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -19991,39 +20142,39 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>P1-E3b: asociación con tasa_empleo_educ_media (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>Media ponderada por educación de las estimaciones por nacionalidad de P1-E3a, E3b y E3c (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_p</t>
+          <t>F5X_PESO_BAJA</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
-        <v>0.995</v>
+        <v>48.7</v>
       </c>
       <c r="C276" s="2" t="n"/>
       <c r="D276" s="2" t="n"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>% de los nativos de 16-64</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2005, 2009, 2015</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -20033,23 +20184,23 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>EPA (INE)</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>P1-E3b: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>Peso de la educación baja entre los nacidos en España de 16-64 (EPA, años iniciales de los periodos)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_beta</t>
+          <t>F5_P1_E1_beta</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.021</v>
       </c>
       <c r="C277" s="2" t="n"/>
       <c r="D277" s="2" t="n"/>
@@ -20090,14 +20241,14 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>P1-E3c: asociación con tasa_empleo_educ_alta (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E1: asociación con tasa_actividad (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_p</t>
+          <t>F5_P1_E1_p</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
@@ -20137,28 +20288,24 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>P1-E3c: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>F5_P1_E4_beta</t>
+          <t>F5_P1_E2_beta</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C279" s="2" t="n">
-        <v>-0.5620000000000001</v>
-      </c>
-      <c r="D279" s="2" t="n">
-        <v>0.361</v>
-      </c>
+        <v>-0.636</v>
+      </c>
+      <c r="C279" s="2" t="n"/>
+      <c r="D279" s="2" t="n"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Δ log salario por punto de cuota</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -20173,44 +20320,44 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2010-2022</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>españoles (nacionalidad)</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>EES y EPA (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>P1-E4 (Borjas): asociación entre la cuota de nacidos fuera en la celda educación × edad y el salario por hora de los españoles (primeras diferencias; IC orientativo por errores agrupados en 15 celdas; p wild bootstrap = 0.61)</t>
+          <t>P1-E2: asociación con log_ocupados (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>F5_P1_E6_beta</t>
+          <t>F5_P1_E2_p</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
-        <v>0.426</v>
+        <v>0.189</v>
       </c>
       <c r="C280" s="2" t="n"/>
       <c r="D280" s="2" t="n"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -20218,11 +20365,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H280" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -20245,24 +20387,24 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>P1-E6: asociación con log_pob_nativos (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>F5_P1_E6_p</t>
+          <t>F5_P1_E3a_CONJ_A</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>0.995</v>
+        <v>-0.85</v>
       </c>
       <c r="C281" s="2" t="n"/>
       <c r="D281" s="2" t="n"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -20282,7 +20424,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -20292,24 +20434,24 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>P1-E6: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E3a: el conjunto AKM0 es (−∞, a] ∪ [b, ∞); este es a</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>F5_P1_F_EFECTIVO</t>
+          <t>F5_P1_E3a_CONJ_B</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>24.4</v>
+        <v>1.81</v>
       </c>
       <c r="C282" s="2" t="n"/>
       <c r="D282" s="2" t="n"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -20329,34 +20471,38 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>F efectivo de primera etapa agrupado por provincia, especificación principal de P1</t>
+          <t>P1-E3a: el conjunto AKM0 es (−∞, a] ∪ [b, ∞); este es b</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>F5_P1_F_NACIONALIDAD</t>
+          <t>F5_P1_E3a_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="C283" s="2" t="n"/>
-      <c r="D283" s="2" t="n"/>
+        <v>-0.361</v>
+      </c>
+      <c r="C283" s="2" t="n">
+        <v>-1.014</v>
+      </c>
+      <c r="D283" s="2" t="n">
+        <v>-0.257</v>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -20364,6 +20510,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H283" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -20376,34 +20527,34 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>padrón (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>F de primera etapa al nivel del shock en la variante por nacionalidad</t>
+          <t>P1-E3a: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True, convexo = True)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>F5_P1_F_SHOCK</t>
+          <t>F5_P1_E3a_PERM_p</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>6.6</v>
+        <v>0.082</v>
       </c>
       <c r="C284" s="2" t="n"/>
       <c r="D284" s="2" t="n"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -20423,34 +20574,34 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>F de primera etapa al nivel del shock (BHJ), especificación principal de P1 (umbral pre-registrado: 10)</t>
+          <t>P1-E3a: p del placebo de permutación de shocks (500 permutaciones)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>F5_P1_F_SIN_TOP3</t>
+          <t>F5_P1_E3a_beta</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>0.21</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="C285" s="2" t="n"/>
       <c r="D285" s="2" t="n"/>
       <c r="E285" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -20458,6 +20609,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H285" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -20470,38 +20626,34 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>padrón (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>F de primera etapa al nivel del shock al excluir los tres orígenes de mayor peso de Rotemberg (prueba no informativa si es &lt; 10)</t>
+          <t>P1-E3a: asociación con tasa_empleo_educ_baja (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_MED</t>
+          <t>F5_P1_E3a_p</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>-0.416</v>
-      </c>
-      <c r="C286" s="2" t="n">
-        <v>-0.652</v>
-      </c>
-      <c r="D286" s="2" t="n">
-        <v>-0.174</v>
-      </c>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="C286" s="2" t="n"/>
+      <c r="D286" s="2" t="n"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -20509,11 +20661,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H286" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -20521,7 +20668,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -20536,24 +20683,24 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>P1-H1: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
+          <t>P1-E3a: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_NEG</t>
+          <t>F5_P1_E3b_beta</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
-        <v>32</v>
+        <v>-0.029</v>
       </c>
       <c r="C287" s="2" t="n"/>
       <c r="D287" s="2" t="n"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -20561,6 +20708,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H287" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -20568,7 +20720,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -20583,24 +20735,24 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso con β negativo (de 32)</t>
+          <t>P1-E3b: asociación con tasa_empleo_educ_media (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_RECHAZA</t>
+          <t>F5_P1_E3b_p</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>0</v>
+        <v>0.995</v>
       </c>
       <c r="C288" s="2" t="n"/>
       <c r="D288" s="2" t="n"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -20615,7 +20767,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -20630,25 +20782,21 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
+          <t>P1-E3b: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>F5_P1_H1_NACIONALIDAD</t>
+          <t>F5_P1_E3c_beta</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>-0.118</v>
-      </c>
-      <c r="C289" s="2" t="n">
-        <v>-0.622</v>
-      </c>
-      <c r="D289" s="2" t="n">
-        <v>0.677</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="C289" s="2" t="n"/>
+      <c r="D289" s="2" t="n"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -20686,24 +20834,24 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>P1-H1: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True)</t>
+          <t>P1-E3c: asociación con tasa_empleo_educ_alta (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>F5_P1_H1_beta</t>
+          <t>F5_P1_E3c_p</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
-        <v>-0.228</v>
+        <v>0.995</v>
       </c>
       <c r="C290" s="2" t="n"/>
       <c r="D290" s="2" t="n"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -20711,11 +20859,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H290" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -20738,24 +20881,28 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>P1-H1: asociación con tasa_empleo (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3c: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>F5_P1_H1_p</t>
+          <t>F5_P1_E4_beta</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="C291" s="2" t="n"/>
-      <c r="D291" s="2" t="n"/>
+        <v>-0.1</v>
+      </c>
+      <c r="C291" s="2" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="D291" s="2" t="n">
+        <v>0.361</v>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>Δ log salario por punto de cuota</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -20763,47 +20910,48 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2010-2022</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>españoles (nacionalidad)</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>EES y EPA (INE)</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>P1-H1: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-E4 (Borjas): asociación entre la cuota de nacidos fuera en la celda educación × edad y el salario por hora de los españoles (primeras diferencias; IC orientativo por errores agrupados en 15 celdas; p wild bootstrap = 0.61)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_MED</t>
+          <t>F5_P1_E6_beta</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="C292" s="2" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D292" s="2" t="n">
-        <v>0.6</v>
-      </c>
+        <v>0.426</v>
+      </c>
+      <c r="C292" s="2" t="n"/>
+      <c r="D292" s="2" t="n"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -20826,7 +20974,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -20841,24 +20989,24 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>P1-H2: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
+          <t>P1-E6: asociación con log_pob_nativos (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_NEG</t>
+          <t>F5_P1_E6_p</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>0</v>
+        <v>0.995</v>
       </c>
       <c r="C293" s="2" t="n"/>
       <c r="D293" s="2" t="n"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -20873,7 +21021,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -20888,24 +21036,24 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso con β negativo (de 32)</t>
+          <t>P1-E6: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_RECHAZA</t>
+          <t>F5_P1_F_EFECTIVO</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
-        <v>3</v>
+        <v>24.4</v>
       </c>
       <c r="C294" s="2" t="n"/>
       <c r="D294" s="2" t="n"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -20920,43 +21068,39 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
+          <t>F efectivo de primera etapa agrupado por provincia, especificación principal de P1</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>F5_P1_H2_NACIONALIDAD</t>
+          <t>F5_P1_F_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="C295" s="2" t="n">
-        <v>-0.733</v>
-      </c>
-      <c r="D295" s="2" t="n">
-        <v>1.227</v>
-      </c>
+        <v>11.1</v>
+      </c>
+      <c r="C295" s="2" t="n"/>
+      <c r="D295" s="2" t="n"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -20964,11 +21108,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H295" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -20981,34 +21120,34 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón (INE)</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>P1-H2: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True)</t>
+          <t>F de primera etapa al nivel del shock en la variante por nacionalidad</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>F5_P1_H2_beta</t>
+          <t>F5_P1_F_SHOCK</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>0.282</v>
+        <v>6.6</v>
       </c>
       <c r="C296" s="2" t="n"/>
       <c r="D296" s="2" t="n"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -21016,11 +21155,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H296" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -21033,34 +21167,34 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>P1-H2: asociación con tasa_paro (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>F de primera etapa al nivel del shock (BHJ), especificación principal de P1 (umbral pre-registrado: 10)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>F5_P1_H2_p</t>
+          <t>F5_P1_F_SIN_TOP3</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
-        <v>0.388</v>
+        <v>0.21</v>
       </c>
       <c r="C297" s="2" t="n"/>
       <c r="D297" s="2" t="n"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -21080,31 +21214,35 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón (INE)</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>P1-H2: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>F de primera etapa al nivel del shock al excluir los tres orígenes de mayor peso de Rotemberg (prueba no informativa si es &lt; 10)</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>F5_P2_E1_beta</t>
+          <t>F5_P1_H1_MULT_MED</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="C298" s="2" t="n"/>
-      <c r="D298" s="2" t="n"/>
+        <v>-0.416</v>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>-0.652</v>
+      </c>
+      <c r="D298" s="2" t="n">
+        <v>-0.174</v>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -21127,7 +21265,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -21142,24 +21280,24 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>P2-E1: asociación con cuota_nomanual (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-H1: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>F5_P2_E1_p</t>
+          <t>F5_P1_H1_MULT_NEG</t>
         </is>
       </c>
       <c r="B299" s="2" t="n">
-        <v>0.985</v>
+        <v>32</v>
       </c>
       <c r="C299" s="2" t="n"/>
       <c r="D299" s="2" t="n"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -21174,7 +21312,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -21189,24 +21327,24 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>P2-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-H1: especificaciones del multiverso con β negativo (de 32)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>F5_P2_E2_beta</t>
+          <t>F5_P1_H1_MULT_RECHAZA</t>
         </is>
       </c>
       <c r="B300" s="2" t="n">
-        <v>0.499</v>
+        <v>0</v>
       </c>
       <c r="C300" s="2" t="n"/>
       <c r="D300" s="2" t="n"/>
       <c r="E300" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -21214,11 +21352,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H300" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -21226,7 +21359,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -21241,24 +21374,28 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>P2-E2: asociación con cuota_alta_cualif (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-H1: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>F5_P2_E2_p</t>
+          <t>F5_P1_H1_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B301" s="2" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="C301" s="2" t="n"/>
-      <c r="D301" s="2" t="n"/>
+        <v>-0.118</v>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>-0.622</v>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>0.677</v>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -21266,6 +21403,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H301" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -21288,28 +21430,24 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>P2-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
+          <t>P1-H1: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True)</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>F5_P3_EDUC_beta</t>
+          <t>F5_P1_H1_beta</t>
         </is>
       </c>
       <c r="B302" s="2" t="n">
-        <v>-0.169</v>
-      </c>
-      <c r="C302" s="2" t="n">
-        <v>-0.752</v>
-      </c>
-      <c r="D302" s="2" t="n">
-        <v>0.414</v>
-      </c>
+        <v>-0.228</v>
+      </c>
+      <c r="C302" s="2" t="n"/>
+      <c r="D302" s="2" t="n"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>alumnos por profesor por punto porcentual</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -21324,44 +21462,44 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2016-2022</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>17 CCAA</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>EDUCAbase, ECP y padrón</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>P3 (educación): asociación entre el aumento de la población nacida fuera de 5-19 años y la ratio de alumnos por profesor en centros públicos (MC2E por comunidad; F efectivo = 39.5; p wild bootstrap de la forma reducida = 0.58; IC orientativo por errores agrupados en 17 comunidades)</t>
+          <t>P1-H1: asociación con tasa_empleo (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>F5_P5_HET_centro_y_este</t>
+          <t>F5_P1_H1_p</t>
         </is>
       </c>
       <c r="B303" s="2" t="n">
-        <v>0.027</v>
+        <v>0.388</v>
       </c>
       <c r="C303" s="2" t="n"/>
       <c r="D303" s="2" t="n"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -21369,48 +21507,47 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>NUTS2, centro y este</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>P5, países centro y este: β leave-one-country-out (28 regiones; p wild bootstrap = 0.94)</t>
+          <t>P1-H1: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>F5_P5_HET_continentales</t>
+          <t>F5_P1_H2_MULT_MED</t>
         </is>
       </c>
       <c r="B304" s="2" t="n">
-        <v>-0.163</v>
-      </c>
-      <c r="C304" s="2" t="n"/>
-      <c r="D304" s="2" t="n"/>
+        <v>0.314</v>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D304" s="2" t="n">
+        <v>0.6</v>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -21428,44 +21565,44 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>NUTS2, continentales</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>P5, países continentales: β leave-one-country-out (93 regiones; p wild bootstrap = 0.80)</t>
+          <t>P1-H2: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>F5_P5_HET_mediterráneos</t>
+          <t>F5_P1_H2_MULT_NEG</t>
         </is>
       </c>
       <c r="B305" s="2" t="n">
-        <v>-0.501</v>
+        <v>0</v>
       </c>
       <c r="C305" s="2" t="n"/>
       <c r="D305" s="2" t="n"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -21473,51 +21610,46 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>NUTS2, mediterráneos</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>P5, países mediterráneos: β leave-one-country-out (57 regiones; p wild bootstrap = 0.31)</t>
+          <t>P1-H2: especificaciones del multiverso con β negativo (de 32)</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>F5_P5_HET_nórdicos</t>
+          <t>F5_P1_H2_MULT_RECHAZA</t>
         </is>
       </c>
       <c r="B306" s="2" t="n">
-        <v>-0.904</v>
+        <v>3</v>
       </c>
       <c r="C306" s="2" t="n"/>
       <c r="D306" s="2" t="n"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -21525,51 +21657,46 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>NUTS2, nórdicos</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>P5, países nórdicos: β leave-one-country-out (17 regiones; p wild bootstrap = 0.33)</t>
+          <t>P1-H2: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>F5_P5_beta</t>
+          <t>F5_P1_H2_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B307" s="2" t="n">
-        <v>-0.325</v>
+        <v>0.181</v>
       </c>
       <c r="C307" s="2" t="n">
-        <v>-0.968</v>
+        <v>-0.733</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>0.318</v>
+        <v>1.227</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -21588,44 +21715,44 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>NUTS2 UE-27</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Eurostat (censo 2021, migr_imm3ctb, EU-LFS)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>P5: asociación entre la llegada de población nacida fuera y la tasa de empleo de los nativos, NUTS2 de la UE-27, 2021-2024 (MC2E leave-one-country-out; p wild bootstrap por país = 0.38; IC orientativo por errores agrupados por país)</t>
+          <t>P1-H2: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 11.1; IC: conjunto AKM0, acotado = True)</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
+          <t>F5_P1_H2_beta</t>
         </is>
       </c>
       <c r="B308" s="2" t="n">
-        <v>1.02</v>
+        <v>0.282</v>
       </c>
       <c r="C308" s="2" t="n"/>
       <c r="D308" s="2" t="n"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -21633,46 +21760,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>P1-H2: asociación con tasa_paro (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
+          <t>F5_P1_H2_p</t>
         </is>
       </c>
       <c r="B309" s="2" t="n">
-        <v>0.84</v>
+        <v>0.388</v>
       </c>
       <c r="C309" s="2" t="n"/>
       <c r="D309" s="2" t="n"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -21682,44 +21814,44 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P1-H2: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
+          <t>F5_P2_E1_beta</t>
         </is>
       </c>
       <c r="B310" s="2" t="n">
-        <v>0.96</v>
+        <v>0.025</v>
       </c>
       <c r="C310" s="2" t="n"/>
       <c r="D310" s="2" t="n"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -21727,46 +21859,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P2-E1: asociación con cuota_nomanual (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_15_34</t>
+          <t>F5_P2_E1_p</t>
         </is>
       </c>
       <c r="B311" s="2" t="n">
-        <v>0.9</v>
+        <v>0.985</v>
       </c>
       <c r="C311" s="2" t="n"/>
       <c r="D311" s="2" t="n"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -21776,44 +21913,44 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>P2-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_35_54</t>
+          <t>F5_P2_E2_beta</t>
         </is>
       </c>
       <c r="B312" s="2" t="n">
-        <v>0.89</v>
+        <v>0.499</v>
       </c>
       <c r="C312" s="2" t="n"/>
       <c r="D312" s="2" t="n"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -21821,46 +21958,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P2-E2: asociación con cuota_alta_cualif (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_55_74</t>
+          <t>F5_P2_E2_p</t>
         </is>
       </c>
       <c r="B313" s="2" t="n">
-        <v>0.85</v>
+        <v>0.306</v>
       </c>
       <c r="C313" s="2" t="n"/>
       <c r="D313" s="2" t="n"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -21870,44 +22012,48 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P2-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño (primera etapa débil al nivel del shock)</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_15_34</t>
+          <t>F5_P3_EDUC_beta</t>
         </is>
       </c>
       <c r="B314" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C314" s="2" t="n"/>
-      <c r="D314" s="2" t="n"/>
+        <v>-0.169</v>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>-0.752</v>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>0.414</v>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>alumnos por profesor por punto porcentual</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -21915,46 +22061,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016-2022</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>17 CCAA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>EDUCAbase, ECP y padrón</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>P3 (educación): asociación entre el aumento de la población nacida fuera de 5-19 años y la ratio de alumnos por profesor en centros públicos (MC2E por comunidad; F efectivo = 39.5; p wild bootstrap de la forma reducida = 0.58; IC orientativo por errores agrupados en 17 comunidades)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_35_54</t>
+          <t>F5_P5_HET_centro_y_este</t>
         </is>
       </c>
       <c r="B315" s="2" t="n">
-        <v>0.82</v>
+        <v>0.027</v>
       </c>
       <c r="C315" s="2" t="n"/>
       <c r="D315" s="2" t="n"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -21962,46 +22113,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2, centro y este</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P5, países centro y este: β leave-one-country-out (28 regiones; p wild bootstrap = 0.94)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_55_74</t>
+          <t>F5_P5_HET_continentales</t>
         </is>
       </c>
       <c r="B316" s="2" t="n">
-        <v>2.58</v>
+        <v>-0.163</v>
       </c>
       <c r="C316" s="2" t="n"/>
       <c r="D316" s="2" t="n"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -22009,46 +22165,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2, continentales</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P5, países continentales: β leave-one-country-out (93 regiones; p wild bootstrap = 0.80)</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_15_34</t>
+          <t>F5_P5_HET_mediterráneos</t>
         </is>
       </c>
       <c r="B317" s="2" t="n">
-        <v>0.9</v>
+        <v>-0.501</v>
       </c>
       <c r="C317" s="2" t="n"/>
       <c r="D317" s="2" t="n"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -22056,46 +22217,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2, mediterráneos</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>P5, países mediterráneos: β leave-one-country-out (57 regiones; p wild bootstrap = 0.31)</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_35_54</t>
+          <t>F5_P5_HET_nórdicos</t>
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>1.16</v>
+        <v>-0.904</v>
       </c>
       <c r="C318" s="2" t="n"/>
       <c r="D318" s="2" t="n"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -22103,46 +22269,55 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2, nórdicos</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P5, países nórdicos: β leave-one-country-out (17 regiones; p wild bootstrap = 0.33)</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_55_74</t>
+          <t>F5_P5_beta</t>
         </is>
       </c>
       <c r="B319" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C319" s="2" t="n"/>
-      <c r="D319" s="2" t="n"/>
+        <v>-0.325</v>
+      </c>
+      <c r="C319" s="2" t="n">
+        <v>-0.968</v>
+      </c>
+      <c r="D319" s="2" t="n">
+        <v>0.318</v>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -22150,56 +22325,61 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2 UE-27</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat (censo 2021, migr_imm3ctb, EU-LFS)</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P5: asociación entre la llegada de población nacida fuera y la tasa de empleo de los nativos, NUTS2 de la UE-27, 2021-2024 (MC2E leave-one-country-out; p wild bootstrap por país = 0.38; IC orientativo por errores agrupados por país)</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>F6_POB_CUOTA_FUERA_ECV</t>
+          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
         </is>
       </c>
       <c r="B320" s="2" t="n">
-        <v>18.5</v>
+        <v>1.02</v>
       </c>
       <c r="C320" s="2" t="n"/>
       <c r="D320" s="2" t="n"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>% de la población</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -22214,39 +22394,39 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>ECV (INE)</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_España</t>
+          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
         </is>
       </c>
       <c r="B321" s="2" t="n">
-        <v>6252</v>
+        <v>0.84</v>
       </c>
       <c r="C321" s="2" t="n"/>
       <c r="D321" s="2" t="n"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -22256,44 +22436,44 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>nacidos fuera</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
+          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
         </is>
       </c>
       <c r="B322" s="2" t="n">
-        <v>2813</v>
+        <v>0.96</v>
       </c>
       <c r="C322" s="2" t="n"/>
       <c r="D322" s="2" t="n"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -22303,44 +22483,44 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>nacidos fuera</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+          <t>F6_ENSE_RAZON_FAR_15_34</t>
         </is>
       </c>
       <c r="B323" s="2" t="n">
-        <v>1927</v>
+        <v>0.9</v>
       </c>
       <c r="C323" s="2" t="n"/>
       <c r="D323" s="2" t="n"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -22350,44 +22530,44 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>nacidos fuera</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+          <t>F6_ENSE_RAZON_FAR_35_54</t>
         </is>
       </c>
       <c r="B324" s="2" t="n">
-        <v>2.5</v>
+        <v>0.89</v>
       </c>
       <c r="C324" s="2" t="n"/>
       <c r="D324" s="2" t="n"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>% de las prestaciones monetarias</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -22397,62 +22577,626 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos fuera</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>F6_TRABAJO_CUOTA_FUERA</t>
+          <t>F6_ENSE_RAZON_FAR_55_74</t>
         </is>
       </c>
       <c r="B325" s="2" t="n">
-        <v>15.5</v>
+        <v>0.85</v>
       </c>
       <c r="C325" s="2" t="n"/>
       <c r="D325" s="2" t="n"/>
       <c r="E325" t="inlineStr">
         <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_15_34</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C326" s="2" t="n"/>
+      <c r="D326" s="2" t="n"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_35_54</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C327" s="2" t="n"/>
+      <c r="D327" s="2" t="n"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_HOSP_55_74</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C328" s="2" t="n"/>
+      <c r="D328" s="2" t="n"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_15_34</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C329" s="2" t="n"/>
+      <c r="D329" s="2" t="n"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_35_54</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C330" s="2" t="n"/>
+      <c r="D330" s="2" t="n"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>F6_ENSE_RAZON_URG_55_74</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C331" s="2" t="n"/>
+      <c r="D331" s="2" t="n"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>razón (nativos = 1)</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>ENSE 2017 (INE)</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>F6_POB_CUOTA_FUERA_ECV</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C332" s="2" t="n"/>
+      <c r="D332" s="2" t="n"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>% de la población</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>nacidos fuera</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>ECV (INE)</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_España</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="n">
+        <v>6252</v>
+      </c>
+      <c r="C333" s="2" t="n"/>
+      <c r="D333" s="2" t="n"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="n">
+        <v>2813</v>
+      </c>
+      <c r="C334" s="2" t="n"/>
+      <c r="D334" s="2" t="n"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Resto UE</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C335" s="2" t="n"/>
+      <c r="D335" s="2" t="n"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Resto del mundo</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C336" s="2" t="n"/>
+      <c r="D336" s="2" t="n"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>% de las prestaciones monetarias</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>F6_TRABAJO_CUOTA_FUERA</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C337" s="2" t="n"/>
+      <c r="D337" s="2" t="n"/>
+      <c r="E337" t="inlineStr">
+        <is>
           <t>% del total</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
+      <c r="F337" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
+      <c r="H337" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr">
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
         <is>
           <t>nacidos fuera</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="K337" t="inlineStr">
         <is>
           <t>ECV (INE) y Eurostat</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="L337" t="inlineStr">
         <is>
           <t>Cuota de los nacidos fuera en IRPF del trabajo y cotizaciones sociales (calibradas a las cuentas de las AAPP)</t>
         </is>

--- a/output/f7/tablas_m1.xlsx
+++ b/output/f7/tablas_m1.xlsx
@@ -5760,229 +5760,229 @@
     </comment>
     <comment ref="B340" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C340" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D340" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B341" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C341" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D341" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B342" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="C342" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="D342" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
+      </text>
+    </comment>
+    <comment ref="B343" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C340" authorId="0" shapeId="0">
+    <comment ref="C343" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D340" authorId="0" shapeId="0">
+    <comment ref="D343" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B341" authorId="0" shapeId="0">
+    <comment ref="B344" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C341" authorId="0" shapeId="0">
+    <comment ref="C344" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D341" authorId="0" shapeId="0">
+    <comment ref="D344" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B342" authorId="0" shapeId="0">
+    <comment ref="B345" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C342" authorId="0" shapeId="0">
+    <comment ref="C345" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D342" authorId="0" shapeId="0">
+    <comment ref="D345" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B343" authorId="0" shapeId="0">
+    <comment ref="B346" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C343" authorId="0" shapeId="0">
+    <comment ref="C346" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D343" authorId="0" shapeId="0">
+    <comment ref="D346" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B344" authorId="0" shapeId="0">
+    <comment ref="B347" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C344" authorId="0" shapeId="0">
+    <comment ref="C347" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D344" authorId="0" shapeId="0">
+    <comment ref="D347" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B345" authorId="0" shapeId="0">
+    <comment ref="B348" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C345" authorId="0" shapeId="0">
+    <comment ref="C348" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D345" authorId="0" shapeId="0">
+    <comment ref="D348" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B346" authorId="0" shapeId="0">
+    <comment ref="B349" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C346" authorId="0" shapeId="0">
+    <comment ref="C349" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D346" authorId="0" shapeId="0">
+    <comment ref="D349" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B347" authorId="0" shapeId="0">
+    <comment ref="B350" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C347" authorId="0" shapeId="0">
+    <comment ref="C350" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D347" authorId="0" shapeId="0">
+    <comment ref="D350" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B348" authorId="0" shapeId="0">
+    <comment ref="B351" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="C348" authorId="0" shapeId="0">
+    <comment ref="C351" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="D348" authorId="0" shapeId="0">
+    <comment ref="D351" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_jackknife.py)</t>
       </text>
     </comment>
-    <comment ref="B349" authorId="0" shapeId="0">
+    <comment ref="B352" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
       </text>
     </comment>
-    <comment ref="C349" authorId="0" shapeId="0">
+    <comment ref="C352" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
       </text>
     </comment>
-    <comment ref="D349" authorId="0" shapeId="0">
+    <comment ref="D352" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
       </text>
     </comment>
-    <comment ref="B350" authorId="0" shapeId="0">
+    <comment ref="B353" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
       </text>
     </comment>
-    <comment ref="C350" authorId="0" shapeId="0">
+    <comment ref="C353" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
       </text>
     </comment>
-    <comment ref="D350" authorId="0" shapeId="0">
+    <comment ref="D353" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EPA (INE) (src/m1/f5_x_e3a_lectura.py)</t>
       </text>
     </comment>
-    <comment ref="B351" authorId="0" shapeId="0">
+    <comment ref="B354" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C351" authorId="0" shapeId="0">
+    <comment ref="C354" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D351" authorId="0" shapeId="0">
+    <comment ref="D354" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B352" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C352" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D352" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B353" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C353" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D353" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B354" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C354" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D354" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
     <comment ref="B355" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
@@ -6825,64 +6825,64 @@
     </comment>
     <comment ref="B411" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C411" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D411" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B412" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C412" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D412" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B413" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C413" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D413" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B414" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="C411" authorId="0" shapeId="0">
+    <comment ref="C414" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="D411" authorId="0" shapeId="0">
+    <comment ref="D414" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EES y EPA (INE) (src/m1/f5_p1e4_borjas.py)</t>
       </text>
     </comment>
-    <comment ref="B412" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C412" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D412" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B413" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C413" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D413" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B414" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C414" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D414" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
     <comment ref="B415" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
@@ -6975,139 +6975,139 @@
     </comment>
     <comment ref="B421" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C421" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D421" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B422" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C422" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D422" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B423" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C423" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D423" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B424" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C421" authorId="0" shapeId="0">
+    <comment ref="C424" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D421" authorId="0" shapeId="0">
+    <comment ref="D424" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B422" authorId="0" shapeId="0">
+    <comment ref="B425" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C422" authorId="0" shapeId="0">
+    <comment ref="C425" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D422" authorId="0" shapeId="0">
+    <comment ref="D425" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B423" authorId="0" shapeId="0">
+    <comment ref="B426" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C423" authorId="0" shapeId="0">
+    <comment ref="C426" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D423" authorId="0" shapeId="0">
+    <comment ref="D426" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B424" authorId="0" shapeId="0">
+    <comment ref="B427" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C424" authorId="0" shapeId="0">
+    <comment ref="C427" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D424" authorId="0" shapeId="0">
+    <comment ref="D427" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B425" authorId="0" shapeId="0">
+    <comment ref="B428" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C425" authorId="0" shapeId="0">
+    <comment ref="C428" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D425" authorId="0" shapeId="0">
+    <comment ref="D428" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B426" authorId="0" shapeId="0">
+    <comment ref="B429" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C426" authorId="0" shapeId="0">
+    <comment ref="C429" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D426" authorId="0" shapeId="0">
+    <comment ref="D429" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B427" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C427" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D427" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B428" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C428" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D428" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B429" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C429" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D429" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
     <comment ref="B430" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
@@ -7725,79 +7725,79 @@
     </comment>
     <comment ref="B471" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C471" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D471" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B472" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C472" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D472" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B473" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C473" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D473" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B474" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C471" authorId="0" shapeId="0">
+    <comment ref="C474" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D471" authorId="0" shapeId="0">
+    <comment ref="D474" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón (INE) (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B472" authorId="0" shapeId="0">
+    <comment ref="B475" authorId="0" shapeId="0">
       <text>
         <t>Fuente: TGSS y padrón (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="C472" authorId="0" shapeId="0">
+    <comment ref="C475" authorId="0" shapeId="0">
       <text>
         <t>Fuente: TGSS y padrón (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="D472" authorId="0" shapeId="0">
+    <comment ref="D475" authorId="0" shapeId="0">
       <text>
         <t>Fuente: TGSS y padrón (src/m1/f5_p1_shiftshare.py)</t>
       </text>
     </comment>
-    <comment ref="B473" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C473" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D473" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B474" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C474" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D474" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="B475" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="C475" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
-    <comment ref="D475" authorId="0" shapeId="0">
-      <text>
-        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
-      </text>
-    </comment>
     <comment ref="B476" authorId="0" shapeId="0">
       <text>
         <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
@@ -8115,360 +8115,405 @@
     </comment>
     <comment ref="B497" authorId="0" shapeId="0">
       <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C497" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D497" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B498" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C498" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D498" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B499" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="C499" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="D499" authorId="0" shapeId="0">
+      <text>
+        <t>Fuente: padrón, ECP, EPA (INE) (src/m1/f5_p1_shiftshare.py)</t>
+      </text>
+    </comment>
+    <comment ref="B500" authorId="0" shapeId="0">
+      <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="C497" authorId="0" shapeId="0">
+    <comment ref="C500" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="D497" authorId="0" shapeId="0">
+    <comment ref="D500" authorId="0" shapeId="0">
       <text>
         <t>Fuente: EDUCAbase, ECP y padrón (src/m1/f5_p3_servicios.py)</t>
       </text>
     </comment>
-    <comment ref="B498" authorId="0" shapeId="0">
+    <comment ref="B501" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C498" authorId="0" shapeId="0">
+    <comment ref="C501" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D498" authorId="0" shapeId="0">
+    <comment ref="D501" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B499" authorId="0" shapeId="0">
+    <comment ref="B502" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C499" authorId="0" shapeId="0">
+    <comment ref="C502" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D499" authorId="0" shapeId="0">
+    <comment ref="D502" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B500" authorId="0" shapeId="0">
+    <comment ref="B503" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C500" authorId="0" shapeId="0">
+    <comment ref="C503" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D500" authorId="0" shapeId="0">
+    <comment ref="D503" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B501" authorId="0" shapeId="0">
+    <comment ref="B504" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C501" authorId="0" shapeId="0">
+    <comment ref="C504" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D501" authorId="0" shapeId="0">
+    <comment ref="D504" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B502" authorId="0" shapeId="0">
+    <comment ref="B505" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="C502" authorId="0" shapeId="0">
+    <comment ref="C505" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="D502" authorId="0" shapeId="0">
+    <comment ref="D505" authorId="0" shapeId="0">
       <text>
         <t>Fuente: Eurostat (censo 2021, migr_imm3ctb, EU-LFS) (src/m1/f5_p5_europa.py)</t>
       </text>
     </comment>
-    <comment ref="B503" authorId="0" shapeId="0">
+    <comment ref="B506" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C503" authorId="0" shapeId="0">
+    <comment ref="C506" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D503" authorId="0" shapeId="0">
+    <comment ref="D506" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B504" authorId="0" shapeId="0">
+    <comment ref="B507" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C504" authorId="0" shapeId="0">
+    <comment ref="C507" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D504" authorId="0" shapeId="0">
+    <comment ref="D507" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B505" authorId="0" shapeId="0">
+    <comment ref="B508" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C505" authorId="0" shapeId="0">
+    <comment ref="C508" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D505" authorId="0" shapeId="0">
+    <comment ref="D508" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B506" authorId="0" shapeId="0">
+    <comment ref="B509" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C506" authorId="0" shapeId="0">
+    <comment ref="C509" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D506" authorId="0" shapeId="0">
+    <comment ref="D509" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B507" authorId="0" shapeId="0">
+    <comment ref="B510" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C507" authorId="0" shapeId="0">
+    <comment ref="C510" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D507" authorId="0" shapeId="0">
+    <comment ref="D510" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B508" authorId="0" shapeId="0">
+    <comment ref="B511" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C508" authorId="0" shapeId="0">
+    <comment ref="C511" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D508" authorId="0" shapeId="0">
+    <comment ref="D511" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B509" authorId="0" shapeId="0">
+    <comment ref="B512" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C509" authorId="0" shapeId="0">
+    <comment ref="C512" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D509" authorId="0" shapeId="0">
+    <comment ref="D512" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B510" authorId="0" shapeId="0">
+    <comment ref="B513" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C510" authorId="0" shapeId="0">
+    <comment ref="C513" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D510" authorId="0" shapeId="0">
+    <comment ref="D513" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B511" authorId="0" shapeId="0">
+    <comment ref="B514" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C511" authorId="0" shapeId="0">
+    <comment ref="C514" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D511" authorId="0" shapeId="0">
+    <comment ref="D514" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B512" authorId="0" shapeId="0">
+    <comment ref="B515" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C512" authorId="0" shapeId="0">
+    <comment ref="C515" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D512" authorId="0" shapeId="0">
+    <comment ref="D515" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B513" authorId="0" shapeId="0">
+    <comment ref="B516" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C513" authorId="0" shapeId="0">
+    <comment ref="C516" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D513" authorId="0" shapeId="0">
+    <comment ref="D516" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B514" authorId="0" shapeId="0">
+    <comment ref="B517" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C514" authorId="0" shapeId="0">
+    <comment ref="C517" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D514" authorId="0" shapeId="0">
+    <comment ref="D517" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ENSE 2017 (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B515" authorId="0" shapeId="0">
+    <comment ref="B518" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C515" authorId="0" shapeId="0">
+    <comment ref="C518" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D515" authorId="0" shapeId="0">
+    <comment ref="D518" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B516" authorId="0" shapeId="0">
+    <comment ref="B519" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C516" authorId="0" shapeId="0">
+    <comment ref="C519" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D516" authorId="0" shapeId="0">
+    <comment ref="D519" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B517" authorId="0" shapeId="0">
+    <comment ref="B520" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C517" authorId="0" shapeId="0">
+    <comment ref="C520" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D517" authorId="0" shapeId="0">
+    <comment ref="D520" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B518" authorId="0" shapeId="0">
+    <comment ref="B521" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C518" authorId="0" shapeId="0">
+    <comment ref="C521" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D518" authorId="0" shapeId="0">
+    <comment ref="D521" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B519" authorId="0" shapeId="0">
+    <comment ref="B522" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C519" authorId="0" shapeId="0">
+    <comment ref="C522" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D519" authorId="0" shapeId="0">
+    <comment ref="D522" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat COFOG (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="B520" authorId="0" shapeId="0">
+    <comment ref="B523" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="C520" authorId="0" shapeId="0">
+    <comment ref="C523" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
     </comment>
-    <comment ref="D520" authorId="0" shapeId="0">
+    <comment ref="D523" authorId="0" shapeId="0">
       <text>
         <t>Fuente: ECV (INE) y Eurostat (src/m1/f6_afirmaciones.py)</t>
       </text>
@@ -9578,7 +9623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L520"/>
+  <dimension ref="A1:L523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -18470,7 +18515,7 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="C184" s="2" t="n"/>
       <c r="D184" s="2" t="n"/>
@@ -18506,7 +18551,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Cobertura de las celdas de edad y sexo con ≥ 50 observaciones de los nacidos en Resto UE</t>
+          <t>Peso nativo de las celdas edad × sexo con ≥ 10 observaciones de los nacidos en Resto UE (el resto usa la media del tramo de edad)</t>
         </is>
       </c>
     </row>
@@ -18517,7 +18562,7 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C185" s="2" t="n"/>
       <c r="D185" s="2" t="n"/>
@@ -18553,7 +18598,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Cobertura de las celdas de edad y sexo con ≥ 50 observaciones de los nacidos en Resto del mundo</t>
+          <t>Peso nativo de las celdas edad × sexo con ≥ 10 observaciones de los nacidos en Resto del mundo (el resto usa la media del tramo de edad)</t>
         </is>
       </c>
     </row>
@@ -18917,13 +18962,13 @@
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>-3295</v>
+        <v>737</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>-4704</v>
+        <v>-210</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>-1887</v>
+        <v>1683</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -18968,13 +19013,13 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>-2809</v>
+        <v>-1627</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>-3405</v>
+        <v>-2055</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>-2213</v>
+        <v>-1200</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -19019,7 +19064,7 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C195" s="2" t="n"/>
       <c r="D195" s="2" t="n"/>
@@ -19066,7 +19111,7 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C196" s="2" t="n"/>
       <c r="D196" s="2" t="n"/>
@@ -19113,13 +19158,13 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>-3295</v>
+        <v>737</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>-3905</v>
+        <v>415</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>-358</v>
+        <v>3481</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -19153,7 +19198,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Diferencia con los nacidos en España a igual edad y sexo, nacidos en Resto UE, sobre las celdas de edad y sexo con ≥ 50 observaciones del grupo (42 % del peso nativo); positiva en 0 de 64 combinaciones</t>
+          <t>Diferencia con los nacidos en España a igual edad y sexo (todas las edades), nacidos en Resto UE; positiva en 64 de 64 combinaciones</t>
         </is>
       </c>
     </row>
@@ -19164,13 +19209,13 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>-2809</v>
+        <v>-1627</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>-3257</v>
+        <v>-1860</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>602</v>
+        <v>1737</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -19204,7 +19249,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Diferencia con los nacidos en España a igual edad y sexo, nacidos en Resto del mundo, sobre las celdas de edad y sexo con ≥ 50 observaciones del grupo (87 % del peso nativo); positiva en 12 de 64 combinaciones</t>
+          <t>Diferencia con los nacidos en España a igual edad y sexo (todas las edades), nacidos en Resto del mundo; positiva en 32 de 64 combinaciones</t>
         </is>
       </c>
     </row>
@@ -19215,13 +19260,13 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>5957</v>
+        <v>-631</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>1656</v>
+        <v>-888</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>8718</v>
+        <v>1899</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -19255,7 +19300,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Contribución neta por persona de los nacidos en Resto UE con la estructura por edad y sexo de los nacidos en España (nivel «edad y sexo»; cobertura de celdas con ≥ 50 observaciones = 42 % del peso nativo; intervalo: 64 combinaciones)</t>
+          <t>Contribución neta por persona de los nacidos en Resto UE con la estructura por edad y sexo de los nacidos en España (nivel «edad y sexo»; peso nativo de celdas edad × sexo con ≥ 10 observaciones del grupo = 100 %, el resto con la media del tramo de edad; intervalo: 64 combinaciones)</t>
         </is>
       </c>
     </row>
@@ -19266,13 +19311,13 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>-1902</v>
+        <v>-2994</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>-2196</v>
+        <v>-3096</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>1079</v>
+        <v>107</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -19306,7 +19351,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Contribución neta por persona de los nacidos en Resto del mundo con la estructura por edad y sexo de los nacidos en España (nivel «edad y sexo»; cobertura de celdas con ≥ 50 observaciones = 87 % del peso nativo; intervalo: 64 combinaciones)</t>
+          <t>Contribución neta por persona de los nacidos en Resto del mundo con la estructura por edad y sexo de los nacidos en España (nivel «edad y sexo»; peso nativo de celdas edad × sexo con ≥ 10 observaciones del grupo = 100 %, el resto con la media del tramo de edad; intervalo: 64 combinaciones)</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21204,7 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>-938</v>
+        <v>-3312</v>
       </c>
       <c r="C239" s="2" t="n"/>
       <c r="D239" s="2" t="n"/>
@@ -21195,7 +21240,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona de los nacidos en Resto UE menos las de los nacidos en España a igual edad y sexo, sobre las celdas comunes (42 % del peso nativo)</t>
+          <t>Prestaciones monetarias por persona de los nacidos en Resto UE menos las de los nacidos en España a igual edad y sexo (todas las edades)</t>
         </is>
       </c>
     </row>
@@ -21206,7 +21251,7 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>-2741</v>
+        <v>-3637</v>
       </c>
       <c r="C240" s="2" t="n"/>
       <c r="D240" s="2" t="n"/>
@@ -21242,7 +21287,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona de los nacidos en Resto del mundo menos las de los nacidos en España a igual edad y sexo, sobre las celdas comunes (87 % del peso nativo)</t>
+          <t>Prestaciones monetarias por persona de los nacidos en Resto del mundo menos las de los nacidos en España a igual edad y sexo (todas las edades)</t>
         </is>
       </c>
     </row>
@@ -25505,17 +25550,21 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>F5X_E3a_ESTEDAD_p</t>
+          <t>F5X_E3a_ESTEDAD_NAC</t>
         </is>
       </c>
       <c r="B328" s="2" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="C328" s="2" t="n"/>
-      <c r="D328" s="2" t="n"/>
+        <v>-0.22</v>
+      </c>
+      <c r="C328" s="2" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="D328" s="2" t="n">
+        <v>0.04</v>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -25523,6 +25572,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H328" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -25545,24 +25599,24 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>p AKM0 sin ajustar: tasa de empleo de los nativos con educación baja estandarizada por edad (pesos de 2005) (exploratorio, a posteriori)</t>
+          <t>Tasa estandarizada por edad, variante por nacionalidad (IC: envolvente del conjunto AKM0; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>F5X_E3a_MCO</t>
+          <t>F5X_E3a_ESTEDAD_PERM_p</t>
         </is>
       </c>
       <c r="B329" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.116</v>
       </c>
       <c r="C329" s="2" t="n"/>
       <c r="D329" s="2" t="n"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -25570,11 +25624,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H329" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -25597,24 +25646,24 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>P1-E3a por MCO con la especificación principal (exploratorio, a posteriori)</t>
+          <t>Tasa estandarizada por edad: p de permutación recentrado (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>F5X_E3a_OCU</t>
+          <t>F5X_E3a_ESTEDAD_WCB_p</t>
         </is>
       </c>
       <c r="B330" s="2" t="n">
-        <v>-1.86</v>
+        <v>0.604</v>
       </c>
       <c r="C330" s="2" t="n"/>
       <c r="D330" s="2" t="n"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>log por pp</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -25622,11 +25671,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H330" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -25649,18 +25693,18 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>Δ log ocupados nacidos en España con educación baja por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.40)</t>
+          <t>Tasa estandarizada por edad: p del wild bootstrap por comunidad (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>F5X_E3a_OCU_p</t>
+          <t>F5X_E3a_ESTEDAD_p</t>
         </is>
       </c>
       <c r="B331" s="2" t="n">
-        <v>0.395</v>
+        <v>0.278</v>
       </c>
       <c r="C331" s="2" t="n"/>
       <c r="D331" s="2" t="n"/>
@@ -25696,24 +25740,24 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>p AKM0 sin ajustar de Δ log ocupados nacidos en España con educación baja (exploratorio, a posteriori)</t>
+          <t>p AKM0 sin ajustar: tasa de empleo de los nativos con educación baja estandarizada por edad (pesos de 2005) (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>F5X_E3a_POB</t>
+          <t>F5X_E3a_MCO</t>
         </is>
       </c>
       <c r="B332" s="2" t="n">
-        <v>-1.07</v>
+        <v>-0.16</v>
       </c>
       <c r="C332" s="2" t="n"/>
       <c r="D332" s="2" t="n"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>log por pp</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -25748,18 +25792,18 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>Δ log población nacida en España de 16-64 con educación baja (EPA) por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.57)</t>
+          <t>P1-E3a por MCO con la especificación principal (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>F5X_E3a_POB_MA</t>
+          <t>F5X_E3a_OCU</t>
         </is>
       </c>
       <c r="B333" s="2" t="n">
-        <v>0.93</v>
+        <v>-1.86</v>
       </c>
       <c r="C333" s="2" t="n"/>
       <c r="D333" s="2" t="n"/>
@@ -25790,7 +25834,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>nacidos en España con educación media o alta</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -25800,18 +25844,18 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>Δ log población nacida en España de 16-64 con educación media o alta (EPA) por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.31)</t>
+          <t>Δ log ocupados nacidos en España con educación baja por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.40)</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>F5X_E3a_POB_MA_p</t>
+          <t>F5X_E3a_OCU_p</t>
         </is>
       </c>
       <c r="B334" s="2" t="n">
-        <v>0.314</v>
+        <v>0.395</v>
       </c>
       <c r="C334" s="2" t="n"/>
       <c r="D334" s="2" t="n"/>
@@ -25837,7 +25881,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>nacidos en España con educación media o alta</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -25847,24 +25891,24 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>p AKM0 sin ajustar de Δ log población nacida en España de 16-64 con educación media o alta (EPA) (exploratorio, a posteriori)</t>
+          <t>p AKM0 sin ajustar de Δ log ocupados nacidos en España con educación baja (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>F5X_E3a_POB_p</t>
+          <t>F5X_E3a_POB</t>
         </is>
       </c>
       <c r="B335" s="2" t="n">
-        <v>0.5659999999999999</v>
+        <v>-1.07</v>
       </c>
       <c r="C335" s="2" t="n"/>
       <c r="D335" s="2" t="n"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>log por pp</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -25872,6 +25916,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H335" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -25894,24 +25943,24 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>p AKM0 sin ajustar de Δ log población nacida en España de 16-64 con educación baja (EPA) (exploratorio, a posteriori)</t>
+          <t>Δ log población nacida en España de 16-64 con educación baja (EPA) por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.57)</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>F5X_E3a_SINSG</t>
+          <t>F5X_E3a_POB_MA</t>
         </is>
       </c>
       <c r="B336" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.93</v>
       </c>
       <c r="C336" s="2" t="n"/>
       <c r="D336" s="2" t="n"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>log por pp</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -25936,7 +25985,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>nacidos en España con educación baja</t>
+          <t>nacidos en España con educación media o alta</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -25946,18 +25995,18 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>tasa de empleo de los nativos con educación baja sin la segunda generación identificable, MC2E con la especificación principal (exploratorio, a posteriori)</t>
+          <t>Δ log población nacida en España de 16-64 con educación media o alta (EPA) por punto de tratamiento, MC2E (exploratorio, a posteriori; p AKM0 sin ajustar = 0.31)</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>F5X_E3a_SINSG_p</t>
+          <t>F5X_E3a_POB_MA_p</t>
         </is>
       </c>
       <c r="B337" s="2" t="n">
-        <v>0.041</v>
+        <v>0.314</v>
       </c>
       <c r="C337" s="2" t="n"/>
       <c r="D337" s="2" t="n"/>
@@ -25983,7 +26032,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>nacidos en España con educación baja</t>
+          <t>nacidos en España con educación media o alta</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -25993,24 +26042,24 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>p AKM0 sin ajustar: tasa de empleo de los nativos con educación baja sin la segunda generación identificable (exploratorio, a posteriori)</t>
+          <t>p AKM0 sin ajustar de Δ log población nacida en España de 16-64 con educación media o alta (EPA) (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>F5X_E3b_NAC</t>
+          <t>F5X_E3a_POB_p</t>
         </is>
       </c>
       <c r="B338" s="2" t="n">
-        <v>0.19</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C338" s="2" t="n"/>
       <c r="D338" s="2" t="n"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -26018,11 +26067,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H338" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26035,7 +26079,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>nacidos en España con educación media</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -26045,18 +26089,18 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>P1-E3b (educación media), variante por nacionalidad (exploratorio, a posteriori)</t>
+          <t>p AKM0 sin ajustar de Δ log población nacida en España de 16-64 con educación baja (EPA) (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>F5X_E3c_NAC</t>
+          <t>F5X_E3a_SINSG</t>
         </is>
       </c>
       <c r="B339" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.51</v>
       </c>
       <c r="C339" s="2" t="n"/>
       <c r="D339" s="2" t="n"/>
@@ -26087,7 +26131,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>nacidos en España con educación alta</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -26097,24 +26141,24 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>P1-E3c (educación alta), variante por nacionalidad (exploratorio, a posteriori)</t>
+          <t>tasa de empleo de los nativos con educación baja sin la segunda generación identificable, MC2E con la especificación principal (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>F5X_JK_E3a_MAX</t>
+          <t>F5X_E3a_SINSG_p</t>
         </is>
       </c>
       <c r="B340" s="2" t="n">
-        <v>-0.19</v>
+        <v>0.041</v>
       </c>
       <c r="C340" s="2" t="n"/>
       <c r="D340" s="2" t="n"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -26122,11 +26166,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H340" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26134,7 +26173,7 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
@@ -26149,25 +26188,21 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>P1-E3a al excluir la comunidad cuya exclusión más lo acerca a cero: Comunitat Valenciana (p AKM0 sin ajustar = 0.28; exploratorio, a posteriori)</t>
+          <t>p AKM0 sin ajustar: tasa de empleo de los nativos con educación baja sin la segunda generación identificable (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_E3a</t>
+          <t>F5X_E3b_NAC</t>
         </is>
       </c>
       <c r="B341" s="2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="C341" s="2" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="D341" s="2" t="n">
-        <v>-0.19</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="C341" s="2" t="n"/>
+      <c r="D341" s="2" t="n"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -26190,12 +26225,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación media</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -26205,24 +26240,24 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>P1-E3a: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
+          <t>P1-E3b (educación media), variante por nacionalidad (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_E3a_RECHAZA</t>
+          <t>F5X_E3c_NAC</t>
         </is>
       </c>
       <c r="B342" s="2" t="n">
-        <v>11</v>
+        <v>0.06</v>
       </c>
       <c r="C342" s="2" t="n"/>
       <c r="D342" s="2" t="n"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -26230,6 +26265,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H342" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26237,12 +26277,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación alta</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -26252,25 +26292,21 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>P1-E3a: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
+          <t>P1-E3c (educación alta), variante por nacionalidad (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_E3c</t>
+          <t>F5X_JK_E3a_MAX</t>
         </is>
       </c>
       <c r="B343" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C343" s="2" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="D343" s="2" t="n">
-        <v>1.11</v>
-      </c>
+        <v>-0.19</v>
+      </c>
+      <c r="C343" s="2" t="n"/>
+      <c r="D343" s="2" t="n"/>
       <c r="E343" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -26298,7 +26334,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -26308,24 +26344,28 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>P1-E3c: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
+          <t>P1-E3a al excluir la comunidad cuya exclusión más lo acerca a cero: Comunitat Valenciana (p AKM0 sin ajustar = 0.28; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_E3c_RECHAZA</t>
+          <t>F5X_JK_P1_E3a</t>
         </is>
       </c>
       <c r="B344" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C344" s="2" t="n"/>
-      <c r="D344" s="2" t="n"/>
+        <v>-0.61</v>
+      </c>
+      <c r="C344" s="2" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="D344" s="2" t="n">
+        <v>-0.19</v>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -26333,6 +26373,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H344" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26355,28 +26400,24 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>P1-E3c: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
+          <t>P1-E3a: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_H1</t>
+          <t>F5X_JK_P1_E3a_RECHAZA</t>
         </is>
       </c>
       <c r="B345" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C345" s="2" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="D345" s="2" t="n">
-        <v>0.49</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C345" s="2" t="n"/>
+      <c r="D345" s="2" t="n"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -26384,11 +26425,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H345" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26411,24 +26447,28 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>P1-H1: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
+          <t>P1-E3a: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_H1_RECHAZA</t>
+          <t>F5X_JK_P1_E3c</t>
         </is>
       </c>
       <c r="B346" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C346" s="2" t="n"/>
-      <c r="D346" s="2" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D346" s="2" t="n">
+        <v>1.11</v>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -26436,6 +26476,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H346" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26458,28 +26503,24 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>P1-H1: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
+          <t>P1-E3c: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_H2</t>
+          <t>F5X_JK_P1_E3c_RECHAZA</t>
         </is>
       </c>
       <c r="B347" s="2" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="C347" s="2" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="D347" s="2" t="n">
-        <v>-0.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C347" s="2" t="n"/>
+      <c r="D347" s="2" t="n"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -26487,11 +26528,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H347" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26514,24 +26550,28 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>P1-H2: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
+          <t>P1-E3c: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>F5X_JK_P1_H2_RECHAZA</t>
+          <t>F5X_JK_P1_H1</t>
         </is>
       </c>
       <c r="B348" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C348" s="2" t="n"/>
-      <c r="D348" s="2" t="n"/>
+        <v>0.06</v>
+      </c>
+      <c r="C348" s="2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="D348" s="2" t="n">
+        <v>0.49</v>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -26539,6 +26579,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H348" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26561,24 +26606,24 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>P1-H2: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
+          <t>P1-H1: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>F5X_NAC_IMPLICITO</t>
+          <t>F5X_JK_P1_H1_RECHAZA</t>
         </is>
       </c>
       <c r="B349" s="2" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="C349" s="2" t="n"/>
       <c r="D349" s="2" t="n"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -26586,11 +26631,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H349" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26598,7 +26638,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
@@ -26613,39 +26653,48 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>Media ponderada por educación de las estimaciones por nacionalidad de P1-E3a, E3b y E3c (exploratorio, a posteriori)</t>
+          <t>P1-H1: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>F5X_PESO_BAJA</t>
+          <t>F5X_JK_P1_H2</t>
         </is>
       </c>
       <c r="B350" s="2" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="C350" s="2" t="n"/>
-      <c r="D350" s="2" t="n"/>
+        <v>-0.57</v>
+      </c>
+      <c r="C350" s="2" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="D350" s="2" t="n">
+        <v>-0.11</v>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>% de los nativos de 16-64</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>2005, 2009, 2015</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -26655,29 +26704,29 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>EPA (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>Peso de la educación baja entre los nacidos en España de 16-64 (EPA, años iniciales de los periodos)</t>
+          <t>P1-H2: mediana de β al excluir una comunidad autónoma cada vez (17 exclusiones; intervalo: mínimo y máximo; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>F5_P1_APALANC_MAX</t>
+          <t>F5X_JK_P1_H2_RECHAZA</t>
         </is>
       </c>
       <c r="B351" s="2" t="n">
-        <v>42.2</v>
+        <v>0</v>
       </c>
       <c r="C351" s="2" t="n"/>
       <c r="D351" s="2" t="n"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>% de la variación del instrumento</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -26692,39 +26741,39 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>Mayor cuota de una comunidad autónoma (05) en la variación del instrumento residualizado (condición del wild bootstrap con 17 grupos, docs/montecarlo.md)</t>
+          <t>P1-H2: exclusiones en las que AKM0 rechaza β = 0 al 5 % sin ajuste (de 17; exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>F5_P1_E1_MNEG</t>
+          <t>F5X_NAC_IMPLICITO</t>
         </is>
       </c>
       <c r="B352" s="2" t="n">
-        <v>32</v>
+        <v>-0.06</v>
       </c>
       <c r="C352" s="2" t="n"/>
       <c r="D352" s="2" t="n"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -26732,6 +26781,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H352" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26739,7 +26793,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -26754,39 +26808,39 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>P1-E1: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>Media ponderada por educación de las estimaciones por nacionalidad de P1-E3a, E3b y E3c (exploratorio, a posteriori)</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>F5_P1_E1_MREJ</t>
+          <t>F5X_PESO_BAJA</t>
         </is>
       </c>
       <c r="B353" s="2" t="n">
-        <v>4</v>
+        <v>48.7</v>
       </c>
       <c r="C353" s="2" t="n"/>
       <c r="D353" s="2" t="n"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>% de los nativos de 16-64</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2005, 2009, 2015</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -26796,29 +26850,29 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>EPA (INE)</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>P1-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>Peso de la educación baja entre los nacidos en España de 16-64 (EPA, años iniciales de los periodos)</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>F5_P1_E1_MREJN</t>
+          <t>F5_P1_APALANC_MAX</t>
         </is>
       </c>
       <c r="B354" s="2" t="n">
-        <v>4</v>
+        <v>42.2</v>
       </c>
       <c r="C354" s="2" t="n"/>
       <c r="D354" s="2" t="n"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>% de la variación del instrumento</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -26833,33 +26887,33 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>P1-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>Mayor cuota de una comunidad autónoma (05) en la variación del instrumento residualizado (condición del wild bootstrap con 17 grupos, docs/montecarlo.md)</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>F5_P1_E1_MREJP</t>
+          <t>F5_P1_E1_MNEG</t>
         </is>
       </c>
       <c r="B355" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C355" s="2" t="n"/>
       <c r="D355" s="2" t="n"/>
@@ -26895,28 +26949,24 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>P1-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-E1: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>F5_P1_E1_NACT</t>
+          <t>F5_P1_E1_MREJ</t>
         </is>
       </c>
       <c r="B356" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C356" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="D356" s="2" t="n">
-        <v>0.25</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C356" s="2" t="n"/>
+      <c r="D356" s="2" t="n"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -26924,11 +26974,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H356" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -26936,7 +26981,7 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
@@ -26951,24 +26996,24 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>P1-E1: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>F5_P1_E1_PERMR_p</t>
+          <t>F5_P1_E1_MREJN</t>
         </is>
       </c>
       <c r="B357" s="2" t="n">
-        <v>0.078</v>
+        <v>4</v>
       </c>
       <c r="C357" s="2" t="n"/>
       <c r="D357" s="2" t="n"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -26983,7 +27028,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -26998,24 +27043,24 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>P1-E1: p de permutación recentrado</t>
+          <t>P1-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>F5_P1_E1_WCBT_p</t>
+          <t>F5_P1_E1_MREJP</t>
         </is>
       </c>
       <c r="B358" s="2" t="n">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="C358" s="2" t="n"/>
       <c r="D358" s="2" t="n"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -27030,7 +27075,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -27045,21 +27090,25 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>P1-E1: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>F5_P1_E1_beta</t>
+          <t>F5_P1_E1_NACT</t>
         </is>
       </c>
       <c r="B359" s="2" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="C359" s="2" t="n"/>
-      <c r="D359" s="2" t="n"/>
+        <v>0.04</v>
+      </c>
+      <c r="C359" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D359" s="2" t="n">
+        <v>0.25</v>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -27097,24 +27146,24 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>P1-E1: asociación con tasa_actividad (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E1: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>F5_P1_E1_p</t>
+          <t>F5_P1_E1_PERMR_p</t>
         </is>
       </c>
       <c r="B360" s="2" t="n">
-        <v>0.402</v>
+        <v>0.078</v>
       </c>
       <c r="C360" s="2" t="n"/>
       <c r="D360" s="2" t="n"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -27144,24 +27193,24 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>P1-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-E1: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>F5_P1_E2_MNEG</t>
+          <t>F5_P1_E1_WCBT_p</t>
         </is>
       </c>
       <c r="B361" s="2" t="n">
-        <v>15</v>
+        <v>0.251</v>
       </c>
       <c r="C361" s="2" t="n"/>
       <c r="D361" s="2" t="n"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -27176,7 +27225,7 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -27191,24 +27240,24 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>P1-E2: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P1-E1: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>F5_P1_E2_MREJ</t>
+          <t>F5_P1_E1_beta</t>
         </is>
       </c>
       <c r="B362" s="2" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="C362" s="2" t="n"/>
       <c r="D362" s="2" t="n"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -27216,6 +27265,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H362" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -27223,7 +27277,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -27238,24 +27292,24 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>P1-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P1-E1: asociación con tasa_actividad (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>F5_P1_E2_MREJN</t>
+          <t>F5_P1_E1_p</t>
         </is>
       </c>
       <c r="B363" s="2" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="C363" s="2" t="n"/>
       <c r="D363" s="2" t="n"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -27270,7 +27324,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -27285,18 +27339,18 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>P1-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P1-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>F5_P1_E2_MREJP</t>
+          <t>F5_P1_E2_MNEG</t>
         </is>
       </c>
       <c r="B364" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C364" s="2" t="n"/>
       <c r="D364" s="2" t="n"/>
@@ -27332,28 +27386,24 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>P1-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-E2: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>F5_P1_E2_NACT</t>
+          <t>F5_P1_E2_MREJ</t>
         </is>
       </c>
       <c r="B365" s="2" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="C365" s="2" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="D365" s="2" t="n">
-        <v>0.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C365" s="2" t="n"/>
+      <c r="D365" s="2" t="n"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>log por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -27361,11 +27411,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H365" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -27373,7 +27418,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -27388,24 +27433,24 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>P1-E2: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>F5_P1_E2_PERMR_p</t>
+          <t>F5_P1_E2_MREJN</t>
         </is>
       </c>
       <c r="B366" s="2" t="n">
-        <v>0.892</v>
+        <v>0</v>
       </c>
       <c r="C366" s="2" t="n"/>
       <c r="D366" s="2" t="n"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -27420,7 +27465,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -27435,24 +27480,24 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>P1-E2: p de permutación recentrado</t>
+          <t>P1-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>F5_P1_E2_WCBT_p</t>
+          <t>F5_P1_E2_MREJP</t>
         </is>
       </c>
       <c r="B367" s="2" t="n">
-        <v>0.983</v>
+        <v>0</v>
       </c>
       <c r="C367" s="2" t="n"/>
       <c r="D367" s="2" t="n"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -27467,7 +27512,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -27482,21 +27527,25 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>P1-E2: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>F5_P1_E2_beta</t>
+          <t>F5_P1_E2_NACT</t>
         </is>
       </c>
       <c r="B368" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C368" s="2" t="n"/>
-      <c r="D368" s="2" t="n"/>
+        <v>-0.22</v>
+      </c>
+      <c r="C368" s="2" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="D368" s="2" t="n">
+        <v>0.49</v>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>log por pp</t>
@@ -27534,24 +27583,24 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>P1-E2: asociación con log_ocupados (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E2: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>F5_P1_E2_p</t>
+          <t>F5_P1_E2_PERMR_p</t>
         </is>
       </c>
       <c r="B369" s="2" t="n">
-        <v>0.981</v>
+        <v>0.892</v>
       </c>
       <c r="C369" s="2" t="n"/>
       <c r="D369" s="2" t="n"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -27581,24 +27630,24 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>P1-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-E2: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_CTRL_CUOTA_1998</t>
+          <t>F5_P1_E2_WCBT_p</t>
         </is>
       </c>
       <c r="B370" s="2" t="n">
-        <v>-0.853</v>
+        <v>0.983</v>
       </c>
       <c r="C370" s="2" t="n"/>
       <c r="D370" s="2" t="n"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -27606,11 +27655,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H370" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -27633,24 +27677,24 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>P1-E3a con el control de cuotas «cuota_1998» (F al nivel del shock = 10.0; p AKM0 sin ajustar = 0.051)</t>
+          <t>P1-E2: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_CTRL_CUOTA_1998_p</t>
+          <t>F5_P1_E2_beta</t>
         </is>
       </c>
       <c r="B371" s="2" t="n">
-        <v>0.051</v>
+        <v>0.03</v>
       </c>
       <c r="C371" s="2" t="n"/>
       <c r="D371" s="2" t="n"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>log por pp</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -27658,6 +27702,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H371" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -27680,24 +27729,24 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>P1-E3a, control «cuota_1998»: p AKM0 sin ajustar</t>
+          <t>P1-E2: asociación con log_ocupados (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_CTRL_ORIGINAL</t>
+          <t>F5_P1_E2_p</t>
         </is>
       </c>
       <c r="B372" s="2" t="n">
-        <v>-0.6889999999999999</v>
+        <v>0.981</v>
       </c>
       <c r="C372" s="2" t="n"/>
       <c r="D372" s="2" t="n"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -27705,11 +27754,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H372" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -27732,24 +27776,24 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>P1-E3a con el control de cuotas «original» (F al nivel del shock = 6.6; p AKM0 sin ajustar = 0.002)</t>
+          <t>P1-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_CTRL_ORIGINAL_p</t>
+          <t>F5_P1_E3a_CTRL_CUOTA_1998</t>
         </is>
       </c>
       <c r="B373" s="2" t="n">
-        <v>0.002</v>
+        <v>-0.853</v>
       </c>
       <c r="C373" s="2" t="n"/>
       <c r="D373" s="2" t="n"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -27757,6 +27801,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H373" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -27779,24 +27828,24 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>P1-E3a, control «original»: p AKM0 sin ajustar</t>
+          <t>P1-E3a con el control de cuotas «cuota_1998» (F al nivel del shock = 10.0; p AKM0 sin ajustar = 0.051)</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MNEG</t>
+          <t>F5_P1_E3a_CTRL_CUOTA_1998_p</t>
         </is>
       </c>
       <c r="B374" s="2" t="n">
-        <v>32</v>
+        <v>0.051</v>
       </c>
       <c r="C374" s="2" t="n"/>
       <c r="D374" s="2" t="n"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -27811,7 +27860,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -27826,24 +27875,24 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>P1-E3a: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P1-E3a, control «cuota_1998»: p AKM0 sin ajustar</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MREJ</t>
+          <t>F5_P1_E3a_CTRL_ORIGINAL</t>
         </is>
       </c>
       <c r="B375" s="2" t="n">
-        <v>13</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="C375" s="2" t="n"/>
       <c r="D375" s="2" t="n"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -27851,6 +27900,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H375" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -27858,7 +27912,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -27873,24 +27927,24 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>P1-E3a: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P1-E3a con el control de cuotas «original» (F al nivel del shock = 6.6; p AKM0 sin ajustar = 0.002)</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MREJN</t>
+          <t>F5_P1_E3a_CTRL_ORIGINAL_p</t>
         </is>
       </c>
       <c r="B376" s="2" t="n">
-        <v>13</v>
+        <v>0.002</v>
       </c>
       <c r="C376" s="2" t="n"/>
       <c r="D376" s="2" t="n"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -27905,7 +27959,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -27920,18 +27974,18 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>P1-E3a: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P1-E3a, control «original»: p AKM0 sin ajustar</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MREJP</t>
+          <t>F5_P1_E3a_MNEG</t>
         </is>
       </c>
       <c r="B377" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C377" s="2" t="n"/>
       <c r="D377" s="2" t="n"/>
@@ -27967,28 +28021,24 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>P1-E3a: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-E3a: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MULT_FUERTE_MED</t>
+          <t>F5_P1_E3a_MREJ</t>
         </is>
       </c>
       <c r="B378" s="2" t="n">
-        <v>-0.607</v>
-      </c>
-      <c r="C378" s="2" t="n">
-        <v>-0.663</v>
-      </c>
-      <c r="D378" s="2" t="n">
-        <v>-0.466</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C378" s="2" t="n"/>
+      <c r="D378" s="2" t="n"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -27996,11 +28046,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H378" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28023,18 +28068,18 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>P1-E3a: mediana de β en las especificaciones del multiverso con F al nivel del shock ≥ 10 (5 de 32; intervalo: mínimo y máximo)</t>
+          <t>P1-E3a: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MULT_FUERTE_N</t>
+          <t>F5_P1_E3a_MREJN</t>
         </is>
       </c>
       <c r="B379" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C379" s="2" t="n"/>
       <c r="D379" s="2" t="n"/>
@@ -28070,28 +28115,24 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>P1-E3a: especificaciones del multiverso con F al nivel del shock ≥ 10</t>
+          <t>P1-E3a: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MULT_MED</t>
+          <t>F5_P1_E3a_MREJP</t>
         </is>
       </c>
       <c r="B380" s="2" t="n">
-        <v>-0.668</v>
-      </c>
-      <c r="C380" s="2" t="n">
-        <v>-12.869</v>
-      </c>
-      <c r="D380" s="2" t="n">
-        <v>-0.227</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C380" s="2" t="n"/>
+      <c r="D380" s="2" t="n"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -28099,11 +28140,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H380" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28116,7 +28152,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>nacidos en España con educación baja</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
@@ -28126,24 +28162,28 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>P1-E3a: mediana de β en el multiverso (32 especificaciones; intervalo: mínimo y máximo)</t>
+          <t>P1-E3a: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MULT_NEG</t>
+          <t>F5_P1_E3a_MULT_FUERTE_MED</t>
         </is>
       </c>
       <c r="B381" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="C381" s="2" t="n"/>
-      <c r="D381" s="2" t="n"/>
+        <v>-0.607</v>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>-0.663</v>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>-0.466</v>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -28151,6 +28191,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H381" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28163,7 +28208,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>nacidos en España con educación baja</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
@@ -28173,18 +28218,18 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>P1-E3a: especificaciones del multiverso con β negativo</t>
+          <t>P1-E3a: mediana de β en las especificaciones del multiverso con F al nivel del shock ≥ 10 (5 de 32; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_MULT_RECHAZA</t>
+          <t>F5_P1_E3a_MULT_FUERTE_N</t>
         </is>
       </c>
       <c r="B382" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C382" s="2" t="n"/>
       <c r="D382" s="2" t="n"/>
@@ -28210,7 +28255,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>nacidos en España con educación baja</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -28220,24 +28265,24 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>P1-E3a: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste</t>
+          <t>P1-E3a: especificaciones del multiverso con F al nivel del shock ≥ 10</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_NACIONALIDAD</t>
+          <t>F5_P1_E3a_MULT_MED</t>
         </is>
       </c>
       <c r="B383" s="2" t="n">
-        <v>-0.256</v>
+        <v>-0.668</v>
       </c>
       <c r="C383" s="2" t="n">
-        <v>-0.455</v>
+        <v>-12.869</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>-0.041</v>
+        <v>-0.227</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -28261,7 +28306,7 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
@@ -28276,28 +28321,24 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>P1-E3a: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 18.4; IC: conjunto AKM0, acotado = True, convexo = True)</t>
+          <t>P1-E3a: mediana de β en el multiverso (32 especificaciones; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_NACT</t>
+          <t>F5_P1_E3a_MULT_NEG</t>
         </is>
       </c>
       <c r="B384" s="2" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="C384" s="2" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="D384" s="2" t="n">
-        <v>-0.04</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C384" s="2" t="n"/>
+      <c r="D384" s="2" t="n"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -28305,11 +28346,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H384" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28317,12 +28353,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -28332,24 +28368,24 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>P1-E3a: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3a: especificaciones del multiverso con β negativo</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_PERMR_p</t>
+          <t>F5_P1_E3a_MULT_RECHAZA</t>
         </is>
       </c>
       <c r="B385" s="2" t="n">
-        <v>0.006</v>
+        <v>13</v>
       </c>
       <c r="C385" s="2" t="n"/>
       <c r="D385" s="2" t="n"/>
       <c r="E385" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -28364,12 +28400,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -28379,28 +28415,28 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>P1-E3a: p de permutación recentrado</t>
+          <t>P1-E3a: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_PERM_MED</t>
+          <t>F5_P1_E3a_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B386" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.256</v>
       </c>
       <c r="C386" s="2" t="n">
-        <v>-1.6</v>
+        <v>-0.455</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>0.78</v>
+        <v>-0.041</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -28408,6 +28444,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H386" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28420,7 +28461,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -28430,24 +28471,28 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>P1-E3a: mediana del t de las 500 permutaciones de los shocks (intervalo: 95 % central)</t>
+          <t>P1-E3a: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 18.4; IC: conjunto AKM0, acotado = True, convexo = True)</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_PERM_p</t>
+          <t>F5_P1_E3a_NACT</t>
         </is>
       </c>
       <c r="B387" s="2" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="C387" s="2" t="n"/>
-      <c r="D387" s="2" t="n"/>
+        <v>-0.26</v>
+      </c>
+      <c r="C387" s="2" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -28455,6 +28500,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H387" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28467,7 +28517,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>nacidos en España con educación baja</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -28477,24 +28527,24 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>P1-E3a: p del placebo de permutación de shocks (500 permutaciones), recentrado en la mediana de la distribución permutada</t>
+          <t>P1-E3a: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_T</t>
+          <t>F5_P1_E3a_PERMR_p</t>
         </is>
       </c>
       <c r="B388" s="2" t="n">
-        <v>-2.22</v>
+        <v>0.006</v>
       </c>
       <c r="C388" s="2" t="n"/>
       <c r="D388" s="2" t="n"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -28524,24 +28574,28 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>P1-E3a: t de la especificación principal con el error BHJ</t>
+          <t>P1-E3a: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_WCBT_p</t>
+          <t>F5_P1_E3a_PERM_MED</t>
         </is>
       </c>
       <c r="B389" s="2" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="C389" s="2" t="n"/>
-      <c r="D389" s="2" t="n"/>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="C389" s="2" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="D389" s="2" t="n">
+        <v>0.78</v>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -28571,18 +28625,18 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>P1-E3a: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-E3a: mediana del t de las 500 permutaciones de los shocks (intervalo: 95 % central)</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_WCB_p</t>
+          <t>F5_P1_E3a_PERM_p</t>
         </is>
       </c>
       <c r="B390" s="2" t="n">
-        <v>0.331</v>
+        <v>0.006</v>
       </c>
       <c r="C390" s="2" t="n"/>
       <c r="D390" s="2" t="n"/>
@@ -28608,7 +28662,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -28618,26 +28672,24 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>P1-E3a: p del wild cluster bootstrap de la forma reducida agrupando por comunidad autónoma (Webb, 17 grupos; pre-registrado)</t>
+          <t>P1-E3a: p del placebo de permutación de shocks (500 permutaciones), recentrado en la mediana de la distribución permutada</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_beta</t>
+          <t>F5_P1_E3a_T</t>
         </is>
       </c>
       <c r="B391" s="2" t="n">
-        <v>-0.607</v>
+        <v>-2.22</v>
       </c>
       <c r="C391" s="2" t="n"/>
-      <c r="D391" s="2" t="n">
-        <v>-0.061</v>
-      </c>
+      <c r="D391" s="2" t="n"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -28645,11 +28697,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H391" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28662,7 +28709,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>nacidos en España con educación baja</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -28672,24 +28719,24 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>P1-E3a: asociación con tasa_empleo_educ_baja (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3a: t de la especificación principal con el error BHJ</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>F5_P1_E3a_p</t>
+          <t>F5_P1_E3a_WCBT_p</t>
         </is>
       </c>
       <c r="B392" s="2" t="n">
-        <v>0.245</v>
+        <v>0.331</v>
       </c>
       <c r="C392" s="2" t="n"/>
       <c r="D392" s="2" t="n"/>
       <c r="E392" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -28719,24 +28766,24 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>P1-E3a: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-E3a: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_MNEG</t>
+          <t>F5_P1_E3a_WCB_p</t>
         </is>
       </c>
       <c r="B393" s="2" t="n">
-        <v>26</v>
+        <v>0.331</v>
       </c>
       <c r="C393" s="2" t="n"/>
       <c r="D393" s="2" t="n"/>
       <c r="E393" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -28751,7 +28798,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -28766,24 +28813,26 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>P1-E3b: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P1-E3a: p del wild cluster bootstrap de la forma reducida agrupando por comunidad autónoma (Webb, 17 grupos; pre-registrado)</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_MREJ</t>
+          <t>F5_P1_E3a_beta</t>
         </is>
       </c>
       <c r="B394" s="2" t="n">
-        <v>4</v>
+        <v>-0.607</v>
       </c>
       <c r="C394" s="2" t="n"/>
-      <c r="D394" s="2" t="n"/>
+      <c r="D394" s="2" t="n">
+        <v>-0.061</v>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -28791,6 +28840,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H394" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28798,12 +28852,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación baja</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -28813,24 +28867,24 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>P1-E3b: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P1-E3a: asociación con tasa_empleo_educ_baja (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_MREJN</t>
+          <t>F5_P1_E3a_p</t>
         </is>
       </c>
       <c r="B395" s="2" t="n">
-        <v>4</v>
+        <v>0.245</v>
       </c>
       <c r="C395" s="2" t="n"/>
       <c r="D395" s="2" t="n"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -28845,7 +28899,7 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -28860,18 +28914,18 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>P1-E3b: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P1-E3a: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_MREJP</t>
+          <t>F5_P1_E3b_MNEG</t>
         </is>
       </c>
       <c r="B396" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C396" s="2" t="n"/>
       <c r="D396" s="2" t="n"/>
@@ -28907,28 +28961,24 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>P1-E3b: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-E3b: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_NACT</t>
+          <t>F5_P1_E3b_MREJ</t>
         </is>
       </c>
       <c r="B397" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="C397" s="2" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="D397" s="2" t="n">
-        <v>0.89</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C397" s="2" t="n"/>
+      <c r="D397" s="2" t="n"/>
       <c r="E397" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -28936,11 +28986,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H397" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -28948,7 +28993,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -28963,24 +29008,24 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>P1-E3b: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3b: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_PERMR_p</t>
+          <t>F5_P1_E3b_MREJN</t>
         </is>
       </c>
       <c r="B398" s="2" t="n">
-        <v>0.654</v>
+        <v>4</v>
       </c>
       <c r="C398" s="2" t="n"/>
       <c r="D398" s="2" t="n"/>
       <c r="E398" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -28995,7 +29040,7 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -29010,24 +29055,24 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>P1-E3b: p de permutación recentrado</t>
+          <t>P1-E3b: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_WCBT_p</t>
+          <t>F5_P1_E3b_MREJP</t>
         </is>
       </c>
       <c r="B399" s="2" t="n">
-        <v>0.925</v>
+        <v>0</v>
       </c>
       <c r="C399" s="2" t="n"/>
       <c r="D399" s="2" t="n"/>
       <c r="E399" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -29042,7 +29087,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -29057,21 +29102,25 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>P1-E3b: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-E3b: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_beta</t>
+          <t>F5_P1_E3b_NACT</t>
         </is>
       </c>
       <c r="B400" s="2" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="C400" s="2" t="n"/>
-      <c r="D400" s="2" t="n"/>
+        <v>0.19</v>
+      </c>
+      <c r="C400" s="2" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>0.89</v>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -29099,7 +29148,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>nacidos en España con educación media</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -29109,24 +29158,24 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>P1-E3b: asociación con tasa_empleo_educ_media (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3b: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>F5_P1_E3b_p</t>
+          <t>F5_P1_E3b_PERMR_p</t>
         </is>
       </c>
       <c r="B401" s="2" t="n">
-        <v>0.981</v>
+        <v>0.654</v>
       </c>
       <c r="C401" s="2" t="n"/>
       <c r="D401" s="2" t="n"/>
       <c r="E401" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -29156,24 +29205,24 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>P1-E3b: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-E3b: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_MNEG</t>
+          <t>F5_P1_E3b_WCBT_p</t>
         </is>
       </c>
       <c r="B402" s="2" t="n">
-        <v>24</v>
+        <v>0.925</v>
       </c>
       <c r="C402" s="2" t="n"/>
       <c r="D402" s="2" t="n"/>
       <c r="E402" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -29188,7 +29237,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -29203,24 +29252,24 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>P1-E3c: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P1-E3b: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_MREJ</t>
+          <t>F5_P1_E3b_beta</t>
         </is>
       </c>
       <c r="B403" s="2" t="n">
-        <v>4</v>
+        <v>0.126</v>
       </c>
       <c r="C403" s="2" t="n"/>
       <c r="D403" s="2" t="n"/>
       <c r="E403" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -29228,6 +29277,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H403" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -29235,12 +29289,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación media</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -29250,24 +29304,24 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>P1-E3c: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P1-E3b: asociación con tasa_empleo_educ_media (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_MREJN</t>
+          <t>F5_P1_E3b_p</t>
         </is>
       </c>
       <c r="B404" s="2" t="n">
-        <v>4</v>
+        <v>0.981</v>
       </c>
       <c r="C404" s="2" t="n"/>
       <c r="D404" s="2" t="n"/>
       <c r="E404" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -29282,7 +29336,7 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -29297,18 +29351,18 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>P1-E3c: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P1-E3b: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_MREJP</t>
+          <t>F5_P1_E3c_MNEG</t>
         </is>
       </c>
       <c r="B405" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C405" s="2" t="n"/>
       <c r="D405" s="2" t="n"/>
@@ -29344,28 +29398,24 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>P1-E3c: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-E3c: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_NACT</t>
+          <t>F5_P1_E3c_MREJ</t>
         </is>
       </c>
       <c r="B406" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C406" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="D406" s="2" t="n">
-        <v>0.62</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C406" s="2" t="n"/>
+      <c r="D406" s="2" t="n"/>
       <c r="E406" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -29373,11 +29423,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H406" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -29385,7 +29430,7 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -29400,24 +29445,24 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>P1-E3c: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3c: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_PERMR_p</t>
+          <t>F5_P1_E3c_MREJN</t>
         </is>
       </c>
       <c r="B407" s="2" t="n">
-        <v>0.028</v>
+        <v>4</v>
       </c>
       <c r="C407" s="2" t="n"/>
       <c r="D407" s="2" t="n"/>
       <c r="E407" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -29432,7 +29477,7 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -29447,24 +29492,24 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>P1-E3c: p de permutación recentrado</t>
+          <t>P1-E3c: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_WCBT_p</t>
+          <t>F5_P1_E3c_MREJP</t>
         </is>
       </c>
       <c r="B408" s="2" t="n">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="C408" s="2" t="n"/>
       <c r="D408" s="2" t="n"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -29479,7 +29524,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -29494,21 +29539,25 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>P1-E3c: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-E3c: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_beta</t>
+          <t>F5_P1_E3c_NACT</t>
         </is>
       </c>
       <c r="B409" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C409" s="2" t="n"/>
-      <c r="D409" s="2" t="n"/>
+        <v>0.06</v>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>0.62</v>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -29536,7 +29585,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>nacidos en España con educación alta</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -29546,24 +29595,24 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>P1-E3c: asociación con tasa_empleo_educ_alta (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E3c: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>F5_P1_E3c_p</t>
+          <t>F5_P1_E3c_PERMR_p</t>
         </is>
       </c>
       <c r="B410" s="2" t="n">
-        <v>0.402</v>
+        <v>0.028</v>
       </c>
       <c r="C410" s="2" t="n"/>
       <c r="D410" s="2" t="n"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -29593,28 +29642,24 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>P1-E3c: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-E3c: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>F5_P1_E4_beta</t>
+          <t>F5_P1_E3c_WCBT_p</t>
         </is>
       </c>
       <c r="B411" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C411" s="2" t="n">
-        <v>-0.5620000000000001</v>
-      </c>
-      <c r="D411" s="2" t="n">
-        <v>0.361</v>
-      </c>
+        <v>0.379</v>
+      </c>
+      <c r="C411" s="2" t="n"/>
+      <c r="D411" s="2" t="n"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Δ log salario por punto de cuota</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -29622,51 +29667,46 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2010-2022</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>españoles (nacionalidad)</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>EES y EPA (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>P1-E4 (Borjas): asociación entre la cuota de nacidos fuera en la celda educación × edad y el salario por hora de los españoles (primeras diferencias; IC orientativo por errores agrupados en 15 celdas; p wild bootstrap = 0.61)</t>
+          <t>P1-E3c: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>F5_P1_E6_MNEG</t>
+          <t>F5_P1_E3c_beta</t>
         </is>
       </c>
       <c r="B412" s="2" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="C412" s="2" t="n"/>
       <c r="D412" s="2" t="n"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -29674,6 +29714,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H412" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -29681,12 +29726,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>nacidos en España con educación alta</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -29696,24 +29741,24 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>P1-E6: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P1-E3c: asociación con tasa_empleo_educ_alta (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>F5_P1_E6_MREJ</t>
+          <t>F5_P1_E3c_p</t>
         </is>
       </c>
       <c r="B413" s="2" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="C413" s="2" t="n"/>
       <c r="D413" s="2" t="n"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -29728,7 +29773,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -29743,24 +29788,28 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>P1-E6: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P1-E3c: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>F5_P1_E6_MREJN</t>
+          <t>F5_P1_E4_beta</t>
         </is>
       </c>
       <c r="B414" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C414" s="2" t="n"/>
-      <c r="D414" s="2" t="n"/>
+        <v>-0.1</v>
+      </c>
+      <c r="C414" s="2" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>0.361</v>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>Δ log salario por punto de cuota</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -29768,40 +29817,45 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>2010-2022</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>España</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>españoles (nacionalidad)</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>EES y EPA (INE)</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>P1-E6: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P1-E4 (Borjas): asociación entre la cuota de nacidos fuera en la celda educación × edad y el salario por hora de los españoles (primeras diferencias; IC orientativo por errores agrupados en 15 celdas; p wild bootstrap = 0.61)</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>F5_P1_E6_MREJP</t>
+          <t>F5_P1_E6_MNEG</t>
         </is>
       </c>
       <c r="B415" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C415" s="2" t="n"/>
       <c r="D415" s="2" t="n"/>
@@ -29837,28 +29891,24 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>P1-E6: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-E6: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>F5_P1_E6_NACT</t>
+          <t>F5_P1_E6_MREJ</t>
         </is>
       </c>
       <c r="B416" s="2" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="C416" s="2" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="D416" s="2" t="n">
-        <v>0.41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C416" s="2" t="n"/>
+      <c r="D416" s="2" t="n"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>log por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -29866,11 +29916,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H416" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -29878,7 +29923,7 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -29893,24 +29938,24 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>P1-E6: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E6: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>F5_P1_E6_PERMR_p</t>
+          <t>F5_P1_E6_MREJN</t>
         </is>
       </c>
       <c r="B417" s="2" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
       <c r="C417" s="2" t="n"/>
       <c r="D417" s="2" t="n"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -29925,7 +29970,7 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -29940,24 +29985,24 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>P1-E6: p de permutación recentrado</t>
+          <t>P1-E6: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>F5_P1_E6_WCBT_p</t>
+          <t>F5_P1_E6_MREJP</t>
         </is>
       </c>
       <c r="B418" s="2" t="n">
-        <v>0.613</v>
+        <v>0</v>
       </c>
       <c r="C418" s="2" t="n"/>
       <c r="D418" s="2" t="n"/>
       <c r="E418" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -29972,7 +30017,7 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -29987,21 +30032,25 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>P1-E6: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-E6: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>F5_P1_E6_beta</t>
+          <t>F5_P1_E6_NACT</t>
         </is>
       </c>
       <c r="B419" s="2" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="C419" s="2" t="n"/>
-      <c r="D419" s="2" t="n"/>
+        <v>-0.09</v>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>0.41</v>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>log por pp</t>
@@ -30039,24 +30088,24 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>P1-E6: asociación con log_pob_nativos (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-E6: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>F5_P1_E6_p</t>
+          <t>F5_P1_E6_PERMR_p</t>
         </is>
       </c>
       <c r="B420" s="2" t="n">
-        <v>0.981</v>
+        <v>0.662</v>
       </c>
       <c r="C420" s="2" t="n"/>
       <c r="D420" s="2" t="n"/>
       <c r="E420" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -30086,24 +30135,24 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>P1-E6: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-E6: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>F5_P1_F_CTRL_CUOTA_1998</t>
+          <t>F5_P1_E6_WCBT_p</t>
         </is>
       </c>
       <c r="B421" s="2" t="n">
-        <v>10</v>
+        <v>0.613</v>
       </c>
       <c r="C421" s="2" t="n"/>
       <c r="D421" s="2" t="n"/>
       <c r="E421" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -30123,34 +30172,34 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>F al nivel del shock con el control «cuota_1998»</t>
+          <t>P1-E6: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>F5_P1_F_CTRL_ORIGINAL</t>
+          <t>F5_P1_E6_beta</t>
         </is>
       </c>
       <c r="B422" s="2" t="n">
-        <v>6.6</v>
+        <v>0.162</v>
       </c>
       <c r="C422" s="2" t="n"/>
       <c r="D422" s="2" t="n"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>log por pp</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -30158,6 +30207,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H422" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30170,34 +30224,34 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>F al nivel del shock con el control «original»</t>
+          <t>P1-E6: asociación con log_pob_nativos (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>F5_P1_F_EFECTIVO</t>
+          <t>F5_P1_E6_p</t>
         </is>
       </c>
       <c r="B423" s="2" t="n">
-        <v>17.9</v>
+        <v>0.981</v>
       </c>
       <c r="C423" s="2" t="n"/>
       <c r="D423" s="2" t="n"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -30217,28 +30271,28 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>padrón, ECP (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>F efectivo de primera etapa agrupado por provincia, especificación principal de P1</t>
+          <t>P1-E6: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>F5_P1_F_NACIONALIDAD</t>
+          <t>F5_P1_F_CTRL_CUOTA_1998</t>
         </is>
       </c>
       <c r="B424" s="2" t="n">
-        <v>18.4</v>
+        <v>10</v>
       </c>
       <c r="C424" s="2" t="n"/>
       <c r="D424" s="2" t="n"/>
@@ -30269,23 +30323,23 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>padrón (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>F de primera etapa al nivel del shock en la variante por nacionalidad</t>
+          <t>F al nivel del shock con el control «cuota_1998»</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>F5_P1_F_SHOCK</t>
+          <t>F5_P1_F_CTRL_ORIGINAL</t>
         </is>
       </c>
       <c r="B425" s="2" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="C425" s="2" t="n"/>
       <c r="D425" s="2" t="n"/>
@@ -30321,18 +30375,18 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>F de primera etapa al nivel del shock (BHJ), especificación principal de P1 (umbral pre-registrado: 10)</t>
+          <t>F al nivel del shock con el control «original»</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>F5_P1_F_SIN_TOP3</t>
+          <t>F5_P1_F_EFECTIVO</t>
         </is>
       </c>
       <c r="B426" s="2" t="n">
-        <v>0.92</v>
+        <v>17.9</v>
       </c>
       <c r="C426" s="2" t="n"/>
       <c r="D426" s="2" t="n"/>
@@ -30363,29 +30417,29 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>padrón (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>F de primera etapa al nivel del shock al excluir los tres orígenes de mayor peso de Rotemberg (prueba no informativa si es &lt; 10)</t>
+          <t>F efectivo de primera etapa agrupado por provincia, especificación principal de P1</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>F5_P1_H1_CTRL_CUOTA_1998</t>
+          <t>F5_P1_F_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B427" s="2" t="n">
-        <v>-0.164</v>
+        <v>18.4</v>
       </c>
       <c r="C427" s="2" t="n"/>
       <c r="D427" s="2" t="n"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -30393,11 +30447,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H427" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30410,34 +30459,34 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón (INE)</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>P1-H1 con el control de cuotas «cuota_1998» (F al nivel del shock = 10.0; p AKM0 sin ajustar = 0.983)</t>
+          <t>F de primera etapa al nivel del shock en la variante por nacionalidad</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>F5_P1_H1_CTRL_CUOTA_1998_p</t>
+          <t>F5_P1_F_SHOCK</t>
         </is>
       </c>
       <c r="B428" s="2" t="n">
-        <v>0.983</v>
+        <v>13.5</v>
       </c>
       <c r="C428" s="2" t="n"/>
       <c r="D428" s="2" t="n"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -30457,34 +30506,34 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón, ECP (INE)</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>P1-H1, control «cuota_1998»: p AKM0 sin ajustar</t>
+          <t>F de primera etapa al nivel del shock (BHJ), especificación principal de P1 (umbral pre-registrado: 10)</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>F5_P1_H1_CTRL_ORIGINAL</t>
+          <t>F5_P1_F_SIN_TOP3</t>
         </is>
       </c>
       <c r="B429" s="2" t="n">
-        <v>-0.228</v>
+        <v>0.92</v>
       </c>
       <c r="C429" s="2" t="n"/>
       <c r="D429" s="2" t="n"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -30492,11 +30541,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H429" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30509,34 +30553,34 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón (INE)</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>P1-H1 con el control de cuotas «original» (F al nivel del shock = 6.6; p AKM0 sin ajustar = 0.194)</t>
+          <t>F de primera etapa al nivel del shock al excluir los tres orígenes de mayor peso de Rotemberg (prueba no informativa si es &lt; 10)</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>F5_P1_H1_CTRL_ORIGINAL_p</t>
+          <t>F5_P1_H1_CTRL_CUOTA_1998</t>
         </is>
       </c>
       <c r="B430" s="2" t="n">
-        <v>0.194</v>
+        <v>-0.164</v>
       </c>
       <c r="C430" s="2" t="n"/>
       <c r="D430" s="2" t="n"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -30544,6 +30588,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H430" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30566,24 +30615,24 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>P1-H1, control «original»: p AKM0 sin ajustar</t>
+          <t>P1-H1 con el control de cuotas «cuota_1998» (F al nivel del shock = 10.0; p AKM0 sin ajustar = 0.983)</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MNEG</t>
+          <t>F5_P1_H1_CTRL_CUOTA_1998_p</t>
         </is>
       </c>
       <c r="B431" s="2" t="n">
-        <v>24</v>
+        <v>0.983</v>
       </c>
       <c r="C431" s="2" t="n"/>
       <c r="D431" s="2" t="n"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -30598,7 +30647,7 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -30613,24 +30662,24 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P1-H1, control «cuota_1998»: p AKM0 sin ajustar</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MREJ</t>
+          <t>F5_P1_H1_CTRL_ORIGINAL</t>
         </is>
       </c>
       <c r="B432" s="2" t="n">
-        <v>6</v>
+        <v>-0.228</v>
       </c>
       <c r="C432" s="2" t="n"/>
       <c r="D432" s="2" t="n"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -30638,6 +30687,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H432" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30645,7 +30699,7 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -30660,24 +30714,24 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P1-H1 con el control de cuotas «original» (F al nivel del shock = 6.6; p AKM0 sin ajustar = 0.194)</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MREJN</t>
+          <t>F5_P1_H1_CTRL_ORIGINAL_p</t>
         </is>
       </c>
       <c r="B433" s="2" t="n">
-        <v>6</v>
+        <v>0.194</v>
       </c>
       <c r="C433" s="2" t="n"/>
       <c r="D433" s="2" t="n"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -30692,7 +30746,7 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -30707,18 +30761,18 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P1-H1, control «original»: p AKM0 sin ajustar</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MREJP</t>
+          <t>F5_P1_H1_MNEG</t>
         </is>
       </c>
       <c r="B434" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C434" s="2" t="n"/>
       <c r="D434" s="2" t="n"/>
@@ -30754,28 +30808,24 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-H1: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_FUERTE_MED</t>
+          <t>F5_P1_H1_MREJ</t>
         </is>
       </c>
       <c r="B435" s="2" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="C435" s="2" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="D435" s="2" t="n">
-        <v>0.133</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C435" s="2" t="n"/>
+      <c r="D435" s="2" t="n"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -30783,11 +30833,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H435" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30810,18 +30855,18 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>P1-H1: mediana de β en las especificaciones del multiverso con F al nivel del shock ≥ 10 (5 de 32; intervalo: mínimo y máximo)</t>
+          <t>P1-H1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_FUERTE_N</t>
+          <t>F5_P1_H1_MREJN</t>
         </is>
       </c>
       <c r="B436" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C436" s="2" t="n"/>
       <c r="D436" s="2" t="n"/>
@@ -30857,28 +30902,24 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso con F al nivel del shock ≥ 10</t>
+          <t>P1-H1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_MED</t>
+          <t>F5_P1_H1_MREJP</t>
         </is>
       </c>
       <c r="B437" s="2" t="n">
-        <v>-0.384</v>
-      </c>
-      <c r="C437" s="2" t="n">
-        <v>-13.291</v>
-      </c>
-      <c r="D437" s="2" t="n">
-        <v>0.228</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C437" s="2" t="n"/>
+      <c r="D437" s="2" t="n"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -30886,11 +30927,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H437" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30913,24 +30949,28 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>P1-H1: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
+          <t>P1-H1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_NEG</t>
+          <t>F5_P1_H1_MULT_FUERTE_MED</t>
         </is>
       </c>
       <c r="B438" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="C438" s="2" t="n"/>
-      <c r="D438" s="2" t="n"/>
+        <v>0.092</v>
+      </c>
+      <c r="C438" s="2" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="D438" s="2" t="n">
+        <v>0.133</v>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -30938,6 +30978,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H438" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -30960,18 +31005,18 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso con β negativo (de 32)</t>
+          <t>P1-H1: mediana de β en las especificaciones del multiverso con F al nivel del shock ≥ 10 (5 de 32; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>F5_P1_H1_MULT_RECHAZA</t>
+          <t>F5_P1_H1_MULT_FUERTE_N</t>
         </is>
       </c>
       <c r="B439" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C439" s="2" t="n"/>
       <c r="D439" s="2" t="n"/>
@@ -31007,24 +31052,24 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>P1-H1: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
+          <t>P1-H1: especificaciones del multiverso con F al nivel del shock ≥ 10</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>F5_P1_H1_NACIONALIDAD</t>
+          <t>F5_P1_H1_MULT_MED</t>
         </is>
       </c>
       <c r="B440" s="2" t="n">
-        <v>-0.065</v>
+        <v>-0.384</v>
       </c>
       <c r="C440" s="2" t="n">
-        <v>-0.54</v>
+        <v>-13.291</v>
       </c>
       <c r="D440" s="2" t="n">
-        <v>0.36</v>
+        <v>0.228</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -31048,7 +31093,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -31063,28 +31108,24 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>P1-H1: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 18.4; IC: conjunto AKM0, acotado = True)</t>
+          <t>P1-H1: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>F5_P1_H1_NACT</t>
+          <t>F5_P1_H1_MULT_NEG</t>
         </is>
       </c>
       <c r="B441" s="2" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="C441" s="2" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="D441" s="2" t="n">
-        <v>0.36</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C441" s="2" t="n"/>
+      <c r="D441" s="2" t="n"/>
       <c r="E441" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -31092,11 +31133,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H441" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31104,7 +31140,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -31119,24 +31155,24 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>P1-H1: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-H1: especificaciones del multiverso con β negativo (de 32)</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>F5_P1_H1_PERMR_p</t>
+          <t>F5_P1_H1_MULT_RECHAZA</t>
         </is>
       </c>
       <c r="B442" s="2" t="n">
-        <v>0.754</v>
+        <v>6</v>
       </c>
       <c r="C442" s="2" t="n"/>
       <c r="D442" s="2" t="n"/>
       <c r="E442" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -31151,7 +31187,7 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -31166,28 +31202,28 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>P1-H1: p de permutación recentrado</t>
+          <t>P1-H1: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>F5_P1_H1_PERM_MED</t>
+          <t>F5_P1_H1_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B443" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.065</v>
       </c>
       <c r="C443" s="2" t="n">
-        <v>-1.65</v>
+        <v>-0.54</v>
       </c>
       <c r="D443" s="2" t="n">
-        <v>0.89</v>
+        <v>0.36</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -31195,6 +31231,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H443" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31217,24 +31258,28 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>P1-H1: mediana del t de las 500 permutaciones de los shocks (intervalo: 95 % central)</t>
+          <t>P1-H1: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 18.4; IC: conjunto AKM0, acotado = True)</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>F5_P1_H1_T</t>
+          <t>F5_P1_H1_NACT</t>
         </is>
       </c>
       <c r="B444" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C444" s="2" t="n"/>
-      <c r="D444" s="2" t="n"/>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="C444" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="D444" s="2" t="n">
+        <v>0.36</v>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -31242,6 +31287,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H444" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31264,18 +31314,18 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>P1-H1: t de la especificación principal con el error BHJ</t>
+          <t>P1-H1: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>F5_P1_H1_WCBT_p</t>
+          <t>F5_P1_H1_PERMR_p</t>
         </is>
       </c>
       <c r="B445" s="2" t="n">
-        <v>0.914</v>
+        <v>0.754</v>
       </c>
       <c r="C445" s="2" t="n"/>
       <c r="D445" s="2" t="n"/>
@@ -31311,24 +31361,28 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>P1-H1: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-H1: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>F5_P1_H1_WCB_p</t>
+          <t>F5_P1_H1_PERM_MED</t>
         </is>
       </c>
       <c r="B446" s="2" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="C446" s="2" t="n"/>
-      <c r="D446" s="2" t="n"/>
+        <v>-0.03</v>
+      </c>
+      <c r="C446" s="2" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="D446" s="2" t="n">
+        <v>0.89</v>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -31358,24 +31412,24 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>P1-H1: p del wild cluster bootstrap de la forma reducida agrupando por comunidad autónoma (Webb, 17 grupos; pre-registrado)</t>
+          <t>P1-H1: mediana del t de las 500 permutaciones de los shocks (intervalo: 95 % central)</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>F5_P1_H1_beta</t>
+          <t>F5_P1_H1_T</t>
         </is>
       </c>
       <c r="B447" s="2" t="n">
-        <v>0.059</v>
+        <v>0.14</v>
       </c>
       <c r="C447" s="2" t="n"/>
       <c r="D447" s="2" t="n"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -31383,11 +31437,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H447" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31410,24 +31459,24 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>P1-H1: asociación con tasa_empleo (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-H1: t de la especificación principal con el error BHJ</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>F5_P1_H1_p</t>
+          <t>F5_P1_H1_WCBT_p</t>
         </is>
       </c>
       <c r="B448" s="2" t="n">
-        <v>0.892</v>
+        <v>0.914</v>
       </c>
       <c r="C448" s="2" t="n"/>
       <c r="D448" s="2" t="n"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -31457,24 +31506,24 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>P1-H1: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-H1: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>F5_P1_H2_CTRL_CUOTA_1998</t>
+          <t>F5_P1_H1_WCB_p</t>
         </is>
       </c>
       <c r="B449" s="2" t="n">
-        <v>-0.357</v>
+        <v>0.914</v>
       </c>
       <c r="C449" s="2" t="n"/>
       <c r="D449" s="2" t="n"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -31482,11 +31531,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H449" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31509,24 +31553,24 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>P1-H2 con el control de cuotas «cuota_1998» (F al nivel del shock = 10.0; p AKM0 sin ajustar = 0.158)</t>
+          <t>P1-H1: p del wild cluster bootstrap de la forma reducida agrupando por comunidad autónoma (Webb, 17 grupos; pre-registrado)</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>F5_P1_H2_CTRL_CUOTA_1998_p</t>
+          <t>F5_P1_H1_beta</t>
         </is>
       </c>
       <c r="B450" s="2" t="n">
-        <v>0.158</v>
+        <v>0.059</v>
       </c>
       <c r="C450" s="2" t="n"/>
       <c r="D450" s="2" t="n"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -31534,6 +31578,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H450" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31556,24 +31605,24 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>P1-H2, control «cuota_1998»: p AKM0 sin ajustar</t>
+          <t>P1-H1: asociación con tasa_empleo (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>F5_P1_H2_CTRL_ORIGINAL</t>
+          <t>F5_P1_H1_p</t>
         </is>
       </c>
       <c r="B451" s="2" t="n">
-        <v>0.282</v>
+        <v>0.892</v>
       </c>
       <c r="C451" s="2" t="n"/>
       <c r="D451" s="2" t="n"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -31581,11 +31630,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H451" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31608,24 +31652,24 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>P1-H2 con el control de cuotas «original» (F al nivel del shock = 6.6; p AKM0 sin ajustar = 0.247)</t>
+          <t>P1-H1: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>F5_P1_H2_CTRL_ORIGINAL_p</t>
+          <t>F5_P1_H2_CTRL_CUOTA_1998</t>
         </is>
       </c>
       <c r="B452" s="2" t="n">
-        <v>0.247</v>
+        <v>-0.357</v>
       </c>
       <c r="C452" s="2" t="n"/>
       <c r="D452" s="2" t="n"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -31633,6 +31677,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H452" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31655,24 +31704,24 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>P1-H2, control «original»: p AKM0 sin ajustar</t>
+          <t>P1-H2 con el control de cuotas «cuota_1998» (F al nivel del shock = 10.0; p AKM0 sin ajustar = 0.158)</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MNEG</t>
+          <t>F5_P1_H2_CTRL_CUOTA_1998_p</t>
         </is>
       </c>
       <c r="B453" s="2" t="n">
-        <v>11</v>
+        <v>0.158</v>
       </c>
       <c r="C453" s="2" t="n"/>
       <c r="D453" s="2" t="n"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -31687,7 +31736,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -31702,24 +31751,24 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P1-H2, control «cuota_1998»: p AKM0 sin ajustar</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MREJ</t>
+          <t>F5_P1_H2_CTRL_ORIGINAL</t>
         </is>
       </c>
       <c r="B454" s="2" t="n">
-        <v>2</v>
+        <v>0.282</v>
       </c>
       <c r="C454" s="2" t="n"/>
       <c r="D454" s="2" t="n"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -31727,6 +31776,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H454" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31734,7 +31788,7 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -31749,24 +31803,24 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P1-H2 con el control de cuotas «original» (F al nivel del shock = 6.6; p AKM0 sin ajustar = 0.247)</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MREJN</t>
+          <t>F5_P1_H2_CTRL_ORIGINAL_p</t>
         </is>
       </c>
       <c r="B455" s="2" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="C455" s="2" t="n"/>
       <c r="D455" s="2" t="n"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -31781,7 +31835,7 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -31796,18 +31850,18 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P1-H2, control «original»: p AKM0 sin ajustar</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MREJP</t>
+          <t>F5_P1_H2_MNEG</t>
         </is>
       </c>
       <c r="B456" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C456" s="2" t="n"/>
       <c r="D456" s="2" t="n"/>
@@ -31843,28 +31897,24 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P1-H2: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_FUERTE_MED</t>
+          <t>F5_P1_H2_MREJ</t>
         </is>
       </c>
       <c r="B457" s="2" t="n">
-        <v>-0.479</v>
-      </c>
-      <c r="C457" s="2" t="n">
-        <v>-0.554</v>
-      </c>
-      <c r="D457" s="2" t="n">
-        <v>-0.375</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C457" s="2" t="n"/>
+      <c r="D457" s="2" t="n"/>
       <c r="E457" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -31872,11 +31922,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H457" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -31899,18 +31944,18 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>P1-H2: mediana de β en las especificaciones del multiverso con F al nivel del shock ≥ 10 (5 de 32; intervalo: mínimo y máximo)</t>
+          <t>P1-H2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_FUERTE_N</t>
+          <t>F5_P1_H2_MREJN</t>
         </is>
       </c>
       <c r="B458" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C458" s="2" t="n"/>
       <c r="D458" s="2" t="n"/>
@@ -31946,28 +31991,24 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso con F al nivel del shock ≥ 10</t>
+          <t>P1-H2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_MED</t>
+          <t>F5_P1_H2_MREJP</t>
         </is>
       </c>
       <c r="B459" s="2" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="C459" s="2" t="n">
-        <v>-0.631</v>
-      </c>
-      <c r="D459" s="2" t="n">
-        <v>5.533</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C459" s="2" t="n"/>
+      <c r="D459" s="2" t="n"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -31975,11 +32016,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H459" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -32002,24 +32038,28 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>P1-H2: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
+          <t>P1-H2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_NEG</t>
+          <t>F5_P1_H2_MULT_FUERTE_MED</t>
         </is>
       </c>
       <c r="B460" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C460" s="2" t="n"/>
-      <c r="D460" s="2" t="n"/>
+        <v>-0.479</v>
+      </c>
+      <c r="C460" s="2" t="n">
+        <v>-0.554</v>
+      </c>
+      <c r="D460" s="2" t="n">
+        <v>-0.375</v>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -32027,6 +32067,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H460" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -32049,18 +32094,18 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso con β negativo (de 32)</t>
+          <t>P1-H2: mediana de β en las especificaciones del multiverso con F al nivel del shock ≥ 10 (5 de 32; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>F5_P1_H2_MULT_RECHAZA</t>
+          <t>F5_P1_H2_MULT_FUERTE_N</t>
         </is>
       </c>
       <c r="B461" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C461" s="2" t="n"/>
       <c r="D461" s="2" t="n"/>
@@ -32096,24 +32141,24 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>P1-H2: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
+          <t>P1-H2: especificaciones del multiverso con F al nivel del shock ≥ 10</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>F5_P1_H2_NACIONALIDAD</t>
+          <t>F5_P1_H2_MULT_MED</t>
         </is>
       </c>
       <c r="B462" s="2" t="n">
-        <v>0.116</v>
+        <v>0.284</v>
       </c>
       <c r="C462" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.631</v>
       </c>
       <c r="D462" s="2" t="n">
-        <v>0.68</v>
+        <v>5.533</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -32137,7 +32182,7 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -32152,28 +32197,24 @@
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t>P1-H2: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 18.4; IC: conjunto AKM0, acotado = True)</t>
+          <t>P1-H2: mediana de β en el multiverso pre-registrado (32 especificaciones; intervalo: mínimo y máximo)</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>F5_P1_H2_NACT</t>
+          <t>F5_P1_H2_MULT_NEG</t>
         </is>
       </c>
       <c r="B463" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C463" s="2" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="D463" s="2" t="n">
-        <v>0.68</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C463" s="2" t="n"/>
+      <c r="D463" s="2" t="n"/>
       <c r="E463" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -32181,11 +32222,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H463" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -32193,7 +32229,7 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -32208,24 +32244,24 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t>P1-H2: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P1-H2: especificaciones del multiverso con β negativo (de 32)</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>F5_P1_H2_PERMR_p</t>
+          <t>F5_P1_H2_MULT_RECHAZA</t>
         </is>
       </c>
       <c r="B464" s="2" t="n">
-        <v>0.026</v>
+        <v>2</v>
       </c>
       <c r="C464" s="2" t="n"/>
       <c r="D464" s="2" t="n"/>
       <c r="E464" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -32240,7 +32276,7 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -32255,28 +32291,28 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>P1-H2: p de permutación recentrado</t>
+          <t>P1-H2: especificaciones del multiverso cuyo AKM0 rechaza β = 0 al 5 % sin ajuste (de 32)</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>F5_P1_H2_PERM_MED</t>
+          <t>F5_P1_H2_NACIONALIDAD</t>
         </is>
       </c>
       <c r="B465" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.116</v>
       </c>
       <c r="C465" s="2" t="n">
-        <v>-1.3</v>
+        <v>-0.44</v>
       </c>
       <c r="D465" s="2" t="n">
-        <v>1.07</v>
+        <v>0.68</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -32284,6 +32320,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H465" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -32306,24 +32347,28 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>P1-H2: mediana del t de las 500 permutaciones de los shocks (intervalo: 95 % central)</t>
+          <t>P1-H2: variante con instrumento y tratamiento por nacionalidad (F al nivel del shock = 18.4; IC: conjunto AKM0, acotado = True)</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>F5_P1_H2_T</t>
+          <t>F5_P1_H2_NACT</t>
         </is>
       </c>
       <c r="B466" s="2" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="C466" s="2" t="n"/>
-      <c r="D466" s="2" t="n"/>
+        <v>0.12</v>
+      </c>
+      <c r="C466" s="2" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="D466" s="2" t="n">
+        <v>0.68</v>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -32331,6 +32376,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H466" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -32353,18 +32403,18 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>P1-H2: t de la especificación principal con el error BHJ</t>
+          <t>P1-H2: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>F5_P1_H2_WCBT_p</t>
+          <t>F5_P1_H2_PERMR_p</t>
         </is>
       </c>
       <c r="B467" s="2" t="n">
-        <v>0.303</v>
+        <v>0.026</v>
       </c>
       <c r="C467" s="2" t="n"/>
       <c r="D467" s="2" t="n"/>
@@ -32400,24 +32450,28 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>P1-H2: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P1-H2: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>F5_P1_H2_WCB_p</t>
+          <t>F5_P1_H2_PERM_MED</t>
         </is>
       </c>
       <c r="B468" s="2" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="C468" s="2" t="n"/>
-      <c r="D468" s="2" t="n"/>
+        <v>-0.02</v>
+      </c>
+      <c r="C468" s="2" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="D468" s="2" t="n">
+        <v>1.07</v>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -32447,24 +32501,24 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>P1-H2: p del wild cluster bootstrap de la forma reducida agrupando por comunidad autónoma (Webb, 17 grupos; pre-registrado)</t>
+          <t>P1-H2: mediana del t de las 500 permutaciones de los shocks (intervalo: 95 % central)</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>F5_P1_H2_beta</t>
+          <t>F5_P1_H2_T</t>
         </is>
       </c>
       <c r="B469" s="2" t="n">
-        <v>-0.554</v>
+        <v>-1.57</v>
       </c>
       <c r="C469" s="2" t="n"/>
       <c r="D469" s="2" t="n"/>
       <c r="E469" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>t</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -32472,11 +32526,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H469" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -32499,24 +32548,24 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>P1-H2: asociación con tasa_paro (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P1-H2: t de la especificación principal con el error BHJ</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>F5_P1_H2_p</t>
+          <t>F5_P1_H2_WCBT_p</t>
         </is>
       </c>
       <c r="B470" s="2" t="n">
-        <v>0.366</v>
+        <v>0.303</v>
       </c>
       <c r="C470" s="2" t="n"/>
       <c r="D470" s="2" t="n"/>
       <c r="E470" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -32546,24 +32595,24 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>P1-H2: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P1-H2: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>F5_P1_PRETEND_CORR</t>
+          <t>F5_P1_H2_WCB_p</t>
         </is>
       </c>
       <c r="B471" s="2" t="n">
-        <v>0.97</v>
+        <v>0.303</v>
       </c>
       <c r="C471" s="2" t="n"/>
       <c r="D471" s="2" t="n"/>
       <c r="E471" t="inlineStr">
         <is>
-          <t>correlación</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -32573,7 +32622,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>1998-2009</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -32583,34 +32632,34 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>padrón (INE)</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>Correlación entre el instrumento del periodo A y el del periodo previo 1998-2005 (pretendencia)</t>
+          <t>P1-H2: p del wild cluster bootstrap de la forma reducida agrupando por comunidad autónoma (Webb, 17 grupos; pre-registrado)</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>F5_P1_PRETEND_p</t>
+          <t>F5_P1_H2_beta</t>
         </is>
       </c>
       <c r="B472" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.554</v>
       </c>
       <c r="C472" s="2" t="n"/>
       <c r="D472" s="2" t="n"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -32618,9 +32667,14 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>1999-2001</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -32630,34 +32684,34 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>TGSS y padrón</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>p de la pretendencia (Δ log afiliación 1999-2001 sobre z_A, controlando z_P0)</t>
+          <t>P1-H2: asociación con tasa_paro (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>F5_P1_ROT_1</t>
+          <t>F5_P1_H2_p</t>
         </is>
       </c>
       <c r="B473" s="2" t="n">
-        <v>0.306</v>
+        <v>0.366</v>
       </c>
       <c r="C473" s="2" t="n"/>
       <c r="D473" s="2" t="n"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>peso de Rotemberg</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -32677,7 +32731,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -32687,24 +32741,24 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Peso de Rotemberg n.º 1: Rumanía|A (β del origen = 0.73), P1-H1</t>
+          <t>P1-H2: p de AKM0 frente a β = 0 ajustado (Holm); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>F5_P1_ROT_2</t>
+          <t>F5_P1_PRETEND_CORR</t>
         </is>
       </c>
       <c r="B474" s="2" t="n">
-        <v>0.188</v>
+        <v>0.97</v>
       </c>
       <c r="C474" s="2" t="n"/>
       <c r="D474" s="2" t="n"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>peso de Rotemberg</t>
+          <t>correlación</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -32714,7 +32768,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>1998-2009</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -32729,29 +32783,29 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>padrón (INE)</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>Peso de Rotemberg n.º 2: Venezuela|C (β del origen = -0.74), P1-H1</t>
+          <t>Correlación entre el instrumento del periodo A y el del periodo previo 1998-2005 (pretendencia)</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>F5_P1_ROT_3</t>
+          <t>F5_P1_PRETEND_p</t>
         </is>
       </c>
       <c r="B475" s="2" t="n">
-        <v>0.152</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C475" s="2" t="n"/>
       <c r="D475" s="2" t="n"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>peso de Rotemberg</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -32761,7 +32815,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>2005-2022</t>
+          <t>1999-2001</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -32776,23 +32830,23 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>padrón, ECP, EPA (INE)</t>
+          <t>TGSS y padrón</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>Peso de Rotemberg n.º 3: Marruecos|A (β del origen = -0.76), P1-H1</t>
+          <t>p de la pretendencia (Δ log afiliación 1999-2001 sobre z_A, controlando z_P0)</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>F5_P1_ROT_4</t>
+          <t>F5_P1_ROT_1</t>
         </is>
       </c>
       <c r="B476" s="2" t="n">
-        <v>0.149</v>
+        <v>0.306</v>
       </c>
       <c r="C476" s="2" t="n"/>
       <c r="D476" s="2" t="n"/>
@@ -32828,18 +32882,18 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>Peso de Rotemberg n.º 4: Marruecos|C (β del origen = -0.20), P1-H1</t>
+          <t>Peso de Rotemberg n.º 1: Rumanía|A (β del origen = 0.73), P1-H1</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>F5_P1_ROT_5</t>
+          <t>F5_P1_ROT_2</t>
         </is>
       </c>
       <c r="B477" s="2" t="n">
-        <v>-0.134</v>
+        <v>0.188</v>
       </c>
       <c r="C477" s="2" t="n"/>
       <c r="D477" s="2" t="n"/>
@@ -32875,24 +32929,24 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>Peso de Rotemberg n.º 5: Reino Unido|A (β del origen = -0.20), P1-H1</t>
+          <t>Peso de Rotemberg n.º 2: Venezuela|C (β del origen = -0.74), P1-H1</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>F5_P1_ROT_NEG</t>
+          <t>F5_P1_ROT_3</t>
         </is>
       </c>
       <c r="B478" s="2" t="n">
-        <v>18.8</v>
+        <v>0.152</v>
       </c>
       <c r="C478" s="2" t="n"/>
       <c r="D478" s="2" t="n"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>% del peso absoluto</t>
+          <t>peso de Rotemberg</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -32922,24 +32976,24 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>Peso de Rotemberg negativo entre los 15 mayores pesos absolutos, P1-H1</t>
+          <t>Peso de Rotemberg n.º 3: Marruecos|A (β del origen = -0.76), P1-H1</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>F5_P2_E1_MNEG</t>
+          <t>F5_P1_ROT_4</t>
         </is>
       </c>
       <c r="B479" s="2" t="n">
-        <v>18</v>
+        <v>0.149</v>
       </c>
       <c r="C479" s="2" t="n"/>
       <c r="D479" s="2" t="n"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>peso de Rotemberg</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -32954,12 +33008,12 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
@@ -32969,24 +33023,24 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>P2-E1: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>Peso de Rotemberg n.º 4: Marruecos|C (β del origen = -0.20), P1-H1</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>F5_P2_E1_MREJ</t>
+          <t>F5_P1_ROT_5</t>
         </is>
       </c>
       <c r="B480" s="2" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
       <c r="C480" s="2" t="n"/>
       <c r="D480" s="2" t="n"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>peso de Rotemberg</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -33001,12 +33055,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -33016,24 +33070,24 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>P2-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>Peso de Rotemberg n.º 5: Reino Unido|A (β del origen = -0.20), P1-H1</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>F5_P2_E1_MREJN</t>
+          <t>F5_P1_ROT_NEG</t>
         </is>
       </c>
       <c r="B481" s="2" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="C481" s="2" t="n"/>
       <c r="D481" s="2" t="n"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>% del peso absoluto</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -33048,12 +33102,12 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>nacidos en España</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
@@ -33063,18 +33117,18 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>P2-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>Peso de Rotemberg negativo entre los 15 mayores pesos absolutos, P1-H1</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>F5_P2_E1_MREJP</t>
+          <t>F5_P2_E1_MNEG</t>
         </is>
       </c>
       <c r="B482" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C482" s="2" t="n"/>
       <c r="D482" s="2" t="n"/>
@@ -33110,28 +33164,24 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>P2-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P2-E1: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>F5_P2_E1_NACT</t>
+          <t>F5_P2_E1_MREJ</t>
         </is>
       </c>
       <c r="B483" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C483" s="2" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="D483" s="2" t="n">
-        <v>0.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C483" s="2" t="n"/>
+      <c r="D483" s="2" t="n"/>
       <c r="E483" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -33139,11 +33189,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H483" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -33151,7 +33196,7 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -33166,24 +33211,24 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>P2-E1: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P2-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>F5_P2_E1_PERMR_p</t>
+          <t>F5_P2_E1_MREJN</t>
         </is>
       </c>
       <c r="B484" s="2" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="C484" s="2" t="n"/>
       <c r="D484" s="2" t="n"/>
       <c r="E484" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -33198,7 +33243,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -33213,24 +33258,24 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>P2-E1: p de permutación recentrado</t>
+          <t>P2-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>F5_P2_E1_WCBT_p</t>
+          <t>F5_P2_E1_MREJP</t>
         </is>
       </c>
       <c r="B485" s="2" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="C485" s="2" t="n"/>
       <c r="D485" s="2" t="n"/>
       <c r="E485" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -33245,7 +33290,7 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -33260,21 +33305,25 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>P2-E1: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P2-E1: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>F5_P2_E1_beta</t>
+          <t>F5_P2_E1_NACT</t>
         </is>
       </c>
       <c r="B486" s="2" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="C486" s="2" t="n"/>
-      <c r="D486" s="2" t="n"/>
+        <v>0.11</v>
+      </c>
+      <c r="C486" s="2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="D486" s="2" t="n">
+        <v>0.37</v>
+      </c>
       <c r="E486" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -33312,24 +33361,24 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>P2-E1: asociación con cuota_nomanual (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P2-E1: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>F5_P2_E1_p</t>
+          <t>F5_P2_E1_PERMR_p</t>
         </is>
       </c>
       <c r="B487" s="2" t="n">
-        <v>0.752</v>
+        <v>0.586</v>
       </c>
       <c r="C487" s="2" t="n"/>
       <c r="D487" s="2" t="n"/>
       <c r="E487" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -33359,24 +33408,24 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>P2-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P2-E1: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>F5_P2_E2_MNEG</t>
+          <t>F5_P2_E1_WCBT_p</t>
         </is>
       </c>
       <c r="B488" s="2" t="n">
-        <v>12</v>
+        <v>0.75</v>
       </c>
       <c r="C488" s="2" t="n"/>
       <c r="D488" s="2" t="n"/>
       <c r="E488" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -33391,7 +33440,7 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -33406,24 +33455,24 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>P2-E2: especificaciones del multiverso (de 32) con β negativo</t>
+          <t>P2-E1: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>F5_P2_E2_MREJ</t>
+          <t>F5_P2_E1_beta</t>
         </is>
       </c>
       <c r="B489" s="2" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="C489" s="2" t="n"/>
       <c r="D489" s="2" t="n"/>
       <c r="E489" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -33431,6 +33480,11 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H489" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -33438,7 +33492,7 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -33453,24 +33507,24 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>P2-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
+          <t>P2-E1: asociación con cuota_nomanual (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>F5_P2_E2_MREJN</t>
+          <t>F5_P2_E1_p</t>
         </is>
       </c>
       <c r="B490" s="2" t="n">
-        <v>0</v>
+        <v>0.752</v>
       </c>
       <c r="C490" s="2" t="n"/>
       <c r="D490" s="2" t="n"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>especificaciones</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -33485,7 +33539,7 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>provincias</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
@@ -33500,18 +33554,18 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>P2-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
+          <t>P2-E1: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>F5_P2_E2_MREJP</t>
+          <t>F5_P2_E2_MNEG</t>
         </is>
       </c>
       <c r="B491" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C491" s="2" t="n"/>
       <c r="D491" s="2" t="n"/>
@@ -33547,28 +33601,24 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>P2-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
+          <t>P2-E2: especificaciones del multiverso (de 32) con β negativo</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>F5_P2_E2_NACT</t>
+          <t>F5_P2_E2_MREJ</t>
         </is>
       </c>
       <c r="B492" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C492" s="2" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="D492" s="2" t="n">
-        <v>0.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C492" s="2" t="n"/>
+      <c r="D492" s="2" t="n"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -33576,11 +33626,6 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H492" t="inlineStr">
         <is>
           <t>2005-2022</t>
@@ -33588,7 +33633,7 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
@@ -33603,24 +33648,24 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>P2-E2: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
+          <t>P2-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>F5_P2_E2_PERMR_p</t>
+          <t>F5_P2_E2_MREJN</t>
         </is>
       </c>
       <c r="B493" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C493" s="2" t="n"/>
       <c r="D493" s="2" t="n"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -33635,7 +33680,7 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -33650,24 +33695,24 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>P2-E2: p de permutación recentrado</t>
+          <t>P2-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β negativo</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>F5_P2_E2_WCBT_p</t>
+          <t>F5_P2_E2_MREJP</t>
         </is>
       </c>
       <c r="B494" s="2" t="n">
-        <v>0.336</v>
+        <v>0</v>
       </c>
       <c r="C494" s="2" t="n"/>
       <c r="D494" s="2" t="n"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>especificaciones</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -33682,7 +33727,7 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>50 provincias</t>
+          <t>provincias</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
@@ -33697,21 +33742,25 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>P2-E2: p del wild bootstrap por comunidad (forma reducida)</t>
+          <t>P2-E2: especificaciones del multiverso que rechazan β = 0 al 5 % sin ajuste con β positivo</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>F5_P2_E2_beta</t>
+          <t>F5_P2_E2_NACT</t>
         </is>
       </c>
       <c r="B495" s="2" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="C495" s="2" t="n"/>
-      <c r="D495" s="2" t="n"/>
+        <v>0.21</v>
+      </c>
+      <c r="C495" s="2" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="D495" s="2" t="n">
+        <v>0.74</v>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -33749,24 +33798,24 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>P2-E2: asociación con cuota_alta_cualif (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
+          <t>P2-E2: variante por nacionalidad (IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>F5_P2_E2_p</t>
+          <t>F5_P2_E2_PERMR_p</t>
         </is>
       </c>
       <c r="B496" s="2" t="n">
-        <v>0.745</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C496" s="2" t="n"/>
       <c r="D496" s="2" t="n"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>p ajustado</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -33796,28 +33845,24 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>P2-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
+          <t>P2-E2: p de permutación recentrado</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>F5_P3_EDUC_beta</t>
+          <t>F5_P2_E2_WCBT_p</t>
         </is>
       </c>
       <c r="B497" s="2" t="n">
-        <v>-0.169</v>
-      </c>
-      <c r="C497" s="2" t="n">
-        <v>-0.752</v>
-      </c>
-      <c r="D497" s="2" t="n">
-        <v>0.414</v>
-      </c>
+        <v>0.336</v>
+      </c>
+      <c r="C497" s="2" t="n"/>
+      <c r="D497" s="2" t="n"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>alumnos por profesor por punto porcentual</t>
+          <t>p</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -33825,45 +33870,40 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>2016-2022</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>17 CCAA</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>EDUCAbase, ECP y padrón</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>P3 (educación): asociación entre el aumento de la población nacida fuera de 5-19 años y la ratio de alumnos por profesor en centros públicos (MC2E por comunidad; F efectivo = 39.5; p wild bootstrap de la forma reducida = 0.58; IC orientativo por errores agrupados en 17 comunidades)</t>
+          <t>P2-E2: p del wild bootstrap por comunidad (forma reducida)</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>F5_P5_HET_centro_y_este</t>
+          <t>F5_P2_E2_beta</t>
         </is>
       </c>
       <c r="B498" s="2" t="n">
-        <v>0.027</v>
+        <v>0.739</v>
       </c>
       <c r="C498" s="2" t="n"/>
       <c r="D498" s="2" t="n"/>
@@ -33884,44 +33924,44 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>NUTS2, centro y este</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>P5, países centro y este: β leave-one-country-out (28 regiones; p wild bootstrap = 0.94)</t>
+          <t>P2-E2: asociación con cuota_alta_cualif (MC2E, especificación principal; IC: envolvente del conjunto AKM0)</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>F5_P5_HET_continentales</t>
+          <t>F5_P2_E2_p</t>
         </is>
       </c>
       <c r="B499" s="2" t="n">
-        <v>-0.163</v>
+        <v>0.745</v>
       </c>
       <c r="C499" s="2" t="n"/>
       <c r="D499" s="2" t="n"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>p ajustado</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -33929,51 +33969,50 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>ASOCIACIÓN</t>
-        </is>
-      </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2005-2022</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>NUTS2, continentales</t>
+          <t>50 provincias</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>nacidos en España</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>padrón, ECP, EPA (INE)</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>P5, países continentales: β leave-one-country-out (93 regiones; p wild bootstrap = 0.80)</t>
+          <t>P2-E2: p de AKM0 frente a β = 0 ajustado (BH); el conjunto AKM0 puede no estar acotado aunque el p sea pequeño</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>F5_P5_HET_mediterráneos</t>
+          <t>F5_P3_EDUC_beta</t>
         </is>
       </c>
       <c r="B500" s="2" t="n">
-        <v>-0.501</v>
-      </c>
-      <c r="C500" s="2" t="n"/>
-      <c r="D500" s="2" t="n"/>
+        <v>-0.169</v>
+      </c>
+      <c r="C500" s="2" t="n">
+        <v>-0.752</v>
+      </c>
+      <c r="D500" s="2" t="n">
+        <v>0.414</v>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>pp por pp</t>
+          <t>alumnos por profesor por punto porcentual</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -33988,38 +34027,38 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>2021-2024</t>
+          <t>2016-2022</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>NUTS2, mediterráneos</t>
+          <t>17 CCAA</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>nativos</t>
+          <t>todos</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>EDUCAbase, ECP y padrón</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>P5, países mediterráneos: β leave-one-country-out (57 regiones; p wild bootstrap = 0.31)</t>
+          <t>P3 (educación): asociación entre el aumento de la población nacida fuera de 5-19 años y la ratio de alumnos por profesor en centros públicos (MC2E por comunidad; F efectivo = 39.5; p wild bootstrap de la forma reducida = 0.58; IC orientativo por errores agrupados en 17 comunidades)</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>F5_P5_HET_nórdicos</t>
+          <t>F5_P5_HET_centro_y_este</t>
         </is>
       </c>
       <c r="B501" s="2" t="n">
-        <v>-0.904</v>
+        <v>0.027</v>
       </c>
       <c r="C501" s="2" t="n"/>
       <c r="D501" s="2" t="n"/>
@@ -34045,7 +34084,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>NUTS2, nórdicos</t>
+          <t>NUTS2, centro y este</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -34060,25 +34099,21 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>P5, países nórdicos: β leave-one-country-out (17 regiones; p wild bootstrap = 0.33)</t>
+          <t>P5, países centro y este: β leave-one-country-out (28 regiones; p wild bootstrap = 0.94)</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>F5_P5_beta</t>
+          <t>F5_P5_HET_continentales</t>
         </is>
       </c>
       <c r="B502" s="2" t="n">
-        <v>-0.325</v>
-      </c>
-      <c r="C502" s="2" t="n">
-        <v>-0.968</v>
-      </c>
-      <c r="D502" s="2" t="n">
-        <v>0.318</v>
-      </c>
+        <v>-0.163</v>
+      </c>
+      <c r="C502" s="2" t="n"/>
+      <c r="D502" s="2" t="n"/>
       <c r="E502" t="inlineStr">
         <is>
           <t>pp por pp</t>
@@ -34101,7 +34136,7 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>NUTS2 UE-27</t>
+          <t>NUTS2, continentales</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -34111,29 +34146,29 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Eurostat (censo 2021, migr_imm3ctb, EU-LFS)</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>P5: asociación entre la llegada de población nacida fuera y la tasa de empleo de los nativos, NUTS2 de la UE-27, 2021-2024 (MC2E leave-one-country-out; p wild bootstrap por país = 0.38; IC orientativo por errores agrupados por país)</t>
+          <t>P5, países continentales: β leave-one-country-out (93 regiones; p wild bootstrap = 0.80)</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
+          <t>F5_P5_HET_mediterráneos</t>
         </is>
       </c>
       <c r="B503" s="2" t="n">
-        <v>1.02</v>
+        <v>-0.501</v>
       </c>
       <c r="C503" s="2" t="n"/>
       <c r="D503" s="2" t="n"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -34141,46 +34176,51 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2, mediterráneos</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>P5, países mediterráneos: β leave-one-country-out (57 regiones; p wild bootstrap = 0.31)</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
+          <t>F5_P5_HET_nórdicos</t>
         </is>
       </c>
       <c r="B504" s="2" t="n">
-        <v>0.84</v>
+        <v>-0.904</v>
       </c>
       <c r="C504" s="2" t="n"/>
       <c r="D504" s="2" t="n"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -34188,46 +34228,55 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2, nórdicos</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>P5, países nórdicos: β leave-one-country-out (17 regiones; p wild bootstrap = 0.33)</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
+          <t>F5_P5_beta</t>
         </is>
       </c>
       <c r="B505" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="C505" s="2" t="n"/>
-      <c r="D505" s="2" t="n"/>
+        <v>-0.325</v>
+      </c>
+      <c r="C505" s="2" t="n">
+        <v>-0.968</v>
+      </c>
+      <c r="D505" s="2" t="n">
+        <v>0.318</v>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>razón (nativos = 1)</t>
+          <t>pp por pp</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -34235,40 +34284,45 @@
           <t>C4</t>
         </is>
       </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>ASOCIACIÓN</t>
+        </is>
+      </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021-2024</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>NUTS2 UE-27</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>nacidos fuera</t>
+          <t>nativos</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>ENSE 2017 (INE)</t>
+          <t>Eurostat (censo 2021, migr_imm3ctb, EU-LFS)</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>P5: asociación entre la llegada de población nacida fuera y la tasa de empleo de los nativos, NUTS2 de la UE-27, 2021-2024 (MC2E leave-one-country-out; p wild bootstrap por país = 0.38; IC orientativo por errores agrupados por país)</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_15_34</t>
+          <t>F6_ENSE_RAZON_CONSULTAS_15_34</t>
         </is>
       </c>
       <c r="B506" s="2" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="C506" s="2" t="n"/>
       <c r="D506" s="2" t="n"/>
@@ -34304,18 +34358,18 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_35_54</t>
+          <t>F6_ENSE_RAZON_CONSULTAS_35_54</t>
         </is>
       </c>
       <c r="B507" s="2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="C507" s="2" t="n"/>
       <c r="D507" s="2" t="n"/>
@@ -34351,18 +34405,18 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_FAR_55_74</t>
+          <t>F6_ENSE_RAZON_CONSULTAS_55_74</t>
         </is>
       </c>
       <c r="B508" s="2" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="C508" s="2" t="n"/>
       <c r="D508" s="2" t="n"/>
@@ -34398,18 +34452,18 @@
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>Uso relativo de consultas de primaria y especialista: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_15_34</t>
+          <t>F6_ENSE_RAZON_FAR_15_34</t>
         </is>
       </c>
       <c r="B509" s="2" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="C509" s="2" t="n"/>
       <c r="D509" s="2" t="n"/>
@@ -34445,18 +34499,18 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_35_54</t>
+          <t>F6_ENSE_RAZON_FAR_35_54</t>
         </is>
       </c>
       <c r="B510" s="2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="C510" s="2" t="n"/>
       <c r="D510" s="2" t="n"/>
@@ -34492,18 +34546,18 @@
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_HOSP_55_74</t>
+          <t>F6_ENSE_RAZON_FAR_55_74</t>
         </is>
       </c>
       <c r="B511" s="2" t="n">
-        <v>2.58</v>
+        <v>0.85</v>
       </c>
       <c r="C511" s="2" t="n"/>
       <c r="D511" s="2" t="n"/>
@@ -34539,18 +34593,18 @@
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>Uso relativo de uso de medicamentos recetados: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_15_34</t>
+          <t>F6_ENSE_RAZON_HOSP_15_34</t>
         </is>
       </c>
       <c r="B512" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C512" s="2" t="n"/>
       <c r="D512" s="2" t="n"/>
@@ -34586,18 +34640,18 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_35_54</t>
+          <t>F6_ENSE_RAZON_HOSP_35_54</t>
         </is>
       </c>
       <c r="B513" s="2" t="n">
-        <v>1.16</v>
+        <v>0.82</v>
       </c>
       <c r="C513" s="2" t="n"/>
       <c r="D513" s="2" t="n"/>
@@ -34633,18 +34687,18 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>F6_ENSE_RAZON_URG_55_74</t>
+          <t>F6_ENSE_RAZON_HOSP_55_74</t>
         </is>
       </c>
       <c r="B514" s="2" t="n">
-        <v>1</v>
+        <v>2.58</v>
       </c>
       <c r="C514" s="2" t="n"/>
       <c r="D514" s="2" t="n"/>
@@ -34680,34 +34734,34 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
+          <t>Uso relativo de días de hospital: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>F6_POB_CUOTA_FUERA_ECV</t>
+          <t>F6_ENSE_RAZON_URG_15_34</t>
         </is>
       </c>
       <c r="B515" s="2" t="n">
-        <v>18.5</v>
+        <v>0.9</v>
       </c>
       <c r="C515" s="2" t="n"/>
       <c r="D515" s="2" t="n"/>
       <c r="E515" t="inlineStr">
         <is>
-          <t>% de la población</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -34722,39 +34776,39 @@
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>ECV (INE)</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 15-34 años (n nacidos fuera = 655)</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_España</t>
+          <t>F6_ENSE_RAZON_URG_35_54</t>
         </is>
       </c>
       <c r="B516" s="2" t="n">
-        <v>6252</v>
+        <v>1.16</v>
       </c>
       <c r="C516" s="2" t="n"/>
       <c r="D516" s="2" t="n"/>
       <c r="E516" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -34764,44 +34818,44 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>nacidos fuera</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 35-54 años (n nacidos fuera = 1126)</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
+          <t>F6_ENSE_RAZON_URG_55_74</t>
         </is>
       </c>
       <c r="B517" s="2" t="n">
-        <v>2813</v>
+        <v>1</v>
       </c>
       <c r="C517" s="2" t="n"/>
       <c r="D517" s="2" t="n"/>
       <c r="E517" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>razón (nativos = 1)</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -34811,34 +34865,34 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>Resto UE</t>
+          <t>nacidos fuera</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>ENSE 2017 (INE)</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+          <t>Uso relativo de urgencias: nacidos fuera / nacidos en España, 55-74 años (n nacidos fuera = 389)</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+          <t>F6_POB_CUOTA_FUERA_ECV</t>
         </is>
       </c>
       <c r="B518" s="2" t="n">
-        <v>1927</v>
+        <v>18.5</v>
       </c>
       <c r="C518" s="2" t="n"/>
       <c r="D518" s="2" t="n"/>
       <c r="E518" t="inlineStr">
         <is>
-          <t>€ por persona y año</t>
+          <t>% de la población</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -34858,34 +34912,34 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>Resto del mundo</t>
+          <t>nacidos fuera</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>ECV (INE) y Eurostat COFOG</t>
+          <t>ECV (INE)</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+          <t>Cuota de los nacidos fuera en la población de la ECV (hogares privados)</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+          <t>F6_PREST_MONETARIAS_PC_España</t>
         </is>
       </c>
       <c r="B519" s="2" t="n">
-        <v>2.5</v>
+        <v>6252</v>
       </c>
       <c r="C519" s="2" t="n"/>
       <c r="D519" s="2" t="n"/>
       <c r="E519" t="inlineStr">
         <is>
-          <t>% de las prestaciones monetarias</t>
+          <t>€ por persona y año</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -34905,7 +34959,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>todos</t>
+          <t>España</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
@@ -34915,52 +34969,193 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en España</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>F6_TRABAJO_CUOTA_FUERA</t>
+          <t>F6_PREST_MONETARIAS_PC_Resto_UE</t>
         </is>
       </c>
       <c r="B520" s="2" t="n">
-        <v>15.5</v>
+        <v>2813</v>
       </c>
       <c r="C520" s="2" t="n"/>
       <c r="D520" s="2" t="n"/>
       <c r="E520" t="inlineStr">
         <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Resto UE</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>F6_PREST_MONETARIAS_PC_Resto_del_mundo</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C521" s="2" t="n"/>
+      <c r="D521" s="2" t="n"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>€ por persona y año</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Resto del mundo</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Prestaciones monetarias por persona (calibradas a COFOG), nacidos en Resto del mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>F6_PREST_NO_CONTRIB_CUOTA</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C522" s="2" t="n"/>
+      <c r="D522" s="2" t="n"/>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>% de las prestaciones monetarias</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>ECV (INE) y Eurostat COFOG</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Rentas mínimas, IMV y ayudas a la vivienda sobre el total de prestaciones monetarias (calibradas a COFOG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>F6_TRABAJO_CUOTA_FUERA</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C523" s="2" t="n"/>
+      <c r="D523" s="2" t="n"/>
+      <c r="E523" t="inlineStr">
+        <is>
           <t>% del total</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr">
+      <c r="F523" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr">
+      <c r="H523" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="I520" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="J520" t="inlineStr">
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
         <is>
           <t>nacidos fuera</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr">
+      <c r="K523" t="inlineStr">
         <is>
           <t>ECV (INE) y Eurostat</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr">
+      <c r="L523" t="inlineStr">
         <is>
           <t>Cuota de los nacidos fuera en IRPF del trabajo y cotizaciones sociales (calibradas a las cuentas de las AAPP)</t>
         </is>

--- a/output/f7/tablas_m1.xlsx
+++ b/output/f7/tablas_m1.xlsx
@@ -9585,27 +9585,27 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Tasa de empleo</t>
+          <t>Tasa de empleo 16-64</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Tasa de paro</t>
+          <t>Tasa de paro (16 años o más)</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Temporalidad</t>
+          <t>Temporalidad (asalariados de 16 años o más)</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>Ocupados</t>
+          <t>Ocupados de 16 años o más (no dividir por la población 16-64)</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>Cuota de los ocupados</t>
+          <t>Cuota de los ocupados de 16 años o más</t>
         </is>
       </c>
     </row>
